--- a/data/mca-RBI_BSE_NSE_IFSCA_IG_links.xlsx
+++ b/data/mca-RBI_BSE_NSE_IFSCA_IG_links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="RBI"/>

--- a/data/mca-RBI_BSE_NSE_IFSCA_IG_links.xlsx
+++ b/data/mca-RBI_BSE_NSE_IFSCA_IG_links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="RBI"/>
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
-    <t>IBBI - Litigation</t>
+    <t/>
   </si>
   <si>
     <t>IFSCA</t>
@@ -185,12 +185,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
@@ -204,6 +204,9 @@
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -537,11 +540,11 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="31.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
@@ -549,15 +552,15 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="31.5">
-      <c r="A3" s="13" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="14" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="31.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -565,8 +568,8 @@
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="31.5">
-      <c r="A5" s="13" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="14" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -599,7 +602,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="61.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="61.43357142857143" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="6" width="13.005" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="6" width="13.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="13.005" customWidth="1" bestFit="1"/>
@@ -623,7 +626,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C1" s="1"/>
@@ -701,8 +704,8 @@
       <c r="U3" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -725,7 +728,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1"/>
-      <c r="B5" s="2"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -748,7 +751,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -771,7 +774,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -794,7 +797,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="1"/>
-      <c r="B8" s="2"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -817,7 +820,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
-      <c r="B9" s="2"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -840,7 +843,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="1"/>
-      <c r="B10" s="2"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -863,7 +866,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -886,7 +889,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -909,7 +912,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -932,7 +935,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -955,7 +958,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -978,7 +981,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1001,7 +1004,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1024,7 +1027,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
       <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1047,7 +1050,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
       <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1070,7 +1073,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
       <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="7"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1093,7 +1096,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18">
       <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1116,7 +1119,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18">
       <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -1139,7 +1142,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18">
       <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1162,7 +1165,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18">
       <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
+      <c r="B24" s="7"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1185,7 +1188,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
       <c r="A25" s="1"/>
-      <c r="B25" s="2"/>
+      <c r="B25" s="7"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1208,7 +1211,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18">
       <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1231,7 +1234,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18">
       <c r="A27" s="1"/>
-      <c r="B27" s="2"/>
+      <c r="B27" s="7"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1254,7 +1257,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18">
       <c r="A28" s="1"/>
-      <c r="B28" s="2"/>
+      <c r="B28" s="7"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1277,7 +1280,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18">
       <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1300,7 +1303,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18">
       <c r="A30" s="1"/>
-      <c r="B30" s="2"/>
+      <c r="B30" s="7"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1323,7 +1326,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18">
       <c r="A31" s="1"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="7"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1346,7 +1349,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18">
       <c r="A32" s="1"/>
-      <c r="B32" s="2"/>
+      <c r="B32" s="7"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1369,7 +1372,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18">
       <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="7"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1392,7 +1395,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18">
       <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
+      <c r="B34" s="7"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1415,7 +1418,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18">
       <c r="A35" s="1"/>
-      <c r="B35" s="2"/>
+      <c r="B35" s="7"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -1438,7 +1441,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18">
       <c r="A36" s="1"/>
-      <c r="B36" s="2"/>
+      <c r="B36" s="7"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -1461,7 +1464,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18">
       <c r="A37" s="1"/>
-      <c r="B37" s="2"/>
+      <c r="B37" s="7"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1484,7 +1487,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18">
       <c r="A38" s="1"/>
-      <c r="B38" s="2"/>
+      <c r="B38" s="7"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1507,7 +1510,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18">
       <c r="A39" s="1"/>
-      <c r="B39" s="2"/>
+      <c r="B39" s="7"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -1530,7 +1533,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18">
       <c r="A40" s="1"/>
-      <c r="B40" s="2"/>
+      <c r="B40" s="7"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -1553,7 +1556,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18">
       <c r="A41" s="1"/>
-      <c r="B41" s="2"/>
+      <c r="B41" s="7"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -1576,7 +1579,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18">
       <c r="A42" s="1"/>
-      <c r="B42" s="2"/>
+      <c r="B42" s="7"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -1599,7 +1602,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18">
       <c r="A43" s="1"/>
-      <c r="B43" s="2"/>
+      <c r="B43" s="7"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -1622,7 +1625,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18">
       <c r="A44" s="1"/>
-      <c r="B44" s="2"/>
+      <c r="B44" s="7"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -1645,7 +1648,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18">
       <c r="A45" s="1"/>
-      <c r="B45" s="2"/>
+      <c r="B45" s="7"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -1668,7 +1671,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18">
       <c r="A46" s="1"/>
-      <c r="B46" s="2"/>
+      <c r="B46" s="7"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -1691,7 +1694,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18">
       <c r="A47" s="1"/>
-      <c r="B47" s="2"/>
+      <c r="B47" s="7"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -1714,7 +1717,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18">
       <c r="A48" s="1"/>
-      <c r="B48" s="2"/>
+      <c r="B48" s="7"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1737,7 +1740,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18">
       <c r="A49" s="1"/>
-      <c r="B49" s="2"/>
+      <c r="B49" s="7"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1760,7 +1763,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18">
       <c r="A50" s="1"/>
-      <c r="B50" s="2"/>
+      <c r="B50" s="7"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -1783,7 +1786,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18">
       <c r="A51" s="1"/>
-      <c r="B51" s="2"/>
+      <c r="B51" s="7"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1806,7 +1809,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18">
       <c r="A52" s="1"/>
-      <c r="B52" s="2"/>
+      <c r="B52" s="7"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -1829,7 +1832,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18">
       <c r="A53" s="1"/>
-      <c r="B53" s="2"/>
+      <c r="B53" s="7"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -1852,7 +1855,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18">
       <c r="A54" s="1"/>
-      <c r="B54" s="2"/>
+      <c r="B54" s="7"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1875,7 +1878,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18">
       <c r="A55" s="1"/>
-      <c r="B55" s="2"/>
+      <c r="B55" s="7"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -1898,7 +1901,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18">
       <c r="A56" s="1"/>
-      <c r="B56" s="2"/>
+      <c r="B56" s="7"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -1921,7 +1924,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18">
       <c r="A57" s="1"/>
-      <c r="B57" s="2"/>
+      <c r="B57" s="7"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -1944,7 +1947,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18">
       <c r="A58" s="1"/>
-      <c r="B58" s="2"/>
+      <c r="B58" s="7"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -1967,7 +1970,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18">
       <c r="A59" s="1"/>
-      <c r="B59" s="2"/>
+      <c r="B59" s="7"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1990,7 +1993,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18">
       <c r="A60" s="1"/>
-      <c r="B60" s="2"/>
+      <c r="B60" s="7"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -2013,7 +2016,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18">
       <c r="A61" s="1"/>
-      <c r="B61" s="2"/>
+      <c r="B61" s="7"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -2036,7 +2039,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18">
       <c r="A62" s="1"/>
-      <c r="B62" s="2"/>
+      <c r="B62" s="7"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -2059,7 +2062,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18">
       <c r="A63" s="1"/>
-      <c r="B63" s="2"/>
+      <c r="B63" s="7"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -2082,7 +2085,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18">
       <c r="A64" s="1"/>
-      <c r="B64" s="2"/>
+      <c r="B64" s="7"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -2105,7 +2108,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18">
       <c r="A65" s="1"/>
-      <c r="B65" s="2"/>
+      <c r="B65" s="7"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -2128,7 +2131,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18">
       <c r="A66" s="1"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="7"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -2151,7 +2154,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18">
       <c r="A67" s="1"/>
-      <c r="B67" s="2"/>
+      <c r="B67" s="7"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -2174,7 +2177,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18">
       <c r="A68" s="1"/>
-      <c r="B68" s="2"/>
+      <c r="B68" s="7"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -2197,7 +2200,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18">
       <c r="A69" s="1"/>
-      <c r="B69" s="2"/>
+      <c r="B69" s="7"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -2220,7 +2223,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18">
       <c r="A70" s="1"/>
-      <c r="B70" s="2"/>
+      <c r="B70" s="7"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -2243,7 +2246,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18">
       <c r="A71" s="1"/>
-      <c r="B71" s="2"/>
+      <c r="B71" s="7"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -2266,7 +2269,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18">
       <c r="A72" s="1"/>
-      <c r="B72" s="2"/>
+      <c r="B72" s="7"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -2289,7 +2292,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18">
       <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
+      <c r="B73" s="7"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -2312,7 +2315,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18">
       <c r="A74" s="1"/>
-      <c r="B74" s="2"/>
+      <c r="B74" s="7"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -2335,7 +2338,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18">
       <c r="A75" s="1"/>
-      <c r="B75" s="2"/>
+      <c r="B75" s="7"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -2358,7 +2361,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18">
       <c r="A76" s="1"/>
-      <c r="B76" s="2"/>
+      <c r="B76" s="7"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -2381,7 +2384,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18">
       <c r="A77" s="1"/>
-      <c r="B77" s="2"/>
+      <c r="B77" s="7"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -2404,7 +2407,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18">
       <c r="A78" s="1"/>
-      <c r="B78" s="2"/>
+      <c r="B78" s="7"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -2427,7 +2430,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18">
       <c r="A79" s="1"/>
-      <c r="B79" s="2"/>
+      <c r="B79" s="7"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -2450,7 +2453,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18">
       <c r="A80" s="1"/>
-      <c r="B80" s="2"/>
+      <c r="B80" s="7"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -2473,7 +2476,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18">
       <c r="A81" s="1"/>
-      <c r="B81" s="2"/>
+      <c r="B81" s="7"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -2496,7 +2499,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18">
       <c r="A82" s="1"/>
-      <c r="B82" s="2"/>
+      <c r="B82" s="7"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -2519,7 +2522,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18">
       <c r="A83" s="1"/>
-      <c r="B83" s="2"/>
+      <c r="B83" s="7"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -2542,7 +2545,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18">
       <c r="A84" s="1"/>
-      <c r="B84" s="2"/>
+      <c r="B84" s="7"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -2565,7 +2568,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18">
       <c r="A85" s="1"/>
-      <c r="B85" s="2"/>
+      <c r="B85" s="7"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -2588,7 +2591,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18">
       <c r="A86" s="1"/>
-      <c r="B86" s="2"/>
+      <c r="B86" s="7"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -2611,7 +2614,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18">
       <c r="A87" s="1"/>
-      <c r="B87" s="2"/>
+      <c r="B87" s="7"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -2634,7 +2637,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18">
       <c r="A88" s="1"/>
-      <c r="B88" s="2"/>
+      <c r="B88" s="7"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -2657,7 +2660,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18">
       <c r="A89" s="1"/>
-      <c r="B89" s="2"/>
+      <c r="B89" s="7"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -2680,7 +2683,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18">
       <c r="A90" s="1"/>
-      <c r="B90" s="2"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -2703,7 +2706,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18">
       <c r="A91" s="1"/>
-      <c r="B91" s="2"/>
+      <c r="B91" s="7"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -2726,7 +2729,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18">
       <c r="A92" s="1"/>
-      <c r="B92" s="2"/>
+      <c r="B92" s="7"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
@@ -2749,7 +2752,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18">
       <c r="A93" s="1"/>
-      <c r="B93" s="2"/>
+      <c r="B93" s="7"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -2772,7 +2775,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18">
       <c r="A94" s="1"/>
-      <c r="B94" s="2"/>
+      <c r="B94" s="7"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -2795,7 +2798,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18">
       <c r="A95" s="1"/>
-      <c r="B95" s="2"/>
+      <c r="B95" s="7"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
@@ -2818,7 +2821,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18">
       <c r="A96" s="1"/>
-      <c r="B96" s="2"/>
+      <c r="B96" s="7"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
@@ -2841,7 +2844,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18">
       <c r="A97" s="1"/>
-      <c r="B97" s="2"/>
+      <c r="B97" s="7"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -2864,7 +2867,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18">
       <c r="A98" s="1"/>
-      <c r="B98" s="2"/>
+      <c r="B98" s="7"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
@@ -2887,7 +2890,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18">
       <c r="A99" s="1"/>
-      <c r="B99" s="2"/>
+      <c r="B99" s="7"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
@@ -2910,7 +2913,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18">
       <c r="A100" s="1"/>
-      <c r="B100" s="2"/>
+      <c r="B100" s="7"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
@@ -2933,7 +2936,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18">
       <c r="A101" s="1"/>
-      <c r="B101" s="2"/>
+      <c r="B101" s="7"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -2956,7 +2959,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18">
       <c r="A102" s="1"/>
-      <c r="B102" s="2"/>
+      <c r="B102" s="7"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -2979,7 +2982,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18">
       <c r="A103" s="1"/>
-      <c r="B103" s="2"/>
+      <c r="B103" s="7"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -3002,7 +3005,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18">
       <c r="A104" s="1"/>
-      <c r="B104" s="2"/>
+      <c r="B104" s="7"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -3025,7 +3028,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18">
       <c r="A105" s="1"/>
-      <c r="B105" s="2"/>
+      <c r="B105" s="7"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -3048,7 +3051,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18">
       <c r="A106" s="1"/>
-      <c r="B106" s="2"/>
+      <c r="B106" s="7"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -3071,7 +3074,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18">
       <c r="A107" s="1"/>
-      <c r="B107" s="2"/>
+      <c r="B107" s="7"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -3094,7 +3097,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18">
       <c r="A108" s="1"/>
-      <c r="B108" s="2"/>
+      <c r="B108" s="7"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -3117,7 +3120,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18">
       <c r="A109" s="1"/>
-      <c r="B109" s="2"/>
+      <c r="B109" s="7"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -3140,7 +3143,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18">
       <c r="A110" s="1"/>
-      <c r="B110" s="2"/>
+      <c r="B110" s="7"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -3163,7 +3166,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18">
       <c r="A111" s="1"/>
-      <c r="B111" s="2"/>
+      <c r="B111" s="7"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -3186,7 +3189,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18">
       <c r="A112" s="1"/>
-      <c r="B112" s="2"/>
+      <c r="B112" s="7"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
@@ -3209,7 +3212,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18">
       <c r="A113" s="1"/>
-      <c r="B113" s="2"/>
+      <c r="B113" s="7"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -3232,7 +3235,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18">
       <c r="A114" s="1"/>
-      <c r="B114" s="2"/>
+      <c r="B114" s="7"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
@@ -3255,7 +3258,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18">
       <c r="A115" s="1"/>
-      <c r="B115" s="2"/>
+      <c r="B115" s="7"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
@@ -3278,7 +3281,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18">
       <c r="A116" s="1"/>
-      <c r="B116" s="2"/>
+      <c r="B116" s="7"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -3301,7 +3304,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18">
       <c r="A117" s="1"/>
-      <c r="B117" s="2"/>
+      <c r="B117" s="7"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -3324,7 +3327,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18">
       <c r="A118" s="1"/>
-      <c r="B118" s="2"/>
+      <c r="B118" s="7"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -3347,7 +3350,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18">
       <c r="A119" s="1"/>
-      <c r="B119" s="2"/>
+      <c r="B119" s="7"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -3370,7 +3373,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18">
       <c r="A120" s="1"/>
-      <c r="B120" s="2"/>
+      <c r="B120" s="7"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -3393,7 +3396,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18">
       <c r="A121" s="1"/>
-      <c r="B121" s="2"/>
+      <c r="B121" s="7"/>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -3416,7 +3419,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18">
       <c r="A122" s="1"/>
-      <c r="B122" s="2"/>
+      <c r="B122" s="7"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -3439,7 +3442,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18">
       <c r="A123" s="1"/>
-      <c r="B123" s="2"/>
+      <c r="B123" s="7"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -3462,7 +3465,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18">
       <c r="A124" s="1"/>
-      <c r="B124" s="2"/>
+      <c r="B124" s="7"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -3485,7 +3488,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18">
       <c r="A125" s="1"/>
-      <c r="B125" s="2"/>
+      <c r="B125" s="7"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -3508,7 +3511,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18">
       <c r="A126" s="1"/>
-      <c r="B126" s="2"/>
+      <c r="B126" s="7"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -3531,7 +3534,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18">
       <c r="A127" s="1"/>
-      <c r="B127" s="2"/>
+      <c r="B127" s="7"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -3554,7 +3557,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18">
       <c r="A128" s="1"/>
-      <c r="B128" s="2"/>
+      <c r="B128" s="7"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -3577,7 +3580,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18">
       <c r="A129" s="1"/>
-      <c r="B129" s="2"/>
+      <c r="B129" s="7"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -3600,7 +3603,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18">
       <c r="A130" s="1"/>
-      <c r="B130" s="2"/>
+      <c r="B130" s="7"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -3623,7 +3626,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18">
       <c r="A131" s="1"/>
-      <c r="B131" s="2"/>
+      <c r="B131" s="7"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -3646,7 +3649,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18">
       <c r="A132" s="1"/>
-      <c r="B132" s="2"/>
+      <c r="B132" s="7"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -3669,7 +3672,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18">
       <c r="A133" s="1"/>
-      <c r="B133" s="2"/>
+      <c r="B133" s="7"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -3692,7 +3695,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18">
       <c r="A134" s="1"/>
-      <c r="B134" s="2"/>
+      <c r="B134" s="7"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -3715,7 +3718,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18">
       <c r="A135" s="1"/>
-      <c r="B135" s="2"/>
+      <c r="B135" s="7"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -3738,7 +3741,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18">
       <c r="A136" s="1"/>
-      <c r="B136" s="2"/>
+      <c r="B136" s="7"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -3761,7 +3764,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18">
       <c r="A137" s="1"/>
-      <c r="B137" s="2"/>
+      <c r="B137" s="7"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -3784,7 +3787,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18">
       <c r="A138" s="1"/>
-      <c r="B138" s="2"/>
+      <c r="B138" s="7"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -3807,7 +3810,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18">
       <c r="A139" s="1"/>
-      <c r="B139" s="2"/>
+      <c r="B139" s="7"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -3830,7 +3833,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18">
       <c r="A140" s="1"/>
-      <c r="B140" s="2"/>
+      <c r="B140" s="7"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -3853,7 +3856,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18">
       <c r="A141" s="1"/>
-      <c r="B141" s="2"/>
+      <c r="B141" s="7"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -3876,7 +3879,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18">
       <c r="A142" s="1"/>
-      <c r="B142" s="2"/>
+      <c r="B142" s="7"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -3899,7 +3902,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18">
       <c r="A143" s="1"/>
-      <c r="B143" s="2"/>
+      <c r="B143" s="7"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -3922,7 +3925,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18">
       <c r="A144" s="1"/>
-      <c r="B144" s="2"/>
+      <c r="B144" s="7"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -3945,7 +3948,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18">
       <c r="A145" s="1"/>
-      <c r="B145" s="2"/>
+      <c r="B145" s="7"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -3968,7 +3971,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18">
       <c r="A146" s="1"/>
-      <c r="B146" s="2"/>
+      <c r="B146" s="7"/>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -3991,7 +3994,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18">
       <c r="A147" s="1"/>
-      <c r="B147" s="2"/>
+      <c r="B147" s="7"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -4014,7 +4017,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18">
       <c r="A148" s="1"/>
-      <c r="B148" s="2"/>
+      <c r="B148" s="7"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -4037,7 +4040,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18">
       <c r="A149" s="1"/>
-      <c r="B149" s="2"/>
+      <c r="B149" s="7"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -4060,7 +4063,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18">
       <c r="A150" s="1"/>
-      <c r="B150" s="2"/>
+      <c r="B150" s="7"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -4083,7 +4086,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18">
       <c r="A151" s="1"/>
-      <c r="B151" s="2"/>
+      <c r="B151" s="7"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -4106,7 +4109,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18">
       <c r="A152" s="1"/>
-      <c r="B152" s="2"/>
+      <c r="B152" s="7"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -4129,7 +4132,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18">
       <c r="A153" s="1"/>
-      <c r="B153" s="2"/>
+      <c r="B153" s="7"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
@@ -4152,7 +4155,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18">
       <c r="A154" s="1"/>
-      <c r="B154" s="2"/>
+      <c r="B154" s="7"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
@@ -4175,7 +4178,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18">
       <c r="A155" s="1"/>
-      <c r="B155" s="2"/>
+      <c r="B155" s="7"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
@@ -4198,7 +4201,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18">
       <c r="A156" s="1"/>
-      <c r="B156" s="2"/>
+      <c r="B156" s="7"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
@@ -4221,7 +4224,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18">
       <c r="A157" s="1"/>
-      <c r="B157" s="2"/>
+      <c r="B157" s="7"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
@@ -4244,7 +4247,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18">
       <c r="A158" s="1"/>
-      <c r="B158" s="2"/>
+      <c r="B158" s="7"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
@@ -4267,7 +4270,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18">
       <c r="A159" s="1"/>
-      <c r="B159" s="2"/>
+      <c r="B159" s="7"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
@@ -4290,7 +4293,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18">
       <c r="A160" s="1"/>
-      <c r="B160" s="2"/>
+      <c r="B160" s="7"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -4313,7 +4316,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18">
       <c r="A161" s="1"/>
-      <c r="B161" s="2"/>
+      <c r="B161" s="7"/>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
@@ -4336,7 +4339,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18">
       <c r="A162" s="1"/>
-      <c r="B162" s="2"/>
+      <c r="B162" s="7"/>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
@@ -4359,7 +4362,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18">
       <c r="A163" s="1"/>
-      <c r="B163" s="2"/>
+      <c r="B163" s="7"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
@@ -4382,7 +4385,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18">
       <c r="A164" s="1"/>
-      <c r="B164" s="2"/>
+      <c r="B164" s="7"/>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
@@ -4405,7 +4408,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18">
       <c r="A165" s="1"/>
-      <c r="B165" s="2"/>
+      <c r="B165" s="7"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
@@ -4428,7 +4431,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18">
       <c r="A166" s="1"/>
-      <c r="B166" s="2"/>
+      <c r="B166" s="7"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
@@ -4451,7 +4454,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18">
       <c r="A167" s="1"/>
-      <c r="B167" s="2"/>
+      <c r="B167" s="7"/>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
@@ -4474,7 +4477,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18">
       <c r="A168" s="1"/>
-      <c r="B168" s="2"/>
+      <c r="B168" s="7"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -4497,7 +4500,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18">
       <c r="A169" s="1"/>
-      <c r="B169" s="2"/>
+      <c r="B169" s="7"/>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
@@ -4520,7 +4523,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18">
       <c r="A170" s="1"/>
-      <c r="B170" s="2"/>
+      <c r="B170" s="7"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
@@ -4543,7 +4546,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18">
       <c r="A171" s="1"/>
-      <c r="B171" s="2"/>
+      <c r="B171" s="7"/>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
@@ -4566,7 +4569,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18">
       <c r="A172" s="1"/>
-      <c r="B172" s="2"/>
+      <c r="B172" s="7"/>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
@@ -4589,7 +4592,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18">
       <c r="A173" s="1"/>
-      <c r="B173" s="2"/>
+      <c r="B173" s="7"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
@@ -4612,7 +4615,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18">
       <c r="A174" s="1"/>
-      <c r="B174" s="2"/>
+      <c r="B174" s="7"/>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
@@ -4635,7 +4638,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18">
       <c r="A175" s="1"/>
-      <c r="B175" s="2"/>
+      <c r="B175" s="7"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
@@ -4658,7 +4661,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18">
       <c r="A176" s="1"/>
-      <c r="B176" s="2"/>
+      <c r="B176" s="7"/>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
@@ -4681,7 +4684,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18">
       <c r="A177" s="1"/>
-      <c r="B177" s="2"/>
+      <c r="B177" s="7"/>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
@@ -4704,7 +4707,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18">
       <c r="A178" s="1"/>
-      <c r="B178" s="2"/>
+      <c r="B178" s="7"/>
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
@@ -4727,7 +4730,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18">
       <c r="A179" s="1"/>
-      <c r="B179" s="2"/>
+      <c r="B179" s="7"/>
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
@@ -4750,7 +4753,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18">
       <c r="A180" s="1"/>
-      <c r="B180" s="2"/>
+      <c r="B180" s="7"/>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
@@ -4773,7 +4776,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18">
       <c r="A181" s="1"/>
-      <c r="B181" s="2"/>
+      <c r="B181" s="7"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -4796,7 +4799,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18">
       <c r="A182" s="1"/>
-      <c r="B182" s="2"/>
+      <c r="B182" s="7"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -4819,7 +4822,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18">
       <c r="A183" s="1"/>
-      <c r="B183" s="2"/>
+      <c r="B183" s="7"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -4842,7 +4845,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18">
       <c r="A184" s="1"/>
-      <c r="B184" s="2"/>
+      <c r="B184" s="7"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -4865,7 +4868,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18">
       <c r="A185" s="1"/>
-      <c r="B185" s="2"/>
+      <c r="B185" s="7"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -4888,7 +4891,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18">
       <c r="A186" s="1"/>
-      <c r="B186" s="2"/>
+      <c r="B186" s="7"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -4911,7 +4914,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18">
       <c r="A187" s="1"/>
-      <c r="B187" s="2"/>
+      <c r="B187" s="7"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -4934,7 +4937,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18">
       <c r="A188" s="1"/>
-      <c r="B188" s="2"/>
+      <c r="B188" s="7"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -4957,7 +4960,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18">
       <c r="A189" s="1"/>
-      <c r="B189" s="2"/>
+      <c r="B189" s="7"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -4980,7 +4983,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18">
       <c r="A190" s="1"/>
-      <c r="B190" s="2"/>
+      <c r="B190" s="7"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -5003,7 +5006,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18">
       <c r="A191" s="1"/>
-      <c r="B191" s="2"/>
+      <c r="B191" s="7"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -5026,7 +5029,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18">
       <c r="A192" s="1"/>
-      <c r="B192" s="2"/>
+      <c r="B192" s="7"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -5049,7 +5052,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18">
       <c r="A193" s="1"/>
-      <c r="B193" s="2"/>
+      <c r="B193" s="7"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -5072,7 +5075,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18">
       <c r="A194" s="1"/>
-      <c r="B194" s="2"/>
+      <c r="B194" s="7"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -5095,7 +5098,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18">
       <c r="A195" s="1"/>
-      <c r="B195" s="2"/>
+      <c r="B195" s="7"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -5118,7 +5121,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18">
       <c r="A196" s="1"/>
-      <c r="B196" s="2"/>
+      <c r="B196" s="7"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -5141,7 +5144,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18">
       <c r="A197" s="1"/>
-      <c r="B197" s="2"/>
+      <c r="B197" s="7"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -5164,7 +5167,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18">
       <c r="A198" s="1"/>
-      <c r="B198" s="2"/>
+      <c r="B198" s="7"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -5187,7 +5190,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18">
       <c r="A199" s="1"/>
-      <c r="B199" s="2"/>
+      <c r="B199" s="7"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -5210,7 +5213,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18">
       <c r="A200" s="1"/>
-      <c r="B200" s="2"/>
+      <c r="B200" s="7"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -5233,7 +5236,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18">
       <c r="A201" s="1"/>
-      <c r="B201" s="2"/>
+      <c r="B201" s="7"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -5256,7 +5259,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18">
       <c r="A202" s="1"/>
-      <c r="B202" s="2"/>
+      <c r="B202" s="7"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -5279,7 +5282,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18">
       <c r="A203" s="1"/>
-      <c r="B203" s="2"/>
+      <c r="B203" s="7"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -5302,7 +5305,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18">
       <c r="A204" s="1"/>
-      <c r="B204" s="2"/>
+      <c r="B204" s="7"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -5325,7 +5328,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18">
       <c r="A205" s="1"/>
-      <c r="B205" s="2"/>
+      <c r="B205" s="7"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -5348,7 +5351,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18">
       <c r="A206" s="1"/>
-      <c r="B206" s="2"/>
+      <c r="B206" s="7"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -5371,7 +5374,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18">
       <c r="A207" s="1"/>
-      <c r="B207" s="2"/>
+      <c r="B207" s="7"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -5394,7 +5397,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18">
       <c r="A208" s="1"/>
-      <c r="B208" s="2"/>
+      <c r="B208" s="7"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -5417,7 +5420,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18">
       <c r="A209" s="1"/>
-      <c r="B209" s="2"/>
+      <c r="B209" s="7"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -5440,7 +5443,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="18">
       <c r="A210" s="1"/>
-      <c r="B210" s="2"/>
+      <c r="B210" s="7"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -5463,7 +5466,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="18">
       <c r="A211" s="1"/>
-      <c r="B211" s="2"/>
+      <c r="B211" s="7"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -5486,7 +5489,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="18">
       <c r="A212" s="1"/>
-      <c r="B212" s="2"/>
+      <c r="B212" s="7"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -5509,7 +5512,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18">
       <c r="A213" s="1"/>
-      <c r="B213" s="2"/>
+      <c r="B213" s="7"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -5532,7 +5535,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="18">
       <c r="A214" s="1"/>
-      <c r="B214" s="2"/>
+      <c r="B214" s="7"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -5555,7 +5558,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18">
       <c r="A215" s="1"/>
-      <c r="B215" s="2"/>
+      <c r="B215" s="7"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -5578,7 +5581,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="18">
       <c r="A216" s="1"/>
-      <c r="B216" s="2"/>
+      <c r="B216" s="7"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -5601,7 +5604,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="18">
       <c r="A217" s="1"/>
-      <c r="B217" s="2"/>
+      <c r="B217" s="7"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -5624,7 +5627,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18">
       <c r="A218" s="1"/>
-      <c r="B218" s="2"/>
+      <c r="B218" s="7"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -5647,7 +5650,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18">
       <c r="A219" s="1"/>
-      <c r="B219" s="2"/>
+      <c r="B219" s="7"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -5670,7 +5673,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="18">
       <c r="A220" s="1"/>
-      <c r="B220" s="2"/>
+      <c r="B220" s="7"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -5693,7 +5696,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18">
       <c r="A221" s="1"/>
-      <c r="B221" s="2"/>
+      <c r="B221" s="7"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -5716,7 +5719,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="18">
       <c r="A222" s="1"/>
-      <c r="B222" s="2"/>
+      <c r="B222" s="7"/>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -5739,7 +5742,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="18">
       <c r="A223" s="1"/>
-      <c r="B223" s="2"/>
+      <c r="B223" s="7"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -5762,7 +5765,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="18">
       <c r="A224" s="1"/>
-      <c r="B224" s="2"/>
+      <c r="B224" s="7"/>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -5785,7 +5788,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="18">
       <c r="A225" s="1"/>
-      <c r="B225" s="2"/>
+      <c r="B225" s="7"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -5808,7 +5811,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="18">
       <c r="A226" s="1"/>
-      <c r="B226" s="2"/>
+      <c r="B226" s="7"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -5831,7 +5834,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="18">
       <c r="A227" s="1"/>
-      <c r="B227" s="2"/>
+      <c r="B227" s="7"/>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -5854,7 +5857,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="18">
       <c r="A228" s="1"/>
-      <c r="B228" s="2"/>
+      <c r="B228" s="7"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -5877,7 +5880,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="18">
       <c r="A229" s="1"/>
-      <c r="B229" s="2"/>
+      <c r="B229" s="7"/>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -5900,7 +5903,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="18">
       <c r="A230" s="1"/>
-      <c r="B230" s="2"/>
+      <c r="B230" s="7"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -5923,7 +5926,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="18">
       <c r="A231" s="1"/>
-      <c r="B231" s="2"/>
+      <c r="B231" s="7"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -5946,7 +5949,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18">
       <c r="A232" s="1"/>
-      <c r="B232" s="2"/>
+      <c r="B232" s="7"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -5969,7 +5972,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="18">
       <c r="A233" s="1"/>
-      <c r="B233" s="2"/>
+      <c r="B233" s="7"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -5992,7 +5995,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18">
       <c r="A234" s="1"/>
-      <c r="B234" s="2"/>
+      <c r="B234" s="7"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -6015,7 +6018,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="18">
       <c r="A235" s="1"/>
-      <c r="B235" s="2"/>
+      <c r="B235" s="7"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -6038,7 +6041,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="18">
       <c r="A236" s="1"/>
-      <c r="B236" s="2"/>
+      <c r="B236" s="7"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -6061,7 +6064,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18">
       <c r="A237" s="1"/>
-      <c r="B237" s="2"/>
+      <c r="B237" s="7"/>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -6084,7 +6087,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18">
       <c r="A238" s="1"/>
-      <c r="B238" s="2"/>
+      <c r="B238" s="7"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -6107,7 +6110,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="18">
       <c r="A239" s="1"/>
-      <c r="B239" s="2"/>
+      <c r="B239" s="7"/>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -6130,7 +6133,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18">
       <c r="A240" s="1"/>
-      <c r="B240" s="2"/>
+      <c r="B240" s="7"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -6153,7 +6156,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="18">
       <c r="A241" s="1"/>
-      <c r="B241" s="2"/>
+      <c r="B241" s="7"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
@@ -6176,7 +6179,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="18">
       <c r="A242" s="1"/>
-      <c r="B242" s="2"/>
+      <c r="B242" s="7"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
@@ -6199,7 +6202,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18">
       <c r="A243" s="1"/>
-      <c r="B243" s="2"/>
+      <c r="B243" s="7"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
@@ -6222,7 +6225,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18">
       <c r="A244" s="1"/>
-      <c r="B244" s="2"/>
+      <c r="B244" s="7"/>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
@@ -6245,7 +6248,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="18">
       <c r="A245" s="1"/>
-      <c r="B245" s="2"/>
+      <c r="B245" s="7"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
@@ -6268,7 +6271,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="18">
       <c r="A246" s="1"/>
-      <c r="B246" s="2"/>
+      <c r="B246" s="7"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
@@ -6291,7 +6294,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="18">
       <c r="A247" s="1"/>
-      <c r="B247" s="2"/>
+      <c r="B247" s="7"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
@@ -6314,7 +6317,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18">
       <c r="A248" s="1"/>
-      <c r="B248" s="2"/>
+      <c r="B248" s="7"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
@@ -6337,7 +6340,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="18">
       <c r="A249" s="1"/>
-      <c r="B249" s="2"/>
+      <c r="B249" s="7"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
@@ -6360,7 +6363,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="18">
       <c r="A250" s="1"/>
-      <c r="B250" s="2"/>
+      <c r="B250" s="7"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
@@ -6383,7 +6386,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="18">
       <c r="A251" s="1"/>
-      <c r="B251" s="2"/>
+      <c r="B251" s="7"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
@@ -6406,7 +6409,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="18">
       <c r="A252" s="1"/>
-      <c r="B252" s="2"/>
+      <c r="B252" s="7"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
@@ -6429,7 +6432,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="18">
       <c r="A253" s="1"/>
-      <c r="B253" s="2"/>
+      <c r="B253" s="7"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
@@ -6452,7 +6455,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="18">
       <c r="A254" s="1"/>
-      <c r="B254" s="2"/>
+      <c r="B254" s="7"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
@@ -6475,7 +6478,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="18">
       <c r="A255" s="1"/>
-      <c r="B255" s="2"/>
+      <c r="B255" s="7"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
@@ -6498,7 +6501,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="18">
       <c r="A256" s="1"/>
-      <c r="B256" s="2"/>
+      <c r="B256" s="7"/>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
@@ -6521,7 +6524,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="18">
       <c r="A257" s="1"/>
-      <c r="B257" s="2"/>
+      <c r="B257" s="7"/>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
@@ -6544,7 +6547,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="18">
       <c r="A258" s="1"/>
-      <c r="B258" s="2"/>
+      <c r="B258" s="7"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
@@ -6567,7 +6570,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="18">
       <c r="A259" s="1"/>
-      <c r="B259" s="2"/>
+      <c r="B259" s="7"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
@@ -6590,7 +6593,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="18">
       <c r="A260" s="1"/>
-      <c r="B260" s="2"/>
+      <c r="B260" s="7"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
@@ -6613,7 +6616,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="18">
       <c r="A261" s="1"/>
-      <c r="B261" s="2"/>
+      <c r="B261" s="7"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
@@ -6636,7 +6639,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="18">
       <c r="A262" s="1"/>
-      <c r="B262" s="2"/>
+      <c r="B262" s="7"/>
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
@@ -6659,7 +6662,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="18">
       <c r="A263" s="1"/>
-      <c r="B263" s="2"/>
+      <c r="B263" s="7"/>
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
@@ -6682,7 +6685,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="18">
       <c r="A264" s="1"/>
-      <c r="B264" s="2"/>
+      <c r="B264" s="7"/>
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
@@ -6705,7 +6708,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="18">
       <c r="A265" s="1"/>
-      <c r="B265" s="2"/>
+      <c r="B265" s="7"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
@@ -6728,7 +6731,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="18">
       <c r="A266" s="1"/>
-      <c r="B266" s="2"/>
+      <c r="B266" s="7"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
@@ -6751,7 +6754,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="18">
       <c r="A267" s="1"/>
-      <c r="B267" s="2"/>
+      <c r="B267" s="7"/>
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
@@ -6774,7 +6777,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="18">
       <c r="A268" s="1"/>
-      <c r="B268" s="2"/>
+      <c r="B268" s="7"/>
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
@@ -6797,7 +6800,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="18">
       <c r="A269" s="1"/>
-      <c r="B269" s="2"/>
+      <c r="B269" s="7"/>
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
@@ -6820,7 +6823,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="18">
       <c r="A270" s="1"/>
-      <c r="B270" s="2"/>
+      <c r="B270" s="7"/>
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
@@ -6843,7 +6846,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="18">
       <c r="A271" s="1"/>
-      <c r="B271" s="2"/>
+      <c r="B271" s="7"/>
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
@@ -6866,7 +6869,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="18">
       <c r="A272" s="1"/>
-      <c r="B272" s="2"/>
+      <c r="B272" s="7"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
@@ -6889,7 +6892,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="18">
       <c r="A273" s="1"/>
-      <c r="B273" s="2"/>
+      <c r="B273" s="7"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
@@ -6912,7 +6915,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="18">
       <c r="A274" s="1"/>
-      <c r="B274" s="2"/>
+      <c r="B274" s="7"/>
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
@@ -6935,7 +6938,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="18">
       <c r="A275" s="1"/>
-      <c r="B275" s="2"/>
+      <c r="B275" s="7"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
@@ -6958,7 +6961,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="18">
       <c r="A276" s="1"/>
-      <c r="B276" s="2"/>
+      <c r="B276" s="7"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
@@ -6981,7 +6984,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="18">
       <c r="A277" s="1"/>
-      <c r="B277" s="2"/>
+      <c r="B277" s="7"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
@@ -7004,7 +7007,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="18">
       <c r="A278" s="1"/>
-      <c r="B278" s="2"/>
+      <c r="B278" s="7"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
@@ -7027,7 +7030,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="18">
       <c r="A279" s="1"/>
-      <c r="B279" s="2"/>
+      <c r="B279" s="7"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
@@ -7050,7 +7053,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="18">
       <c r="A280" s="1"/>
-      <c r="B280" s="2"/>
+      <c r="B280" s="7"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
@@ -7073,7 +7076,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="18">
       <c r="A281" s="1"/>
-      <c r="B281" s="2"/>
+      <c r="B281" s="7"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
@@ -7096,7 +7099,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="18">
       <c r="A282" s="1"/>
-      <c r="B282" s="2"/>
+      <c r="B282" s="7"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
@@ -7119,7 +7122,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="18">
       <c r="A283" s="1"/>
-      <c r="B283" s="2"/>
+      <c r="B283" s="7"/>
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
@@ -7142,7 +7145,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="18">
       <c r="A284" s="1"/>
-      <c r="B284" s="2"/>
+      <c r="B284" s="7"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
@@ -7165,7 +7168,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="18">
       <c r="A285" s="1"/>
-      <c r="B285" s="2"/>
+      <c r="B285" s="7"/>
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
@@ -7188,7 +7191,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="18">
       <c r="A286" s="1"/>
-      <c r="B286" s="2"/>
+      <c r="B286" s="7"/>
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
@@ -7211,7 +7214,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="18">
       <c r="A287" s="1"/>
-      <c r="B287" s="2"/>
+      <c r="B287" s="7"/>
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
@@ -7234,7 +7237,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="18">
       <c r="A288" s="1"/>
-      <c r="B288" s="2"/>
+      <c r="B288" s="7"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
@@ -7257,7 +7260,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="18">
       <c r="A289" s="1"/>
-      <c r="B289" s="2"/>
+      <c r="B289" s="7"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
@@ -7280,7 +7283,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="18">
       <c r="A290" s="1"/>
-      <c r="B290" s="2"/>
+      <c r="B290" s="7"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
@@ -7303,7 +7306,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="18">
       <c r="A291" s="1"/>
-      <c r="B291" s="2"/>
+      <c r="B291" s="7"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
@@ -7326,7 +7329,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="18">
       <c r="A292" s="1"/>
-      <c r="B292" s="2"/>
+      <c r="B292" s="7"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
@@ -7349,7 +7352,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="18">
       <c r="A293" s="1"/>
-      <c r="B293" s="2"/>
+      <c r="B293" s="7"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
@@ -7372,7 +7375,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="18">
       <c r="A294" s="1"/>
-      <c r="B294" s="2"/>
+      <c r="B294" s="7"/>
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
@@ -7395,7 +7398,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="18">
       <c r="A295" s="1"/>
-      <c r="B295" s="2"/>
+      <c r="B295" s="7"/>
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
@@ -7418,7 +7421,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="18">
       <c r="A296" s="1"/>
-      <c r="B296" s="2"/>
+      <c r="B296" s="7"/>
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
@@ -7441,7 +7444,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="18">
       <c r="A297" s="1"/>
-      <c r="B297" s="2"/>
+      <c r="B297" s="7"/>
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
@@ -7464,7 +7467,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="18">
       <c r="A298" s="1"/>
-      <c r="B298" s="2"/>
+      <c r="B298" s="7"/>
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
@@ -7487,7 +7490,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="18">
       <c r="A299" s="1"/>
-      <c r="B299" s="2"/>
+      <c r="B299" s="7"/>
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
@@ -7510,7 +7513,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="18">
       <c r="A300" s="1"/>
-      <c r="B300" s="2"/>
+      <c r="B300" s="7"/>
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
@@ -7533,7 +7536,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="18">
       <c r="A301" s="1"/>
-      <c r="B301" s="2"/>
+      <c r="B301" s="7"/>
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
@@ -7556,7 +7559,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="18">
       <c r="A302" s="1"/>
-      <c r="B302" s="2"/>
+      <c r="B302" s="7"/>
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
@@ -7579,7 +7582,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="18">
       <c r="A303" s="1"/>
-      <c r="B303" s="2"/>
+      <c r="B303" s="7"/>
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
@@ -7602,7 +7605,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="18">
       <c r="A304" s="1"/>
-      <c r="B304" s="2"/>
+      <c r="B304" s="7"/>
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
@@ -7625,7 +7628,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="18">
       <c r="A305" s="1"/>
-      <c r="B305" s="2"/>
+      <c r="B305" s="7"/>
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
@@ -7648,7 +7651,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="18">
       <c r="A306" s="1"/>
-      <c r="B306" s="2"/>
+      <c r="B306" s="7"/>
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
@@ -7671,7 +7674,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="18">
       <c r="A307" s="1"/>
-      <c r="B307" s="2"/>
+      <c r="B307" s="7"/>
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
@@ -7694,7 +7697,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="18">
       <c r="A308" s="1"/>
-      <c r="B308" s="2"/>
+      <c r="B308" s="7"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
@@ -7717,7 +7720,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="18">
       <c r="A309" s="1"/>
-      <c r="B309" s="2"/>
+      <c r="B309" s="7"/>
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
@@ -7740,7 +7743,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="18">
       <c r="A310" s="1"/>
-      <c r="B310" s="2"/>
+      <c r="B310" s="7"/>
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
@@ -7763,7 +7766,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="18">
       <c r="A311" s="1"/>
-      <c r="B311" s="2"/>
+      <c r="B311" s="7"/>
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
@@ -7786,7 +7789,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="18">
       <c r="A312" s="1"/>
-      <c r="B312" s="2"/>
+      <c r="B312" s="7"/>
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
@@ -7809,7 +7812,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="18">
       <c r="A313" s="1"/>
-      <c r="B313" s="2"/>
+      <c r="B313" s="7"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
@@ -7832,7 +7835,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="18">
       <c r="A314" s="1"/>
-      <c r="B314" s="2"/>
+      <c r="B314" s="7"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
@@ -7855,7 +7858,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="18">
       <c r="A315" s="1"/>
-      <c r="B315" s="2"/>
+      <c r="B315" s="7"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
@@ -7878,7 +7881,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="18">
       <c r="A316" s="1"/>
-      <c r="B316" s="2"/>
+      <c r="B316" s="7"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
@@ -7901,7 +7904,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="18">
       <c r="A317" s="1"/>
-      <c r="B317" s="2"/>
+      <c r="B317" s="7"/>
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
@@ -7924,7 +7927,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="18">
       <c r="A318" s="1"/>
-      <c r="B318" s="2"/>
+      <c r="B318" s="7"/>
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
@@ -7947,7 +7950,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="18">
       <c r="A319" s="1"/>
-      <c r="B319" s="2"/>
+      <c r="B319" s="7"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
@@ -7970,7 +7973,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="18">
       <c r="A320" s="1"/>
-      <c r="B320" s="2"/>
+      <c r="B320" s="7"/>
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
@@ -7993,7 +7996,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="18">
       <c r="A321" s="1"/>
-      <c r="B321" s="2"/>
+      <c r="B321" s="7"/>
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
@@ -8016,7 +8019,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="18">
       <c r="A322" s="1"/>
-      <c r="B322" s="2"/>
+      <c r="B322" s="7"/>
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
@@ -8039,7 +8042,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="18">
       <c r="A323" s="1"/>
-      <c r="B323" s="2"/>
+      <c r="B323" s="7"/>
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
@@ -8062,7 +8065,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="18">
       <c r="A324" s="1"/>
-      <c r="B324" s="2"/>
+      <c r="B324" s="7"/>
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
@@ -8085,7 +8088,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="18">
       <c r="A325" s="1"/>
-      <c r="B325" s="2"/>
+      <c r="B325" s="7"/>
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
@@ -8108,7 +8111,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="18">
       <c r="A326" s="1"/>
-      <c r="B326" s="2"/>
+      <c r="B326" s="7"/>
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
@@ -8131,7 +8134,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="18">
       <c r="A327" s="1"/>
-      <c r="B327" s="2"/>
+      <c r="B327" s="7"/>
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
@@ -8154,7 +8157,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="18">
       <c r="A328" s="1"/>
-      <c r="B328" s="2"/>
+      <c r="B328" s="7"/>
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
@@ -8177,7 +8180,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="18">
       <c r="A329" s="1"/>
-      <c r="B329" s="2"/>
+      <c r="B329" s="7"/>
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
@@ -8200,7 +8203,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="18">
       <c r="A330" s="1"/>
-      <c r="B330" s="2"/>
+      <c r="B330" s="7"/>
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
@@ -8223,7 +8226,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="18">
       <c r="A331" s="1"/>
-      <c r="B331" s="2"/>
+      <c r="B331" s="7"/>
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
@@ -8246,7 +8249,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="18">
       <c r="A332" s="1"/>
-      <c r="B332" s="2"/>
+      <c r="B332" s="7"/>
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
@@ -8269,7 +8272,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="18">
       <c r="A333" s="1"/>
-      <c r="B333" s="2"/>
+      <c r="B333" s="7"/>
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
@@ -8292,7 +8295,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="18">
       <c r="A334" s="1"/>
-      <c r="B334" s="2"/>
+      <c r="B334" s="7"/>
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
@@ -8315,7 +8318,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="18">
       <c r="A335" s="1"/>
-      <c r="B335" s="2"/>
+      <c r="B335" s="7"/>
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
@@ -8338,7 +8341,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="18">
       <c r="A336" s="1"/>
-      <c r="B336" s="2"/>
+      <c r="B336" s="7"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
@@ -8361,7 +8364,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="18">
       <c r="A337" s="1"/>
-      <c r="B337" s="2"/>
+      <c r="B337" s="7"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
@@ -8384,7 +8387,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="18">
       <c r="A338" s="1"/>
-      <c r="B338" s="2"/>
+      <c r="B338" s="7"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
@@ -8407,7 +8410,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="18">
       <c r="A339" s="1"/>
-      <c r="B339" s="2"/>
+      <c r="B339" s="7"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
@@ -8430,7 +8433,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="18">
       <c r="A340" s="1"/>
-      <c r="B340" s="2"/>
+      <c r="B340" s="7"/>
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
@@ -8453,7 +8456,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="18">
       <c r="A341" s="1"/>
-      <c r="B341" s="2"/>
+      <c r="B341" s="7"/>
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
@@ -8476,7 +8479,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="18">
       <c r="A342" s="1"/>
-      <c r="B342" s="2"/>
+      <c r="B342" s="7"/>
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
@@ -8499,7 +8502,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="18">
       <c r="A343" s="1"/>
-      <c r="B343" s="2"/>
+      <c r="B343" s="7"/>
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
@@ -8522,7 +8525,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="18">
       <c r="A344" s="1"/>
-      <c r="B344" s="2"/>
+      <c r="B344" s="7"/>
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
@@ -8545,7 +8548,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="18">
       <c r="A345" s="1"/>
-      <c r="B345" s="2"/>
+      <c r="B345" s="7"/>
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
@@ -8568,7 +8571,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="18">
       <c r="A346" s="1"/>
-      <c r="B346" s="2"/>
+      <c r="B346" s="7"/>
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
@@ -8591,7 +8594,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="18">
       <c r="A347" s="1"/>
-      <c r="B347" s="2"/>
+      <c r="B347" s="7"/>
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
@@ -8614,7 +8617,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="18">
       <c r="A348" s="1"/>
-      <c r="B348" s="2"/>
+      <c r="B348" s="7"/>
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
@@ -8637,7 +8640,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="18">
       <c r="A349" s="1"/>
-      <c r="B349" s="2"/>
+      <c r="B349" s="7"/>
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
@@ -8660,7 +8663,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="18">
       <c r="A350" s="1"/>
-      <c r="B350" s="2"/>
+      <c r="B350" s="7"/>
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
@@ -8683,7 +8686,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="18">
       <c r="A351" s="1"/>
-      <c r="B351" s="2"/>
+      <c r="B351" s="7"/>
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
@@ -8706,7 +8709,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="18">
       <c r="A352" s="1"/>
-      <c r="B352" s="2"/>
+      <c r="B352" s="7"/>
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
@@ -8729,7 +8732,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="18">
       <c r="A353" s="1"/>
-      <c r="B353" s="2"/>
+      <c r="B353" s="7"/>
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
@@ -8752,7 +8755,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="18">
       <c r="A354" s="1"/>
-      <c r="B354" s="2"/>
+      <c r="B354" s="7"/>
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
@@ -8775,7 +8778,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="18">
       <c r="A355" s="1"/>
-      <c r="B355" s="2"/>
+      <c r="B355" s="7"/>
       <c r="C355" s="1"/>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
@@ -8798,7 +8801,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="18">
       <c r="A356" s="1"/>
-      <c r="B356" s="2"/>
+      <c r="B356" s="7"/>
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
@@ -8821,7 +8824,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="18">
       <c r="A357" s="1"/>
-      <c r="B357" s="2"/>
+      <c r="B357" s="7"/>
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
@@ -8844,7 +8847,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="18">
       <c r="A358" s="1"/>
-      <c r="B358" s="2"/>
+      <c r="B358" s="7"/>
       <c r="C358" s="1"/>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
@@ -8867,7 +8870,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="18">
       <c r="A359" s="1"/>
-      <c r="B359" s="2"/>
+      <c r="B359" s="7"/>
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
@@ -8890,7 +8893,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="18">
       <c r="A360" s="1"/>
-      <c r="B360" s="2"/>
+      <c r="B360" s="7"/>
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
@@ -8913,7 +8916,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="18">
       <c r="A361" s="1"/>
-      <c r="B361" s="2"/>
+      <c r="B361" s="7"/>
       <c r="C361" s="1"/>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
@@ -8936,7 +8939,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="18">
       <c r="A362" s="1"/>
-      <c r="B362" s="2"/>
+      <c r="B362" s="7"/>
       <c r="C362" s="1"/>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
@@ -8959,7 +8962,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="18">
       <c r="A363" s="1"/>
-      <c r="B363" s="2"/>
+      <c r="B363" s="7"/>
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
@@ -8982,7 +8985,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="18">
       <c r="A364" s="1"/>
-      <c r="B364" s="2"/>
+      <c r="B364" s="7"/>
       <c r="C364" s="1"/>
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
@@ -9005,7 +9008,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="18">
       <c r="A365" s="1"/>
-      <c r="B365" s="2"/>
+      <c r="B365" s="7"/>
       <c r="C365" s="1"/>
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
@@ -9028,7 +9031,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="18">
       <c r="A366" s="1"/>
-      <c r="B366" s="2"/>
+      <c r="B366" s="7"/>
       <c r="C366" s="1"/>
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
@@ -9051,7 +9054,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="18">
       <c r="A367" s="1"/>
-      <c r="B367" s="2"/>
+      <c r="B367" s="7"/>
       <c r="C367" s="1"/>
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
@@ -9074,7 +9077,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="18">
       <c r="A368" s="1"/>
-      <c r="B368" s="2"/>
+      <c r="B368" s="7"/>
       <c r="C368" s="1"/>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
@@ -9097,7 +9100,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="18">
       <c r="A369" s="1"/>
-      <c r="B369" s="2"/>
+      <c r="B369" s="7"/>
       <c r="C369" s="1"/>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
@@ -9120,7 +9123,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="18">
       <c r="A370" s="1"/>
-      <c r="B370" s="2"/>
+      <c r="B370" s="7"/>
       <c r="C370" s="1"/>
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
@@ -9143,7 +9146,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="18">
       <c r="A371" s="1"/>
-      <c r="B371" s="2"/>
+      <c r="B371" s="7"/>
       <c r="C371" s="1"/>
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
@@ -9166,7 +9169,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="18">
       <c r="A372" s="1"/>
-      <c r="B372" s="2"/>
+      <c r="B372" s="7"/>
       <c r="C372" s="1"/>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
@@ -9189,7 +9192,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="18">
       <c r="A373" s="1"/>
-      <c r="B373" s="2"/>
+      <c r="B373" s="7"/>
       <c r="C373" s="1"/>
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
@@ -9212,7 +9215,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="18">
       <c r="A374" s="1"/>
-      <c r="B374" s="2"/>
+      <c r="B374" s="7"/>
       <c r="C374" s="1"/>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
@@ -9235,7 +9238,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="18">
       <c r="A375" s="1"/>
-      <c r="B375" s="2"/>
+      <c r="B375" s="7"/>
       <c r="C375" s="1"/>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
@@ -9258,7 +9261,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="18">
       <c r="A376" s="1"/>
-      <c r="B376" s="2"/>
+      <c r="B376" s="7"/>
       <c r="C376" s="1"/>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
@@ -9281,7 +9284,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="18">
       <c r="A377" s="1"/>
-      <c r="B377" s="2"/>
+      <c r="B377" s="7"/>
       <c r="C377" s="1"/>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
@@ -9304,7 +9307,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="18">
       <c r="A378" s="1"/>
-      <c r="B378" s="2"/>
+      <c r="B378" s="7"/>
       <c r="C378" s="1"/>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
@@ -9327,7 +9330,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="18">
       <c r="A379" s="1"/>
-      <c r="B379" s="2"/>
+      <c r="B379" s="7"/>
       <c r="C379" s="1"/>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
@@ -9350,7 +9353,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="18">
       <c r="A380" s="1"/>
-      <c r="B380" s="2"/>
+      <c r="B380" s="7"/>
       <c r="C380" s="1"/>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
@@ -9373,7 +9376,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="18">
       <c r="A381" s="1"/>
-      <c r="B381" s="2"/>
+      <c r="B381" s="7"/>
       <c r="C381" s="1"/>
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
@@ -9396,7 +9399,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="18">
       <c r="A382" s="1"/>
-      <c r="B382" s="2"/>
+      <c r="B382" s="7"/>
       <c r="C382" s="1"/>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
@@ -9419,7 +9422,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="18">
       <c r="A383" s="1"/>
-      <c r="B383" s="2"/>
+      <c r="B383" s="7"/>
       <c r="C383" s="1"/>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
@@ -9442,7 +9445,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="18">
       <c r="A384" s="1"/>
-      <c r="B384" s="2"/>
+      <c r="B384" s="7"/>
       <c r="C384" s="1"/>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
@@ -9465,7 +9468,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="18">
       <c r="A385" s="1"/>
-      <c r="B385" s="2"/>
+      <c r="B385" s="7"/>
       <c r="C385" s="1"/>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
@@ -9488,7 +9491,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="18">
       <c r="A386" s="1"/>
-      <c r="B386" s="2"/>
+      <c r="B386" s="7"/>
       <c r="C386" s="1"/>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
@@ -9511,7 +9514,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="18">
       <c r="A387" s="1"/>
-      <c r="B387" s="2"/>
+      <c r="B387" s="7"/>
       <c r="C387" s="1"/>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
@@ -9534,7 +9537,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="18">
       <c r="A388" s="1"/>
-      <c r="B388" s="2"/>
+      <c r="B388" s="7"/>
       <c r="C388" s="1"/>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
@@ -9557,7 +9560,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="18">
       <c r="A389" s="1"/>
-      <c r="B389" s="2"/>
+      <c r="B389" s="7"/>
       <c r="C389" s="1"/>
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
@@ -9580,7 +9583,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="18">
       <c r="A390" s="1"/>
-      <c r="B390" s="2"/>
+      <c r="B390" s="7"/>
       <c r="C390" s="1"/>
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
@@ -9603,7 +9606,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="18">
       <c r="A391" s="1"/>
-      <c r="B391" s="2"/>
+      <c r="B391" s="7"/>
       <c r="C391" s="1"/>
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
@@ -9626,7 +9629,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="18">
       <c r="A392" s="1"/>
-      <c r="B392" s="2"/>
+      <c r="B392" s="7"/>
       <c r="C392" s="1"/>
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
@@ -9649,7 +9652,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="18">
       <c r="A393" s="1"/>
-      <c r="B393" s="2"/>
+      <c r="B393" s="7"/>
       <c r="C393" s="1"/>
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
@@ -9672,7 +9675,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="18">
       <c r="A394" s="1"/>
-      <c r="B394" s="2"/>
+      <c r="B394" s="7"/>
       <c r="C394" s="1"/>
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
@@ -9695,7 +9698,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="18">
       <c r="A395" s="1"/>
-      <c r="B395" s="2"/>
+      <c r="B395" s="7"/>
       <c r="C395" s="1"/>
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
@@ -9718,7 +9721,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="18">
       <c r="A396" s="1"/>
-      <c r="B396" s="2"/>
+      <c r="B396" s="7"/>
       <c r="C396" s="1"/>
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
@@ -9741,7 +9744,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="18">
       <c r="A397" s="1"/>
-      <c r="B397" s="2"/>
+      <c r="B397" s="7"/>
       <c r="C397" s="1"/>
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
@@ -9764,7 +9767,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="18">
       <c r="A398" s="1"/>
-      <c r="B398" s="2"/>
+      <c r="B398" s="7"/>
       <c r="C398" s="1"/>
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
@@ -9787,7 +9790,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="18">
       <c r="A399" s="1"/>
-      <c r="B399" s="2"/>
+      <c r="B399" s="7"/>
       <c r="C399" s="1"/>
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
@@ -9810,7 +9813,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="18">
       <c r="A400" s="1"/>
-      <c r="B400" s="2"/>
+      <c r="B400" s="7"/>
       <c r="C400" s="1"/>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
@@ -9833,7 +9836,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="18">
       <c r="A401" s="1"/>
-      <c r="B401" s="2"/>
+      <c r="B401" s="7"/>
       <c r="C401" s="1"/>
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
@@ -9856,7 +9859,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="18">
       <c r="A402" s="1"/>
-      <c r="B402" s="2"/>
+      <c r="B402" s="7"/>
       <c r="C402" s="1"/>
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
@@ -9879,7 +9882,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="18">
       <c r="A403" s="1"/>
-      <c r="B403" s="2"/>
+      <c r="B403" s="7"/>
       <c r="C403" s="1"/>
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
@@ -9902,7 +9905,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="18">
       <c r="A404" s="1"/>
-      <c r="B404" s="2"/>
+      <c r="B404" s="7"/>
       <c r="C404" s="1"/>
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
@@ -9925,7 +9928,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="18">
       <c r="A405" s="1"/>
-      <c r="B405" s="2"/>
+      <c r="B405" s="7"/>
       <c r="C405" s="1"/>
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
@@ -9948,7 +9951,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="18">
       <c r="A406" s="1"/>
-      <c r="B406" s="2"/>
+      <c r="B406" s="7"/>
       <c r="C406" s="1"/>
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
@@ -9971,7 +9974,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="18">
       <c r="A407" s="1"/>
-      <c r="B407" s="2"/>
+      <c r="B407" s="7"/>
       <c r="C407" s="1"/>
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
@@ -9994,7 +9997,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="18">
       <c r="A408" s="1"/>
-      <c r="B408" s="2"/>
+      <c r="B408" s="7"/>
       <c r="C408" s="1"/>
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
@@ -10017,7 +10020,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="18">
       <c r="A409" s="1"/>
-      <c r="B409" s="2"/>
+      <c r="B409" s="7"/>
       <c r="C409" s="1"/>
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
@@ -10040,7 +10043,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="18">
       <c r="A410" s="1"/>
-      <c r="B410" s="2"/>
+      <c r="B410" s="7"/>
       <c r="C410" s="1"/>
       <c r="D410" s="1"/>
       <c r="E410" s="1"/>
@@ -10063,7 +10066,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="18">
       <c r="A411" s="1"/>
-      <c r="B411" s="2"/>
+      <c r="B411" s="7"/>
       <c r="C411" s="1"/>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
@@ -10086,7 +10089,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="412" customHeight="1" ht="18">
       <c r="A412" s="1"/>
-      <c r="B412" s="2"/>
+      <c r="B412" s="7"/>
       <c r="C412" s="1"/>
       <c r="D412" s="1"/>
       <c r="E412" s="1"/>
@@ -10109,7 +10112,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="413" customHeight="1" ht="18">
       <c r="A413" s="1"/>
-      <c r="B413" s="2"/>
+      <c r="B413" s="7"/>
       <c r="C413" s="1"/>
       <c r="D413" s="1"/>
       <c r="E413" s="1"/>
@@ -10132,7 +10135,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="414" customHeight="1" ht="18">
       <c r="A414" s="1"/>
-      <c r="B414" s="2"/>
+      <c r="B414" s="7"/>
       <c r="C414" s="1"/>
       <c r="D414" s="1"/>
       <c r="E414" s="1"/>
@@ -10155,7 +10158,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="415" customHeight="1" ht="18">
       <c r="A415" s="1"/>
-      <c r="B415" s="2"/>
+      <c r="B415" s="7"/>
       <c r="C415" s="1"/>
       <c r="D415" s="1"/>
       <c r="E415" s="1"/>
@@ -10178,7 +10181,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="416" customHeight="1" ht="18">
       <c r="A416" s="1"/>
-      <c r="B416" s="2"/>
+      <c r="B416" s="7"/>
       <c r="C416" s="1"/>
       <c r="D416" s="1"/>
       <c r="E416" s="1"/>
@@ -10201,7 +10204,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="417" customHeight="1" ht="18">
       <c r="A417" s="1"/>
-      <c r="B417" s="2"/>
+      <c r="B417" s="7"/>
       <c r="C417" s="1"/>
       <c r="D417" s="1"/>
       <c r="E417" s="1"/>
@@ -10224,7 +10227,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="418" customHeight="1" ht="18">
       <c r="A418" s="1"/>
-      <c r="B418" s="2"/>
+      <c r="B418" s="7"/>
       <c r="C418" s="1"/>
       <c r="D418" s="1"/>
       <c r="E418" s="1"/>
@@ -10247,7 +10250,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="419" customHeight="1" ht="18">
       <c r="A419" s="1"/>
-      <c r="B419" s="2"/>
+      <c r="B419" s="7"/>
       <c r="C419" s="1"/>
       <c r="D419" s="1"/>
       <c r="E419" s="1"/>
@@ -10270,7 +10273,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="420" customHeight="1" ht="18">
       <c r="A420" s="1"/>
-      <c r="B420" s="2"/>
+      <c r="B420" s="7"/>
       <c r="C420" s="1"/>
       <c r="D420" s="1"/>
       <c r="E420" s="1"/>
@@ -10293,7 +10296,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="421" customHeight="1" ht="18">
       <c r="A421" s="1"/>
-      <c r="B421" s="2"/>
+      <c r="B421" s="7"/>
       <c r="C421" s="1"/>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
@@ -10316,7 +10319,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="422" customHeight="1" ht="18">
       <c r="A422" s="1"/>
-      <c r="B422" s="2"/>
+      <c r="B422" s="7"/>
       <c r="C422" s="1"/>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
@@ -10339,7 +10342,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="423" customHeight="1" ht="18">
       <c r="A423" s="1"/>
-      <c r="B423" s="2"/>
+      <c r="B423" s="7"/>
       <c r="C423" s="1"/>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
@@ -10362,7 +10365,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="424" customHeight="1" ht="18">
       <c r="A424" s="1"/>
-      <c r="B424" s="2"/>
+      <c r="B424" s="7"/>
       <c r="C424" s="1"/>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
@@ -10385,7 +10388,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="425" customHeight="1" ht="18">
       <c r="A425" s="1"/>
-      <c r="B425" s="2"/>
+      <c r="B425" s="7"/>
       <c r="C425" s="1"/>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
@@ -10408,7 +10411,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="426" customHeight="1" ht="18">
       <c r="A426" s="1"/>
-      <c r="B426" s="2"/>
+      <c r="B426" s="7"/>
       <c r="C426" s="1"/>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
@@ -10431,7 +10434,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="427" customHeight="1" ht="18">
       <c r="A427" s="1"/>
-      <c r="B427" s="2"/>
+      <c r="B427" s="7"/>
       <c r="C427" s="1"/>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
@@ -10454,7 +10457,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="428" customHeight="1" ht="18">
       <c r="A428" s="1"/>
-      <c r="B428" s="2"/>
+      <c r="B428" s="7"/>
       <c r="C428" s="1"/>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
@@ -10477,7 +10480,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="429" customHeight="1" ht="18">
       <c r="A429" s="1"/>
-      <c r="B429" s="2"/>
+      <c r="B429" s="7"/>
       <c r="C429" s="1"/>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
@@ -10500,7 +10503,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="430" customHeight="1" ht="18">
       <c r="A430" s="1"/>
-      <c r="B430" s="2"/>
+      <c r="B430" s="7"/>
       <c r="C430" s="1"/>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
@@ -10523,7 +10526,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="431" customHeight="1" ht="18">
       <c r="A431" s="1"/>
-      <c r="B431" s="2"/>
+      <c r="B431" s="7"/>
       <c r="C431" s="1"/>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
@@ -10546,7 +10549,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="432" customHeight="1" ht="18">
       <c r="A432" s="1"/>
-      <c r="B432" s="2"/>
+      <c r="B432" s="7"/>
       <c r="C432" s="1"/>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
@@ -10569,7 +10572,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="433" customHeight="1" ht="18">
       <c r="A433" s="1"/>
-      <c r="B433" s="2"/>
+      <c r="B433" s="7"/>
       <c r="C433" s="1"/>
       <c r="D433" s="1"/>
       <c r="E433" s="1"/>
@@ -10592,7 +10595,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="434" customHeight="1" ht="18">
       <c r="A434" s="1"/>
-      <c r="B434" s="2"/>
+      <c r="B434" s="7"/>
       <c r="C434" s="1"/>
       <c r="D434" s="1"/>
       <c r="E434" s="1"/>
@@ -10615,7 +10618,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="435" customHeight="1" ht="18">
       <c r="A435" s="1"/>
-      <c r="B435" s="2"/>
+      <c r="B435" s="7"/>
       <c r="C435" s="1"/>
       <c r="D435" s="1"/>
       <c r="E435" s="1"/>
@@ -10638,7 +10641,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="436" customHeight="1" ht="18">
       <c r="A436" s="1"/>
-      <c r="B436" s="2"/>
+      <c r="B436" s="7"/>
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
       <c r="E436" s="1"/>
@@ -10661,7 +10664,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="437" customHeight="1" ht="18">
       <c r="A437" s="1"/>
-      <c r="B437" s="2"/>
+      <c r="B437" s="7"/>
       <c r="C437" s="1"/>
       <c r="D437" s="1"/>
       <c r="E437" s="1"/>
@@ -10684,7 +10687,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="438" customHeight="1" ht="18">
       <c r="A438" s="1"/>
-      <c r="B438" s="2"/>
+      <c r="B438" s="7"/>
       <c r="C438" s="1"/>
       <c r="D438" s="1"/>
       <c r="E438" s="1"/>
@@ -10707,7 +10710,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="439" customHeight="1" ht="18">
       <c r="A439" s="1"/>
-      <c r="B439" s="2"/>
+      <c r="B439" s="7"/>
       <c r="C439" s="1"/>
       <c r="D439" s="1"/>
       <c r="E439" s="1"/>
@@ -10730,7 +10733,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="440" customHeight="1" ht="18">
       <c r="A440" s="1"/>
-      <c r="B440" s="2"/>
+      <c r="B440" s="7"/>
       <c r="C440" s="1"/>
       <c r="D440" s="1"/>
       <c r="E440" s="1"/>
@@ -10753,7 +10756,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="441" customHeight="1" ht="18">
       <c r="A441" s="1"/>
-      <c r="B441" s="2"/>
+      <c r="B441" s="7"/>
       <c r="C441" s="1"/>
       <c r="D441" s="1"/>
       <c r="E441" s="1"/>
@@ -10776,7 +10779,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="442" customHeight="1" ht="18">
       <c r="A442" s="1"/>
-      <c r="B442" s="2"/>
+      <c r="B442" s="7"/>
       <c r="C442" s="1"/>
       <c r="D442" s="1"/>
       <c r="E442" s="1"/>
@@ -10799,7 +10802,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="443" customHeight="1" ht="18">
       <c r="A443" s="1"/>
-      <c r="B443" s="2"/>
+      <c r="B443" s="7"/>
       <c r="C443" s="1"/>
       <c r="D443" s="1"/>
       <c r="E443" s="1"/>
@@ -10822,7 +10825,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="444" customHeight="1" ht="18">
       <c r="A444" s="1"/>
-      <c r="B444" s="2"/>
+      <c r="B444" s="7"/>
       <c r="C444" s="1"/>
       <c r="D444" s="1"/>
       <c r="E444" s="1"/>
@@ -10845,7 +10848,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="445" customHeight="1" ht="18">
       <c r="A445" s="1"/>
-      <c r="B445" s="2"/>
+      <c r="B445" s="7"/>
       <c r="C445" s="1"/>
       <c r="D445" s="1"/>
       <c r="E445" s="1"/>
@@ -10868,7 +10871,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="446" customHeight="1" ht="18">
       <c r="A446" s="1"/>
-      <c r="B446" s="2"/>
+      <c r="B446" s="7"/>
       <c r="C446" s="1"/>
       <c r="D446" s="1"/>
       <c r="E446" s="1"/>
@@ -10891,7 +10894,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="447" customHeight="1" ht="18">
       <c r="A447" s="1"/>
-      <c r="B447" s="2"/>
+      <c r="B447" s="7"/>
       <c r="C447" s="1"/>
       <c r="D447" s="1"/>
       <c r="E447" s="1"/>
@@ -10914,7 +10917,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="448" customHeight="1" ht="18">
       <c r="A448" s="1"/>
-      <c r="B448" s="2"/>
+      <c r="B448" s="7"/>
       <c r="C448" s="1"/>
       <c r="D448" s="1"/>
       <c r="E448" s="1"/>
@@ -10937,7 +10940,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="449" customHeight="1" ht="18">
       <c r="A449" s="1"/>
-      <c r="B449" s="2"/>
+      <c r="B449" s="7"/>
       <c r="C449" s="1"/>
       <c r="D449" s="1"/>
       <c r="E449" s="1"/>
@@ -10960,7 +10963,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="450" customHeight="1" ht="18">
       <c r="A450" s="1"/>
-      <c r="B450" s="2"/>
+      <c r="B450" s="7"/>
       <c r="C450" s="1"/>
       <c r="D450" s="1"/>
       <c r="E450" s="1"/>
@@ -10983,7 +10986,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="451" customHeight="1" ht="18">
       <c r="A451" s="1"/>
-      <c r="B451" s="2"/>
+      <c r="B451" s="7"/>
       <c r="C451" s="1"/>
       <c r="D451" s="1"/>
       <c r="E451" s="1"/>
@@ -11006,7 +11009,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="452" customHeight="1" ht="18">
       <c r="A452" s="1"/>
-      <c r="B452" s="2"/>
+      <c r="B452" s="7"/>
       <c r="C452" s="1"/>
       <c r="D452" s="1"/>
       <c r="E452" s="1"/>
@@ -11029,7 +11032,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="453" customHeight="1" ht="18">
       <c r="A453" s="1"/>
-      <c r="B453" s="2"/>
+      <c r="B453" s="7"/>
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
       <c r="E453" s="1"/>
@@ -11052,7 +11055,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="454" customHeight="1" ht="18">
       <c r="A454" s="1"/>
-      <c r="B454" s="2"/>
+      <c r="B454" s="7"/>
       <c r="C454" s="1"/>
       <c r="D454" s="1"/>
       <c r="E454" s="1"/>
@@ -11075,7 +11078,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="455" customHeight="1" ht="18">
       <c r="A455" s="1"/>
-      <c r="B455" s="2"/>
+      <c r="B455" s="7"/>
       <c r="C455" s="1"/>
       <c r="D455" s="1"/>
       <c r="E455" s="1"/>
@@ -11098,7 +11101,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="456" customHeight="1" ht="18">
       <c r="A456" s="1"/>
-      <c r="B456" s="2"/>
+      <c r="B456" s="7"/>
       <c r="C456" s="1"/>
       <c r="D456" s="1"/>
       <c r="E456" s="1"/>
@@ -11121,7 +11124,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="457" customHeight="1" ht="18">
       <c r="A457" s="1"/>
-      <c r="B457" s="2"/>
+      <c r="B457" s="7"/>
       <c r="C457" s="1"/>
       <c r="D457" s="1"/>
       <c r="E457" s="1"/>
@@ -11144,7 +11147,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="458" customHeight="1" ht="18">
       <c r="A458" s="1"/>
-      <c r="B458" s="2"/>
+      <c r="B458" s="7"/>
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
       <c r="E458" s="1"/>
@@ -11167,7 +11170,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="459" customHeight="1" ht="18">
       <c r="A459" s="1"/>
-      <c r="B459" s="2"/>
+      <c r="B459" s="7"/>
       <c r="C459" s="1"/>
       <c r="D459" s="1"/>
       <c r="E459" s="1"/>
@@ -11190,7 +11193,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="460" customHeight="1" ht="18">
       <c r="A460" s="1"/>
-      <c r="B460" s="2"/>
+      <c r="B460" s="7"/>
       <c r="C460" s="1"/>
       <c r="D460" s="1"/>
       <c r="E460" s="1"/>
@@ -11213,7 +11216,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="461" customHeight="1" ht="18">
       <c r="A461" s="1"/>
-      <c r="B461" s="2"/>
+      <c r="B461" s="7"/>
       <c r="C461" s="1"/>
       <c r="D461" s="1"/>
       <c r="E461" s="1"/>
@@ -11236,7 +11239,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="462" customHeight="1" ht="18">
       <c r="A462" s="1"/>
-      <c r="B462" s="2"/>
+      <c r="B462" s="7"/>
       <c r="C462" s="1"/>
       <c r="D462" s="1"/>
       <c r="E462" s="1"/>
@@ -11259,7 +11262,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="463" customHeight="1" ht="18">
       <c r="A463" s="1"/>
-      <c r="B463" s="2"/>
+      <c r="B463" s="7"/>
       <c r="C463" s="1"/>
       <c r="D463" s="1"/>
       <c r="E463" s="1"/>
@@ -11282,7 +11285,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="464" customHeight="1" ht="18">
       <c r="A464" s="1"/>
-      <c r="B464" s="2"/>
+      <c r="B464" s="7"/>
       <c r="C464" s="1"/>
       <c r="D464" s="1"/>
       <c r="E464" s="1"/>
@@ -11305,7 +11308,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="465" customHeight="1" ht="18">
       <c r="A465" s="1"/>
-      <c r="B465" s="2"/>
+      <c r="B465" s="7"/>
       <c r="C465" s="1"/>
       <c r="D465" s="1"/>
       <c r="E465" s="1"/>
@@ -11328,7 +11331,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="466" customHeight="1" ht="18">
       <c r="A466" s="1"/>
-      <c r="B466" s="2"/>
+      <c r="B466" s="7"/>
       <c r="C466" s="1"/>
       <c r="D466" s="1"/>
       <c r="E466" s="1"/>
@@ -11351,7 +11354,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="467" customHeight="1" ht="18">
       <c r="A467" s="1"/>
-      <c r="B467" s="2"/>
+      <c r="B467" s="7"/>
       <c r="C467" s="1"/>
       <c r="D467" s="1"/>
       <c r="E467" s="1"/>
@@ -11374,7 +11377,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="468" customHeight="1" ht="18">
       <c r="A468" s="1"/>
-      <c r="B468" s="2"/>
+      <c r="B468" s="7"/>
       <c r="C468" s="1"/>
       <c r="D468" s="1"/>
       <c r="E468" s="1"/>
@@ -11397,7 +11400,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="469" customHeight="1" ht="18">
       <c r="A469" s="1"/>
-      <c r="B469" s="2"/>
+      <c r="B469" s="7"/>
       <c r="C469" s="1"/>
       <c r="D469" s="1"/>
       <c r="E469" s="1"/>
@@ -11420,7 +11423,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="470" customHeight="1" ht="18">
       <c r="A470" s="1"/>
-      <c r="B470" s="2"/>
+      <c r="B470" s="7"/>
       <c r="C470" s="1"/>
       <c r="D470" s="1"/>
       <c r="E470" s="1"/>
@@ -11443,7 +11446,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="471" customHeight="1" ht="18">
       <c r="A471" s="1"/>
-      <c r="B471" s="2"/>
+      <c r="B471" s="7"/>
       <c r="C471" s="1"/>
       <c r="D471" s="1"/>
       <c r="E471" s="1"/>
@@ -11466,7 +11469,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="472" customHeight="1" ht="18">
       <c r="A472" s="1"/>
-      <c r="B472" s="2"/>
+      <c r="B472" s="7"/>
       <c r="C472" s="1"/>
       <c r="D472" s="1"/>
       <c r="E472" s="1"/>
@@ -11489,7 +11492,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="473" customHeight="1" ht="18">
       <c r="A473" s="1"/>
-      <c r="B473" s="2"/>
+      <c r="B473" s="7"/>
       <c r="C473" s="1"/>
       <c r="D473" s="1"/>
       <c r="E473" s="1"/>
@@ -11512,7 +11515,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="474" customHeight="1" ht="18">
       <c r="A474" s="1"/>
-      <c r="B474" s="2"/>
+      <c r="B474" s="7"/>
       <c r="C474" s="1"/>
       <c r="D474" s="1"/>
       <c r="E474" s="1"/>
@@ -11535,7 +11538,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="475" customHeight="1" ht="18">
       <c r="A475" s="1"/>
-      <c r="B475" s="2"/>
+      <c r="B475" s="7"/>
       <c r="C475" s="1"/>
       <c r="D475" s="1"/>
       <c r="E475" s="1"/>
@@ -11558,7 +11561,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="476" customHeight="1" ht="18">
       <c r="A476" s="1"/>
-      <c r="B476" s="2"/>
+      <c r="B476" s="7"/>
       <c r="C476" s="1"/>
       <c r="D476" s="1"/>
       <c r="E476" s="1"/>
@@ -11581,7 +11584,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="477" customHeight="1" ht="18">
       <c r="A477" s="1"/>
-      <c r="B477" s="2"/>
+      <c r="B477" s="7"/>
       <c r="C477" s="1"/>
       <c r="D477" s="1"/>
       <c r="E477" s="1"/>
@@ -11604,7 +11607,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="478" customHeight="1" ht="18">
       <c r="A478" s="1"/>
-      <c r="B478" s="2"/>
+      <c r="B478" s="7"/>
       <c r="C478" s="1"/>
       <c r="D478" s="1"/>
       <c r="E478" s="1"/>
@@ -11627,7 +11630,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="479" customHeight="1" ht="18">
       <c r="A479" s="1"/>
-      <c r="B479" s="2"/>
+      <c r="B479" s="7"/>
       <c r="C479" s="1"/>
       <c r="D479" s="1"/>
       <c r="E479" s="1"/>
@@ -11650,7 +11653,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="480" customHeight="1" ht="18">
       <c r="A480" s="1"/>
-      <c r="B480" s="2"/>
+      <c r="B480" s="7"/>
       <c r="C480" s="1"/>
       <c r="D480" s="1"/>
       <c r="E480" s="1"/>
@@ -11673,7 +11676,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="481" customHeight="1" ht="18">
       <c r="A481" s="1"/>
-      <c r="B481" s="2"/>
+      <c r="B481" s="7"/>
       <c r="C481" s="1"/>
       <c r="D481" s="1"/>
       <c r="E481" s="1"/>
@@ -11696,7 +11699,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="482" customHeight="1" ht="18">
       <c r="A482" s="1"/>
-      <c r="B482" s="2"/>
+      <c r="B482" s="7"/>
       <c r="C482" s="1"/>
       <c r="D482" s="1"/>
       <c r="E482" s="1"/>
@@ -11719,7 +11722,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="483" customHeight="1" ht="18">
       <c r="A483" s="1"/>
-      <c r="B483" s="2"/>
+      <c r="B483" s="7"/>
       <c r="C483" s="1"/>
       <c r="D483" s="1"/>
       <c r="E483" s="1"/>
@@ -11742,7 +11745,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="484" customHeight="1" ht="18">
       <c r="A484" s="1"/>
-      <c r="B484" s="2"/>
+      <c r="B484" s="7"/>
       <c r="C484" s="1"/>
       <c r="D484" s="1"/>
       <c r="E484" s="1"/>
@@ -11765,7 +11768,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="485" customHeight="1" ht="18">
       <c r="A485" s="1"/>
-      <c r="B485" s="2"/>
+      <c r="B485" s="7"/>
       <c r="C485" s="1"/>
       <c r="D485" s="1"/>
       <c r="E485" s="1"/>
@@ -11788,7 +11791,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="486" customHeight="1" ht="18">
       <c r="A486" s="1"/>
-      <c r="B486" s="2"/>
+      <c r="B486" s="7"/>
       <c r="C486" s="1"/>
       <c r="D486" s="1"/>
       <c r="E486" s="1"/>
@@ -11811,7 +11814,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="487" customHeight="1" ht="18">
       <c r="A487" s="1"/>
-      <c r="B487" s="2"/>
+      <c r="B487" s="7"/>
       <c r="C487" s="1"/>
       <c r="D487" s="1"/>
       <c r="E487" s="1"/>
@@ -11834,7 +11837,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="488" customHeight="1" ht="18">
       <c r="A488" s="1"/>
-      <c r="B488" s="2"/>
+      <c r="B488" s="7"/>
       <c r="C488" s="1"/>
       <c r="D488" s="1"/>
       <c r="E488" s="1"/>
@@ -11857,7 +11860,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="489" customHeight="1" ht="18">
       <c r="A489" s="1"/>
-      <c r="B489" s="2"/>
+      <c r="B489" s="7"/>
       <c r="C489" s="1"/>
       <c r="D489" s="1"/>
       <c r="E489" s="1"/>
@@ -11880,7 +11883,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="490" customHeight="1" ht="18">
       <c r="A490" s="1"/>
-      <c r="B490" s="2"/>
+      <c r="B490" s="7"/>
       <c r="C490" s="1"/>
       <c r="D490" s="1"/>
       <c r="E490" s="1"/>
@@ -11903,7 +11906,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="491" customHeight="1" ht="18">
       <c r="A491" s="1"/>
-      <c r="B491" s="2"/>
+      <c r="B491" s="7"/>
       <c r="C491" s="1"/>
       <c r="D491" s="1"/>
       <c r="E491" s="1"/>
@@ -11926,7 +11929,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="492" customHeight="1" ht="18">
       <c r="A492" s="1"/>
-      <c r="B492" s="2"/>
+      <c r="B492" s="7"/>
       <c r="C492" s="1"/>
       <c r="D492" s="1"/>
       <c r="E492" s="1"/>
@@ -11949,7 +11952,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="493" customHeight="1" ht="18">
       <c r="A493" s="1"/>
-      <c r="B493" s="2"/>
+      <c r="B493" s="7"/>
       <c r="C493" s="1"/>
       <c r="D493" s="1"/>
       <c r="E493" s="1"/>
@@ -11972,7 +11975,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="494" customHeight="1" ht="18">
       <c r="A494" s="1"/>
-      <c r="B494" s="2"/>
+      <c r="B494" s="7"/>
       <c r="C494" s="1"/>
       <c r="D494" s="1"/>
       <c r="E494" s="1"/>
@@ -11995,7 +11998,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="495" customHeight="1" ht="18">
       <c r="A495" s="1"/>
-      <c r="B495" s="2"/>
+      <c r="B495" s="7"/>
       <c r="C495" s="1"/>
       <c r="D495" s="1"/>
       <c r="E495" s="1"/>
@@ -12018,7 +12021,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="496" customHeight="1" ht="18">
       <c r="A496" s="1"/>
-      <c r="B496" s="2"/>
+      <c r="B496" s="7"/>
       <c r="C496" s="1"/>
       <c r="D496" s="1"/>
       <c r="E496" s="1"/>
@@ -12041,7 +12044,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="497" customHeight="1" ht="18">
       <c r="A497" s="1"/>
-      <c r="B497" s="2"/>
+      <c r="B497" s="7"/>
       <c r="C497" s="1"/>
       <c r="D497" s="1"/>
       <c r="E497" s="1"/>
@@ -12064,7 +12067,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="498" customHeight="1" ht="18">
       <c r="A498" s="1"/>
-      <c r="B498" s="2"/>
+      <c r="B498" s="7"/>
       <c r="C498" s="1"/>
       <c r="D498" s="1"/>
       <c r="E498" s="1"/>
@@ -12087,7 +12090,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="499" customHeight="1" ht="18">
       <c r="A499" s="1"/>
-      <c r="B499" s="2"/>
+      <c r="B499" s="7"/>
       <c r="C499" s="1"/>
       <c r="D499" s="1"/>
       <c r="E499" s="1"/>
@@ -12110,7 +12113,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="500" customHeight="1" ht="18">
       <c r="A500" s="1"/>
-      <c r="B500" s="2"/>
+      <c r="B500" s="7"/>
       <c r="C500" s="1"/>
       <c r="D500" s="1"/>
       <c r="E500" s="1"/>
@@ -12133,7 +12136,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="18">
       <c r="A501" s="1"/>
-      <c r="B501" s="2"/>
+      <c r="B501" s="7"/>
       <c r="C501" s="1"/>
       <c r="D501" s="1"/>
       <c r="E501" s="1"/>
@@ -12156,7 +12159,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="18">
       <c r="A502" s="1"/>
-      <c r="B502" s="2"/>
+      <c r="B502" s="7"/>
       <c r="C502" s="1"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1"/>
@@ -12179,7 +12182,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="18">
       <c r="A503" s="1"/>
-      <c r="B503" s="2"/>
+      <c r="B503" s="7"/>
       <c r="C503" s="1"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1"/>
@@ -12202,7 +12205,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="18">
       <c r="A504" s="1"/>
-      <c r="B504" s="2"/>
+      <c r="B504" s="7"/>
       <c r="C504" s="1"/>
       <c r="D504" s="1"/>
       <c r="E504" s="1"/>
@@ -12225,7 +12228,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="18">
       <c r="A505" s="1"/>
-      <c r="B505" s="2"/>
+      <c r="B505" s="7"/>
       <c r="C505" s="1"/>
       <c r="D505" s="1"/>
       <c r="E505" s="1"/>
@@ -12248,7 +12251,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="18">
       <c r="A506" s="1"/>
-      <c r="B506" s="2"/>
+      <c r="B506" s="7"/>
       <c r="C506" s="1"/>
       <c r="D506" s="1"/>
       <c r="E506" s="1"/>
@@ -12271,7 +12274,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="18">
       <c r="A507" s="1"/>
-      <c r="B507" s="2"/>
+      <c r="B507" s="7"/>
       <c r="C507" s="1"/>
       <c r="D507" s="1"/>
       <c r="E507" s="1"/>
@@ -12294,7 +12297,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="18">
       <c r="A508" s="1"/>
-      <c r="B508" s="2"/>
+      <c r="B508" s="7"/>
       <c r="C508" s="1"/>
       <c r="D508" s="1"/>
       <c r="E508" s="1"/>
@@ -12317,7 +12320,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="18">
       <c r="A509" s="1"/>
-      <c r="B509" s="2"/>
+      <c r="B509" s="7"/>
       <c r="C509" s="1"/>
       <c r="D509" s="1"/>
       <c r="E509" s="1"/>
@@ -12340,7 +12343,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="18">
       <c r="A510" s="1"/>
-      <c r="B510" s="2"/>
+      <c r="B510" s="7"/>
       <c r="C510" s="1"/>
       <c r="D510" s="1"/>
       <c r="E510" s="1"/>
@@ -12363,7 +12366,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="18">
       <c r="A511" s="1"/>
-      <c r="B511" s="2"/>
+      <c r="B511" s="7"/>
       <c r="C511" s="1"/>
       <c r="D511" s="1"/>
       <c r="E511" s="1"/>
@@ -12386,7 +12389,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="18">
       <c r="A512" s="1"/>
-      <c r="B512" s="2"/>
+      <c r="B512" s="7"/>
       <c r="C512" s="1"/>
       <c r="D512" s="1"/>
       <c r="E512" s="1"/>
@@ -12409,7 +12412,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="18">
       <c r="A513" s="1"/>
-      <c r="B513" s="2"/>
+      <c r="B513" s="7"/>
       <c r="C513" s="1"/>
       <c r="D513" s="1"/>
       <c r="E513" s="1"/>
@@ -12432,7 +12435,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="18">
       <c r="A514" s="1"/>
-      <c r="B514" s="2"/>
+      <c r="B514" s="7"/>
       <c r="C514" s="1"/>
       <c r="D514" s="1"/>
       <c r="E514" s="1"/>
@@ -12455,7 +12458,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="18">
       <c r="A515" s="1"/>
-      <c r="B515" s="2"/>
+      <c r="B515" s="7"/>
       <c r="C515" s="1"/>
       <c r="D515" s="1"/>
       <c r="E515" s="1"/>
@@ -12478,7 +12481,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="18">
       <c r="A516" s="1"/>
-      <c r="B516" s="2"/>
+      <c r="B516" s="7"/>
       <c r="C516" s="1"/>
       <c r="D516" s="1"/>
       <c r="E516" s="1"/>
@@ -12501,7 +12504,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="18">
       <c r="A517" s="1"/>
-      <c r="B517" s="2"/>
+      <c r="B517" s="7"/>
       <c r="C517" s="1"/>
       <c r="D517" s="1"/>
       <c r="E517" s="1"/>
@@ -12524,7 +12527,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="18">
       <c r="A518" s="1"/>
-      <c r="B518" s="2"/>
+      <c r="B518" s="7"/>
       <c r="C518" s="1"/>
       <c r="D518" s="1"/>
       <c r="E518" s="1"/>
@@ -12547,7 +12550,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="18">
       <c r="A519" s="1"/>
-      <c r="B519" s="2"/>
+      <c r="B519" s="7"/>
       <c r="C519" s="1"/>
       <c r="D519" s="1"/>
       <c r="E519" s="1"/>
@@ -12570,7 +12573,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="18">
       <c r="A520" s="1"/>
-      <c r="B520" s="2"/>
+      <c r="B520" s="7"/>
       <c r="C520" s="1"/>
       <c r="D520" s="1"/>
       <c r="E520" s="1"/>
@@ -12593,7 +12596,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="18">
       <c r="A521" s="1"/>
-      <c r="B521" s="2"/>
+      <c r="B521" s="7"/>
       <c r="C521" s="1"/>
       <c r="D521" s="1"/>
       <c r="E521" s="1"/>
@@ -12616,7 +12619,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="18">
       <c r="A522" s="1"/>
-      <c r="B522" s="2"/>
+      <c r="B522" s="7"/>
       <c r="C522" s="1"/>
       <c r="D522" s="1"/>
       <c r="E522" s="1"/>
@@ -12639,7 +12642,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="18">
       <c r="A523" s="1"/>
-      <c r="B523" s="2"/>
+      <c r="B523" s="7"/>
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
       <c r="E523" s="1"/>
@@ -12662,7 +12665,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="18">
       <c r="A524" s="1"/>
-      <c r="B524" s="2"/>
+      <c r="B524" s="7"/>
       <c r="C524" s="1"/>
       <c r="D524" s="1"/>
       <c r="E524" s="1"/>
@@ -12685,7 +12688,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="18">
       <c r="A525" s="1"/>
-      <c r="B525" s="2"/>
+      <c r="B525" s="7"/>
       <c r="C525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1"/>
@@ -12708,7 +12711,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="18">
       <c r="A526" s="1"/>
-      <c r="B526" s="2"/>
+      <c r="B526" s="7"/>
       <c r="C526" s="1"/>
       <c r="D526" s="1"/>
       <c r="E526" s="1"/>
@@ -12731,7 +12734,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="18">
       <c r="A527" s="1"/>
-      <c r="B527" s="2"/>
+      <c r="B527" s="7"/>
       <c r="C527" s="1"/>
       <c r="D527" s="1"/>
       <c r="E527" s="1"/>
@@ -12754,7 +12757,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="18">
       <c r="A528" s="1"/>
-      <c r="B528" s="2"/>
+      <c r="B528" s="7"/>
       <c r="C528" s="1"/>
       <c r="D528" s="1"/>
       <c r="E528" s="1"/>
@@ -12777,7 +12780,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="18">
       <c r="A529" s="1"/>
-      <c r="B529" s="2"/>
+      <c r="B529" s="7"/>
       <c r="C529" s="1"/>
       <c r="D529" s="1"/>
       <c r="E529" s="1"/>
@@ -12800,7 +12803,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="530" customHeight="1" ht="18">
       <c r="A530" s="1"/>
-      <c r="B530" s="2"/>
+      <c r="B530" s="7"/>
       <c r="C530" s="1"/>
       <c r="D530" s="1"/>
       <c r="E530" s="1"/>
@@ -12823,7 +12826,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="531" customHeight="1" ht="18">
       <c r="A531" s="1"/>
-      <c r="B531" s="2"/>
+      <c r="B531" s="7"/>
       <c r="C531" s="1"/>
       <c r="D531" s="1"/>
       <c r="E531" s="1"/>
@@ -12846,7 +12849,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="532" customHeight="1" ht="18">
       <c r="A532" s="1"/>
-      <c r="B532" s="2"/>
+      <c r="B532" s="7"/>
       <c r="C532" s="1"/>
       <c r="D532" s="1"/>
       <c r="E532" s="1"/>
@@ -12869,7 +12872,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="533" customHeight="1" ht="18">
       <c r="A533" s="1"/>
-      <c r="B533" s="2"/>
+      <c r="B533" s="7"/>
       <c r="C533" s="1"/>
       <c r="D533" s="1"/>
       <c r="E533" s="1"/>
@@ -12892,7 +12895,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="534" customHeight="1" ht="18">
       <c r="A534" s="1"/>
-      <c r="B534" s="2"/>
+      <c r="B534" s="7"/>
       <c r="C534" s="1"/>
       <c r="D534" s="1"/>
       <c r="E534" s="1"/>
@@ -12915,7 +12918,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="535" customHeight="1" ht="18">
       <c r="A535" s="1"/>
-      <c r="B535" s="2"/>
+      <c r="B535" s="7"/>
       <c r="C535" s="1"/>
       <c r="D535" s="1"/>
       <c r="E535" s="1"/>
@@ -12938,7 +12941,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="536" customHeight="1" ht="18">
       <c r="A536" s="1"/>
-      <c r="B536" s="2"/>
+      <c r="B536" s="7"/>
       <c r="C536" s="1"/>
       <c r="D536" s="1"/>
       <c r="E536" s="1"/>
@@ -12961,7 +12964,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="537" customHeight="1" ht="18">
       <c r="A537" s="1"/>
-      <c r="B537" s="2"/>
+      <c r="B537" s="7"/>
       <c r="C537" s="1"/>
       <c r="D537" s="1"/>
       <c r="E537" s="1"/>
@@ -12984,7 +12987,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="538" customHeight="1" ht="18">
       <c r="A538" s="1"/>
-      <c r="B538" s="2"/>
+      <c r="B538" s="7"/>
       <c r="C538" s="1"/>
       <c r="D538" s="1"/>
       <c r="E538" s="1"/>
@@ -13007,7 +13010,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="539" customHeight="1" ht="18">
       <c r="A539" s="1"/>
-      <c r="B539" s="2"/>
+      <c r="B539" s="7"/>
       <c r="C539" s="1"/>
       <c r="D539" s="1"/>
       <c r="E539" s="1"/>
@@ -13030,7 +13033,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="540" customHeight="1" ht="18">
       <c r="A540" s="1"/>
-      <c r="B540" s="2"/>
+      <c r="B540" s="7"/>
       <c r="C540" s="1"/>
       <c r="D540" s="1"/>
       <c r="E540" s="1"/>
@@ -13053,7 +13056,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="541" customHeight="1" ht="18">
       <c r="A541" s="1"/>
-      <c r="B541" s="2"/>
+      <c r="B541" s="7"/>
       <c r="C541" s="1"/>
       <c r="D541" s="1"/>
       <c r="E541" s="1"/>
@@ -13076,7 +13079,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="542" customHeight="1" ht="18">
       <c r="A542" s="1"/>
-      <c r="B542" s="2"/>
+      <c r="B542" s="7"/>
       <c r="C542" s="1"/>
       <c r="D542" s="1"/>
       <c r="E542" s="1"/>
@@ -13099,7 +13102,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="543" customHeight="1" ht="18">
       <c r="A543" s="1"/>
-      <c r="B543" s="2"/>
+      <c r="B543" s="7"/>
       <c r="C543" s="1"/>
       <c r="D543" s="1"/>
       <c r="E543" s="1"/>
@@ -13122,7 +13125,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="544" customHeight="1" ht="18">
       <c r="A544" s="1"/>
-      <c r="B544" s="2"/>
+      <c r="B544" s="7"/>
       <c r="C544" s="1"/>
       <c r="D544" s="1"/>
       <c r="E544" s="1"/>
@@ -13145,7 +13148,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="545" customHeight="1" ht="18">
       <c r="A545" s="1"/>
-      <c r="B545" s="2"/>
+      <c r="B545" s="7"/>
       <c r="C545" s="1"/>
       <c r="D545" s="1"/>
       <c r="E545" s="1"/>
@@ -13168,7 +13171,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="546" customHeight="1" ht="18">
       <c r="A546" s="1"/>
-      <c r="B546" s="2"/>
+      <c r="B546" s="7"/>
       <c r="C546" s="1"/>
       <c r="D546" s="1"/>
       <c r="E546" s="1"/>
@@ -13191,7 +13194,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="547" customHeight="1" ht="18">
       <c r="A547" s="1"/>
-      <c r="B547" s="2"/>
+      <c r="B547" s="7"/>
       <c r="C547" s="1"/>
       <c r="D547" s="1"/>
       <c r="E547" s="1"/>
@@ -13214,7 +13217,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="548" customHeight="1" ht="18">
       <c r="A548" s="1"/>
-      <c r="B548" s="2"/>
+      <c r="B548" s="7"/>
       <c r="C548" s="1"/>
       <c r="D548" s="1"/>
       <c r="E548" s="1"/>
@@ -13237,7 +13240,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="549" customHeight="1" ht="18">
       <c r="A549" s="1"/>
-      <c r="B549" s="2"/>
+      <c r="B549" s="7"/>
       <c r="C549" s="1"/>
       <c r="D549" s="1"/>
       <c r="E549" s="1"/>
@@ -13260,7 +13263,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="550" customHeight="1" ht="18">
       <c r="A550" s="1"/>
-      <c r="B550" s="2"/>
+      <c r="B550" s="7"/>
       <c r="C550" s="1"/>
       <c r="D550" s="1"/>
       <c r="E550" s="1"/>
@@ -13283,7 +13286,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="551" customHeight="1" ht="18">
       <c r="A551" s="1"/>
-      <c r="B551" s="2"/>
+      <c r="B551" s="7"/>
       <c r="C551" s="1"/>
       <c r="D551" s="1"/>
       <c r="E551" s="1"/>
@@ -13306,7 +13309,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="552" customHeight="1" ht="18">
       <c r="A552" s="1"/>
-      <c r="B552" s="2"/>
+      <c r="B552" s="7"/>
       <c r="C552" s="1"/>
       <c r="D552" s="1"/>
       <c r="E552" s="1"/>
@@ -13329,7 +13332,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="553" customHeight="1" ht="18">
       <c r="A553" s="1"/>
-      <c r="B553" s="2"/>
+      <c r="B553" s="7"/>
       <c r="C553" s="1"/>
       <c r="D553" s="1"/>
       <c r="E553" s="1"/>
@@ -13352,7 +13355,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="554" customHeight="1" ht="18">
       <c r="A554" s="1"/>
-      <c r="B554" s="2"/>
+      <c r="B554" s="7"/>
       <c r="C554" s="1"/>
       <c r="D554" s="1"/>
       <c r="E554" s="1"/>
@@ -13375,7 +13378,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="555" customHeight="1" ht="18">
       <c r="A555" s="1"/>
-      <c r="B555" s="2"/>
+      <c r="B555" s="7"/>
       <c r="C555" s="1"/>
       <c r="D555" s="1"/>
       <c r="E555" s="1"/>
@@ -13398,7 +13401,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="556" customHeight="1" ht="18">
       <c r="A556" s="1"/>
-      <c r="B556" s="2"/>
+      <c r="B556" s="7"/>
       <c r="C556" s="1"/>
       <c r="D556" s="1"/>
       <c r="E556" s="1"/>
@@ -13421,7 +13424,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="557" customHeight="1" ht="18">
       <c r="A557" s="1"/>
-      <c r="B557" s="2"/>
+      <c r="B557" s="7"/>
       <c r="C557" s="1"/>
       <c r="D557" s="1"/>
       <c r="E557" s="1"/>
@@ -13444,7 +13447,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="558" customHeight="1" ht="18">
       <c r="A558" s="1"/>
-      <c r="B558" s="2"/>
+      <c r="B558" s="7"/>
       <c r="C558" s="1"/>
       <c r="D558" s="1"/>
       <c r="E558" s="1"/>
@@ -13467,7 +13470,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="559" customHeight="1" ht="18">
       <c r="A559" s="1"/>
-      <c r="B559" s="2"/>
+      <c r="B559" s="7"/>
       <c r="C559" s="1"/>
       <c r="D559" s="1"/>
       <c r="E559" s="1"/>
@@ -13490,7 +13493,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="560" customHeight="1" ht="18">
       <c r="A560" s="1"/>
-      <c r="B560" s="2"/>
+      <c r="B560" s="7"/>
       <c r="C560" s="1"/>
       <c r="D560" s="1"/>
       <c r="E560" s="1"/>
@@ -13513,7 +13516,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="561" customHeight="1" ht="18">
       <c r="A561" s="1"/>
-      <c r="B561" s="2"/>
+      <c r="B561" s="7"/>
       <c r="C561" s="1"/>
       <c r="D561" s="1"/>
       <c r="E561" s="1"/>
@@ -13536,7 +13539,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="562" customHeight="1" ht="18">
       <c r="A562" s="1"/>
-      <c r="B562" s="2"/>
+      <c r="B562" s="7"/>
       <c r="C562" s="1"/>
       <c r="D562" s="1"/>
       <c r="E562" s="1"/>
@@ -13559,7 +13562,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="563" customHeight="1" ht="18">
       <c r="A563" s="1"/>
-      <c r="B563" s="2"/>
+      <c r="B563" s="7"/>
       <c r="C563" s="1"/>
       <c r="D563" s="1"/>
       <c r="E563" s="1"/>
@@ -13582,7 +13585,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="564" customHeight="1" ht="18">
       <c r="A564" s="1"/>
-      <c r="B564" s="2"/>
+      <c r="B564" s="7"/>
       <c r="C564" s="1"/>
       <c r="D564" s="1"/>
       <c r="E564" s="1"/>
@@ -13605,7 +13608,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="565" customHeight="1" ht="18">
       <c r="A565" s="1"/>
-      <c r="B565" s="2"/>
+      <c r="B565" s="7"/>
       <c r="C565" s="1"/>
       <c r="D565" s="1"/>
       <c r="E565" s="1"/>
@@ -13628,7 +13631,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="566" customHeight="1" ht="18">
       <c r="A566" s="1"/>
-      <c r="B566" s="2"/>
+      <c r="B566" s="7"/>
       <c r="C566" s="1"/>
       <c r="D566" s="1"/>
       <c r="E566" s="1"/>
@@ -13651,7 +13654,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="567" customHeight="1" ht="18">
       <c r="A567" s="1"/>
-      <c r="B567" s="2"/>
+      <c r="B567" s="7"/>
       <c r="C567" s="1"/>
       <c r="D567" s="1"/>
       <c r="E567" s="1"/>
@@ -13674,7 +13677,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="568" customHeight="1" ht="18">
       <c r="A568" s="1"/>
-      <c r="B568" s="2"/>
+      <c r="B568" s="7"/>
       <c r="C568" s="1"/>
       <c r="D568" s="1"/>
       <c r="E568" s="1"/>
@@ -13697,7 +13700,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="569" customHeight="1" ht="18">
       <c r="A569" s="1"/>
-      <c r="B569" s="2"/>
+      <c r="B569" s="7"/>
       <c r="C569" s="1"/>
       <c r="D569" s="1"/>
       <c r="E569" s="1"/>
@@ -13720,7 +13723,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="570" customHeight="1" ht="18">
       <c r="A570" s="1"/>
-      <c r="B570" s="2"/>
+      <c r="B570" s="7"/>
       <c r="C570" s="1"/>
       <c r="D570" s="1"/>
       <c r="E570" s="1"/>
@@ -13743,7 +13746,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="571" customHeight="1" ht="18">
       <c r="A571" s="1"/>
-      <c r="B571" s="2"/>
+      <c r="B571" s="7"/>
       <c r="C571" s="1"/>
       <c r="D571" s="1"/>
       <c r="E571" s="1"/>
@@ -13766,7 +13769,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="572" customHeight="1" ht="18">
       <c r="A572" s="1"/>
-      <c r="B572" s="2"/>
+      <c r="B572" s="7"/>
       <c r="C572" s="1"/>
       <c r="D572" s="1"/>
       <c r="E572" s="1"/>
@@ -13789,7 +13792,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="573" customHeight="1" ht="18">
       <c r="A573" s="1"/>
-      <c r="B573" s="2"/>
+      <c r="B573" s="7"/>
       <c r="C573" s="1"/>
       <c r="D573" s="1"/>
       <c r="E573" s="1"/>
@@ -13812,7 +13815,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="574" customHeight="1" ht="18">
       <c r="A574" s="1"/>
-      <c r="B574" s="2"/>
+      <c r="B574" s="7"/>
       <c r="C574" s="1"/>
       <c r="D574" s="1"/>
       <c r="E574" s="1"/>
@@ -13835,7 +13838,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="575" customHeight="1" ht="18">
       <c r="A575" s="1"/>
-      <c r="B575" s="2"/>
+      <c r="B575" s="7"/>
       <c r="C575" s="1"/>
       <c r="D575" s="1"/>
       <c r="E575" s="1"/>
@@ -13858,7 +13861,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="576" customHeight="1" ht="18">
       <c r="A576" s="1"/>
-      <c r="B576" s="2"/>
+      <c r="B576" s="7"/>
       <c r="C576" s="1"/>
       <c r="D576" s="1"/>
       <c r="E576" s="1"/>
@@ -13881,7 +13884,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="577" customHeight="1" ht="18">
       <c r="A577" s="1"/>
-      <c r="B577" s="2"/>
+      <c r="B577" s="7"/>
       <c r="C577" s="1"/>
       <c r="D577" s="1"/>
       <c r="E577" s="1"/>
@@ -13904,7 +13907,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="578" customHeight="1" ht="18">
       <c r="A578" s="1"/>
-      <c r="B578" s="2"/>
+      <c r="B578" s="7"/>
       <c r="C578" s="1"/>
       <c r="D578" s="1"/>
       <c r="E578" s="1"/>
@@ -13927,7 +13930,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="579" customHeight="1" ht="18">
       <c r="A579" s="1"/>
-      <c r="B579" s="2"/>
+      <c r="B579" s="7"/>
       <c r="C579" s="1"/>
       <c r="D579" s="1"/>
       <c r="E579" s="1"/>
@@ -13950,7 +13953,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="580" customHeight="1" ht="18">
       <c r="A580" s="1"/>
-      <c r="B580" s="2"/>
+      <c r="B580" s="7"/>
       <c r="C580" s="1"/>
       <c r="D580" s="1"/>
       <c r="E580" s="1"/>
@@ -13973,7 +13976,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="581" customHeight="1" ht="18">
       <c r="A581" s="1"/>
-      <c r="B581" s="2"/>
+      <c r="B581" s="7"/>
       <c r="C581" s="1"/>
       <c r="D581" s="1"/>
       <c r="E581" s="1"/>
@@ -13996,7 +13999,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="582" customHeight="1" ht="18">
       <c r="A582" s="1"/>
-      <c r="B582" s="2"/>
+      <c r="B582" s="7"/>
       <c r="C582" s="1"/>
       <c r="D582" s="1"/>
       <c r="E582" s="1"/>
@@ -14019,7 +14022,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="583" customHeight="1" ht="18">
       <c r="A583" s="1"/>
-      <c r="B583" s="2"/>
+      <c r="B583" s="7"/>
       <c r="C583" s="1"/>
       <c r="D583" s="1"/>
       <c r="E583" s="1"/>
@@ -14042,7 +14045,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="584" customHeight="1" ht="18">
       <c r="A584" s="1"/>
-      <c r="B584" s="2"/>
+      <c r="B584" s="7"/>
       <c r="C584" s="1"/>
       <c r="D584" s="1"/>
       <c r="E584" s="1"/>
@@ -14065,7 +14068,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="585" customHeight="1" ht="18">
       <c r="A585" s="1"/>
-      <c r="B585" s="2"/>
+      <c r="B585" s="7"/>
       <c r="C585" s="1"/>
       <c r="D585" s="1"/>
       <c r="E585" s="1"/>
@@ -14088,7 +14091,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="586" customHeight="1" ht="18">
       <c r="A586" s="1"/>
-      <c r="B586" s="2"/>
+      <c r="B586" s="7"/>
       <c r="C586" s="1"/>
       <c r="D586" s="1"/>
       <c r="E586" s="1"/>
@@ -14111,7 +14114,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="587" customHeight="1" ht="18">
       <c r="A587" s="1"/>
-      <c r="B587" s="2"/>
+      <c r="B587" s="7"/>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
       <c r="E587" s="1"/>
@@ -14134,7 +14137,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="588" customHeight="1" ht="18">
       <c r="A588" s="1"/>
-      <c r="B588" s="2"/>
+      <c r="B588" s="7"/>
       <c r="C588" s="1"/>
       <c r="D588" s="1"/>
       <c r="E588" s="1"/>
@@ -14157,7 +14160,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="589" customHeight="1" ht="18">
       <c r="A589" s="1"/>
-      <c r="B589" s="2"/>
+      <c r="B589" s="7"/>
       <c r="C589" s="1"/>
       <c r="D589" s="1"/>
       <c r="E589" s="1"/>
@@ -14180,7 +14183,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="590" customHeight="1" ht="18">
       <c r="A590" s="1"/>
-      <c r="B590" s="2"/>
+      <c r="B590" s="7"/>
       <c r="C590" s="1"/>
       <c r="D590" s="1"/>
       <c r="E590" s="1"/>
@@ -14203,7 +14206,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="591" customHeight="1" ht="18">
       <c r="A591" s="1"/>
-      <c r="B591" s="2"/>
+      <c r="B591" s="7"/>
       <c r="C591" s="1"/>
       <c r="D591" s="1"/>
       <c r="E591" s="1"/>
@@ -14226,7 +14229,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="592" customHeight="1" ht="18">
       <c r="A592" s="1"/>
-      <c r="B592" s="2"/>
+      <c r="B592" s="7"/>
       <c r="C592" s="1"/>
       <c r="D592" s="1"/>
       <c r="E592" s="1"/>
@@ -14249,7 +14252,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="593" customHeight="1" ht="18">
       <c r="A593" s="1"/>
-      <c r="B593" s="2"/>
+      <c r="B593" s="7"/>
       <c r="C593" s="1"/>
       <c r="D593" s="1"/>
       <c r="E593" s="1"/>
@@ -14272,7 +14275,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="594" customHeight="1" ht="18">
       <c r="A594" s="1"/>
-      <c r="B594" s="2"/>
+      <c r="B594" s="7"/>
       <c r="C594" s="1"/>
       <c r="D594" s="1"/>
       <c r="E594" s="1"/>
@@ -14295,7 +14298,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="595" customHeight="1" ht="18">
       <c r="A595" s="1"/>
-      <c r="B595" s="2"/>
+      <c r="B595" s="7"/>
       <c r="C595" s="1"/>
       <c r="D595" s="1"/>
       <c r="E595" s="1"/>
@@ -14318,7 +14321,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="596" customHeight="1" ht="18">
       <c r="A596" s="1"/>
-      <c r="B596" s="2"/>
+      <c r="B596" s="7"/>
       <c r="C596" s="1"/>
       <c r="D596" s="1"/>
       <c r="E596" s="1"/>
@@ -14341,7 +14344,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="597" customHeight="1" ht="18">
       <c r="A597" s="1"/>
-      <c r="B597" s="2"/>
+      <c r="B597" s="7"/>
       <c r="C597" s="1"/>
       <c r="D597" s="1"/>
       <c r="E597" s="1"/>
@@ -14364,7 +14367,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="598" customHeight="1" ht="18">
       <c r="A598" s="1"/>
-      <c r="B598" s="2"/>
+      <c r="B598" s="7"/>
       <c r="C598" s="1"/>
       <c r="D598" s="1"/>
       <c r="E598" s="1"/>
@@ -14387,7 +14390,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="599" customHeight="1" ht="18">
       <c r="A599" s="1"/>
-      <c r="B599" s="2"/>
+      <c r="B599" s="7"/>
       <c r="C599" s="1"/>
       <c r="D599" s="1"/>
       <c r="E599" s="1"/>
@@ -14410,7 +14413,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="600" customHeight="1" ht="18">
       <c r="A600" s="1"/>
-      <c r="B600" s="2"/>
+      <c r="B600" s="7"/>
       <c r="C600" s="1"/>
       <c r="D600" s="1"/>
       <c r="E600" s="1"/>
@@ -14433,7 +14436,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="601" customHeight="1" ht="18">
       <c r="A601" s="1"/>
-      <c r="B601" s="2"/>
+      <c r="B601" s="7"/>
       <c r="C601" s="1"/>
       <c r="D601" s="1"/>
       <c r="E601" s="1"/>
@@ -14456,7 +14459,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="602" customHeight="1" ht="18">
       <c r="A602" s="1"/>
-      <c r="B602" s="2"/>
+      <c r="B602" s="7"/>
       <c r="C602" s="1"/>
       <c r="D602" s="1"/>
       <c r="E602" s="1"/>
@@ -14479,7 +14482,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="603" customHeight="1" ht="18">
       <c r="A603" s="1"/>
-      <c r="B603" s="2"/>
+      <c r="B603" s="7"/>
       <c r="C603" s="1"/>
       <c r="D603" s="1"/>
       <c r="E603" s="1"/>
@@ -14502,7 +14505,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="604" customHeight="1" ht="18">
       <c r="A604" s="1"/>
-      <c r="B604" s="2"/>
+      <c r="B604" s="7"/>
       <c r="C604" s="1"/>
       <c r="D604" s="1"/>
       <c r="E604" s="1"/>
@@ -14525,7 +14528,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="605" customHeight="1" ht="18">
       <c r="A605" s="1"/>
-      <c r="B605" s="2"/>
+      <c r="B605" s="7"/>
       <c r="C605" s="1"/>
       <c r="D605" s="1"/>
       <c r="E605" s="1"/>
@@ -14548,7 +14551,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="606" customHeight="1" ht="18">
       <c r="A606" s="1"/>
-      <c r="B606" s="2"/>
+      <c r="B606" s="7"/>
       <c r="C606" s="1"/>
       <c r="D606" s="1"/>
       <c r="E606" s="1"/>
@@ -14571,7 +14574,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="607" customHeight="1" ht="18">
       <c r="A607" s="1"/>
-      <c r="B607" s="2"/>
+      <c r="B607" s="7"/>
       <c r="C607" s="1"/>
       <c r="D607" s="1"/>
       <c r="E607" s="1"/>
@@ -14594,7 +14597,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="608" customHeight="1" ht="18">
       <c r="A608" s="1"/>
-      <c r="B608" s="2"/>
+      <c r="B608" s="7"/>
       <c r="C608" s="1"/>
       <c r="D608" s="1"/>
       <c r="E608" s="1"/>
@@ -14617,7 +14620,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="609" customHeight="1" ht="18">
       <c r="A609" s="1"/>
-      <c r="B609" s="2"/>
+      <c r="B609" s="7"/>
       <c r="C609" s="1"/>
       <c r="D609" s="1"/>
       <c r="E609" s="1"/>
@@ -14640,7 +14643,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="610" customHeight="1" ht="18">
       <c r="A610" s="1"/>
-      <c r="B610" s="2"/>
+      <c r="B610" s="7"/>
       <c r="C610" s="1"/>
       <c r="D610" s="1"/>
       <c r="E610" s="1"/>
@@ -14663,7 +14666,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="611" customHeight="1" ht="18">
       <c r="A611" s="1"/>
-      <c r="B611" s="2"/>
+      <c r="B611" s="7"/>
       <c r="C611" s="1"/>
       <c r="D611" s="1"/>
       <c r="E611" s="1"/>
@@ -14686,7 +14689,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="612" customHeight="1" ht="18">
       <c r="A612" s="1"/>
-      <c r="B612" s="2"/>
+      <c r="B612" s="7"/>
       <c r="C612" s="1"/>
       <c r="D612" s="1"/>
       <c r="E612" s="1"/>
@@ -14709,7 +14712,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="613" customHeight="1" ht="18">
       <c r="A613" s="1"/>
-      <c r="B613" s="2"/>
+      <c r="B613" s="7"/>
       <c r="C613" s="1"/>
       <c r="D613" s="1"/>
       <c r="E613" s="1"/>
@@ -14732,7 +14735,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="614" customHeight="1" ht="18">
       <c r="A614" s="1"/>
-      <c r="B614" s="2"/>
+      <c r="B614" s="7"/>
       <c r="C614" s="1"/>
       <c r="D614" s="1"/>
       <c r="E614" s="1"/>
@@ -14755,7 +14758,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="615" customHeight="1" ht="18">
       <c r="A615" s="1"/>
-      <c r="B615" s="2"/>
+      <c r="B615" s="7"/>
       <c r="C615" s="1"/>
       <c r="D615" s="1"/>
       <c r="E615" s="1"/>
@@ -14778,7 +14781,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="616" customHeight="1" ht="18">
       <c r="A616" s="1"/>
-      <c r="B616" s="2"/>
+      <c r="B616" s="7"/>
       <c r="C616" s="1"/>
       <c r="D616" s="1"/>
       <c r="E616" s="1"/>
@@ -14801,7 +14804,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="617" customHeight="1" ht="18">
       <c r="A617" s="1"/>
-      <c r="B617" s="2"/>
+      <c r="B617" s="7"/>
       <c r="C617" s="1"/>
       <c r="D617" s="1"/>
       <c r="E617" s="1"/>
@@ -14824,7 +14827,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="618" customHeight="1" ht="18">
       <c r="A618" s="1"/>
-      <c r="B618" s="2"/>
+      <c r="B618" s="7"/>
       <c r="C618" s="1"/>
       <c r="D618" s="1"/>
       <c r="E618" s="1"/>
@@ -14847,7 +14850,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="619" customHeight="1" ht="18">
       <c r="A619" s="1"/>
-      <c r="B619" s="2"/>
+      <c r="B619" s="7"/>
       <c r="C619" s="1"/>
       <c r="D619" s="1"/>
       <c r="E619" s="1"/>
@@ -14870,7 +14873,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="620" customHeight="1" ht="18">
       <c r="A620" s="1"/>
-      <c r="B620" s="2"/>
+      <c r="B620" s="7"/>
       <c r="C620" s="1"/>
       <c r="D620" s="1"/>
       <c r="E620" s="1"/>
@@ -14893,7 +14896,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="621" customHeight="1" ht="18">
       <c r="A621" s="1"/>
-      <c r="B621" s="2"/>
+      <c r="B621" s="7"/>
       <c r="C621" s="1"/>
       <c r="D621" s="1"/>
       <c r="E621" s="1"/>
@@ -14916,7 +14919,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="622" customHeight="1" ht="18">
       <c r="A622" s="1"/>
-      <c r="B622" s="2"/>
+      <c r="B622" s="7"/>
       <c r="C622" s="1"/>
       <c r="D622" s="1"/>
       <c r="E622" s="1"/>
@@ -14939,7 +14942,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="623" customHeight="1" ht="18">
       <c r="A623" s="1"/>
-      <c r="B623" s="2"/>
+      <c r="B623" s="7"/>
       <c r="C623" s="1"/>
       <c r="D623" s="1"/>
       <c r="E623" s="1"/>
@@ -14962,7 +14965,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="624" customHeight="1" ht="18">
       <c r="A624" s="1"/>
-      <c r="B624" s="2"/>
+      <c r="B624" s="7"/>
       <c r="C624" s="1"/>
       <c r="D624" s="1"/>
       <c r="E624" s="1"/>
@@ -14985,7 +14988,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="625" customHeight="1" ht="18">
       <c r="A625" s="1"/>
-      <c r="B625" s="2"/>
+      <c r="B625" s="7"/>
       <c r="C625" s="1"/>
       <c r="D625" s="1"/>
       <c r="E625" s="1"/>
@@ -15008,7 +15011,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="626" customHeight="1" ht="18">
       <c r="A626" s="1"/>
-      <c r="B626" s="2"/>
+      <c r="B626" s="7"/>
       <c r="C626" s="1"/>
       <c r="D626" s="1"/>
       <c r="E626" s="1"/>
@@ -15031,7 +15034,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="627" customHeight="1" ht="18">
       <c r="A627" s="1"/>
-      <c r="B627" s="2"/>
+      <c r="B627" s="7"/>
       <c r="C627" s="1"/>
       <c r="D627" s="1"/>
       <c r="E627" s="1"/>
@@ -15054,7 +15057,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="628" customHeight="1" ht="18">
       <c r="A628" s="1"/>
-      <c r="B628" s="2"/>
+      <c r="B628" s="7"/>
       <c r="C628" s="1"/>
       <c r="D628" s="1"/>
       <c r="E628" s="1"/>
@@ -15077,7 +15080,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="629" customHeight="1" ht="18">
       <c r="A629" s="1"/>
-      <c r="B629" s="2"/>
+      <c r="B629" s="7"/>
       <c r="C629" s="1"/>
       <c r="D629" s="1"/>
       <c r="E629" s="1"/>
@@ -15100,7 +15103,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="630" customHeight="1" ht="18">
       <c r="A630" s="1"/>
-      <c r="B630" s="2"/>
+      <c r="B630" s="7"/>
       <c r="C630" s="1"/>
       <c r="D630" s="1"/>
       <c r="E630" s="1"/>
@@ -15123,7 +15126,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="631" customHeight="1" ht="18">
       <c r="A631" s="1"/>
-      <c r="B631" s="2"/>
+      <c r="B631" s="7"/>
       <c r="C631" s="1"/>
       <c r="D631" s="1"/>
       <c r="E631" s="1"/>
@@ -15146,7 +15149,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="632" customHeight="1" ht="18">
       <c r="A632" s="1"/>
-      <c r="B632" s="2"/>
+      <c r="B632" s="7"/>
       <c r="C632" s="1"/>
       <c r="D632" s="1"/>
       <c r="E632" s="1"/>
@@ -15169,7 +15172,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="633" customHeight="1" ht="18">
       <c r="A633" s="1"/>
-      <c r="B633" s="2"/>
+      <c r="B633" s="7"/>
       <c r="C633" s="1"/>
       <c r="D633" s="1"/>
       <c r="E633" s="1"/>
@@ -15192,7 +15195,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="634" customHeight="1" ht="18">
       <c r="A634" s="1"/>
-      <c r="B634" s="2"/>
+      <c r="B634" s="7"/>
       <c r="C634" s="1"/>
       <c r="D634" s="1"/>
       <c r="E634" s="1"/>
@@ -15215,7 +15218,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="635" customHeight="1" ht="18">
       <c r="A635" s="1"/>
-      <c r="B635" s="2"/>
+      <c r="B635" s="7"/>
       <c r="C635" s="1"/>
       <c r="D635" s="1"/>
       <c r="E635" s="1"/>
@@ -15238,7 +15241,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="636" customHeight="1" ht="18">
       <c r="A636" s="1"/>
-      <c r="B636" s="2"/>
+      <c r="B636" s="7"/>
       <c r="C636" s="1"/>
       <c r="D636" s="1"/>
       <c r="E636" s="1"/>
@@ -15261,7 +15264,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="637" customHeight="1" ht="18">
       <c r="A637" s="1"/>
-      <c r="B637" s="2"/>
+      <c r="B637" s="7"/>
       <c r="C637" s="1"/>
       <c r="D637" s="1"/>
       <c r="E637" s="1"/>
@@ -15284,7 +15287,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="638" customHeight="1" ht="18">
       <c r="A638" s="1"/>
-      <c r="B638" s="2"/>
+      <c r="B638" s="7"/>
       <c r="C638" s="1"/>
       <c r="D638" s="1"/>
       <c r="E638" s="1"/>
@@ -15307,7 +15310,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="639" customHeight="1" ht="18">
       <c r="A639" s="1"/>
-      <c r="B639" s="2"/>
+      <c r="B639" s="7"/>
       <c r="C639" s="1"/>
       <c r="D639" s="1"/>
       <c r="E639" s="1"/>
@@ -15330,7 +15333,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="640" customHeight="1" ht="18">
       <c r="A640" s="1"/>
-      <c r="B640" s="2"/>
+      <c r="B640" s="7"/>
       <c r="C640" s="1"/>
       <c r="D640" s="1"/>
       <c r="E640" s="1"/>
@@ -15353,7 +15356,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="641" customHeight="1" ht="18">
       <c r="A641" s="1"/>
-      <c r="B641" s="2"/>
+      <c r="B641" s="7"/>
       <c r="C641" s="1"/>
       <c r="D641" s="1"/>
       <c r="E641" s="1"/>
@@ -15376,7 +15379,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="642" customHeight="1" ht="18">
       <c r="A642" s="1"/>
-      <c r="B642" s="2"/>
+      <c r="B642" s="7"/>
       <c r="C642" s="1"/>
       <c r="D642" s="1"/>
       <c r="E642" s="1"/>
@@ -15399,7 +15402,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="643" customHeight="1" ht="18">
       <c r="A643" s="1"/>
-      <c r="B643" s="2"/>
+      <c r="B643" s="7"/>
       <c r="C643" s="1"/>
       <c r="D643" s="1"/>
       <c r="E643" s="1"/>
@@ -15422,7 +15425,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="644" customHeight="1" ht="18">
       <c r="A644" s="1"/>
-      <c r="B644" s="2"/>
+      <c r="B644" s="7"/>
       <c r="C644" s="1"/>
       <c r="D644" s="1"/>
       <c r="E644" s="1"/>
@@ -15445,7 +15448,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="645" customHeight="1" ht="18">
       <c r="A645" s="1"/>
-      <c r="B645" s="2"/>
+      <c r="B645" s="7"/>
       <c r="C645" s="1"/>
       <c r="D645" s="1"/>
       <c r="E645" s="1"/>
@@ -15468,7 +15471,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="646" customHeight="1" ht="18">
       <c r="A646" s="1"/>
-      <c r="B646" s="2"/>
+      <c r="B646" s="7"/>
       <c r="C646" s="1"/>
       <c r="D646" s="1"/>
       <c r="E646" s="1"/>
@@ -15491,7 +15494,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="647" customHeight="1" ht="18">
       <c r="A647" s="1"/>
-      <c r="B647" s="2"/>
+      <c r="B647" s="7"/>
       <c r="C647" s="1"/>
       <c r="D647" s="1"/>
       <c r="E647" s="1"/>
@@ -15514,7 +15517,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="648" customHeight="1" ht="18">
       <c r="A648" s="1"/>
-      <c r="B648" s="2"/>
+      <c r="B648" s="7"/>
       <c r="C648" s="1"/>
       <c r="D648" s="1"/>
       <c r="E648" s="1"/>
@@ -15537,7 +15540,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="649" customHeight="1" ht="18">
       <c r="A649" s="1"/>
-      <c r="B649" s="2"/>
+      <c r="B649" s="7"/>
       <c r="C649" s="1"/>
       <c r="D649" s="1"/>
       <c r="E649" s="1"/>
@@ -15560,7 +15563,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="650" customHeight="1" ht="18">
       <c r="A650" s="1"/>
-      <c r="B650" s="2"/>
+      <c r="B650" s="7"/>
       <c r="C650" s="1"/>
       <c r="D650" s="1"/>
       <c r="E650" s="1"/>
@@ -15583,7 +15586,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="651" customHeight="1" ht="18">
       <c r="A651" s="1"/>
-      <c r="B651" s="2"/>
+      <c r="B651" s="7"/>
       <c r="C651" s="1"/>
       <c r="D651" s="1"/>
       <c r="E651" s="1"/>
@@ -15606,7 +15609,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="652" customHeight="1" ht="18">
       <c r="A652" s="1"/>
-      <c r="B652" s="2"/>
+      <c r="B652" s="7"/>
       <c r="C652" s="1"/>
       <c r="D652" s="1"/>
       <c r="E652" s="1"/>
@@ -15629,7 +15632,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="653" customHeight="1" ht="18">
       <c r="A653" s="1"/>
-      <c r="B653" s="2"/>
+      <c r="B653" s="7"/>
       <c r="C653" s="1"/>
       <c r="D653" s="1"/>
       <c r="E653" s="1"/>
@@ -15652,7 +15655,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="654" customHeight="1" ht="18">
       <c r="A654" s="1"/>
-      <c r="B654" s="2"/>
+      <c r="B654" s="7"/>
       <c r="C654" s="1"/>
       <c r="D654" s="1"/>
       <c r="E654" s="1"/>
@@ -15675,7 +15678,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="655" customHeight="1" ht="18">
       <c r="A655" s="1"/>
-      <c r="B655" s="2"/>
+      <c r="B655" s="7"/>
       <c r="C655" s="1"/>
       <c r="D655" s="1"/>
       <c r="E655" s="1"/>
@@ -15698,7 +15701,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="656" customHeight="1" ht="18">
       <c r="A656" s="1"/>
-      <c r="B656" s="2"/>
+      <c r="B656" s="7"/>
       <c r="C656" s="1"/>
       <c r="D656" s="1"/>
       <c r="E656" s="1"/>
@@ -15721,7 +15724,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="657" customHeight="1" ht="18">
       <c r="A657" s="1"/>
-      <c r="B657" s="2"/>
+      <c r="B657" s="7"/>
       <c r="C657" s="1"/>
       <c r="D657" s="1"/>
       <c r="E657" s="1"/>
@@ -15744,7 +15747,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="658" customHeight="1" ht="18">
       <c r="A658" s="1"/>
-      <c r="B658" s="2"/>
+      <c r="B658" s="7"/>
       <c r="C658" s="1"/>
       <c r="D658" s="1"/>
       <c r="E658" s="1"/>
@@ -15767,7 +15770,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="659" customHeight="1" ht="18">
       <c r="A659" s="1"/>
-      <c r="B659" s="2"/>
+      <c r="B659" s="7"/>
       <c r="C659" s="1"/>
       <c r="D659" s="1"/>
       <c r="E659" s="1"/>
@@ -15790,7 +15793,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="660" customHeight="1" ht="18">
       <c r="A660" s="1"/>
-      <c r="B660" s="2"/>
+      <c r="B660" s="7"/>
       <c r="C660" s="1"/>
       <c r="D660" s="1"/>
       <c r="E660" s="1"/>
@@ -15813,7 +15816,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="661" customHeight="1" ht="18">
       <c r="A661" s="1"/>
-      <c r="B661" s="2"/>
+      <c r="B661" s="7"/>
       <c r="C661" s="1"/>
       <c r="D661" s="1"/>
       <c r="E661" s="1"/>
@@ -15836,7 +15839,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="662" customHeight="1" ht="18">
       <c r="A662" s="1"/>
-      <c r="B662" s="2"/>
+      <c r="B662" s="7"/>
       <c r="C662" s="1"/>
       <c r="D662" s="1"/>
       <c r="E662" s="1"/>
@@ -15859,7 +15862,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="663" customHeight="1" ht="18">
       <c r="A663" s="1"/>
-      <c r="B663" s="2"/>
+      <c r="B663" s="7"/>
       <c r="C663" s="1"/>
       <c r="D663" s="1"/>
       <c r="E663" s="1"/>
@@ -15882,7 +15885,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="664" customHeight="1" ht="18">
       <c r="A664" s="1"/>
-      <c r="B664" s="2"/>
+      <c r="B664" s="7"/>
       <c r="C664" s="1"/>
       <c r="D664" s="1"/>
       <c r="E664" s="1"/>
@@ -15905,7 +15908,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="665" customHeight="1" ht="18">
       <c r="A665" s="1"/>
-      <c r="B665" s="2"/>
+      <c r="B665" s="7"/>
       <c r="C665" s="1"/>
       <c r="D665" s="1"/>
       <c r="E665" s="1"/>
@@ -15928,7 +15931,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="666" customHeight="1" ht="18">
       <c r="A666" s="1"/>
-      <c r="B666" s="2"/>
+      <c r="B666" s="7"/>
       <c r="C666" s="1"/>
       <c r="D666" s="1"/>
       <c r="E666" s="1"/>
@@ -15951,7 +15954,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="667" customHeight="1" ht="18">
       <c r="A667" s="1"/>
-      <c r="B667" s="2"/>
+      <c r="B667" s="7"/>
       <c r="C667" s="1"/>
       <c r="D667" s="1"/>
       <c r="E667" s="1"/>
@@ -15974,7 +15977,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="668" customHeight="1" ht="18">
       <c r="A668" s="1"/>
-      <c r="B668" s="2"/>
+      <c r="B668" s="7"/>
       <c r="C668" s="1"/>
       <c r="D668" s="1"/>
       <c r="E668" s="1"/>
@@ -15997,7 +16000,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="669" customHeight="1" ht="18">
       <c r="A669" s="1"/>
-      <c r="B669" s="2"/>
+      <c r="B669" s="7"/>
       <c r="C669" s="1"/>
       <c r="D669" s="1"/>
       <c r="E669" s="1"/>
@@ -16020,7 +16023,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="670" customHeight="1" ht="18">
       <c r="A670" s="1"/>
-      <c r="B670" s="2"/>
+      <c r="B670" s="7"/>
       <c r="C670" s="1"/>
       <c r="D670" s="1"/>
       <c r="E670" s="1"/>
@@ -16043,7 +16046,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="671" customHeight="1" ht="18">
       <c r="A671" s="1"/>
-      <c r="B671" s="2"/>
+      <c r="B671" s="7"/>
       <c r="C671" s="1"/>
       <c r="D671" s="1"/>
       <c r="E671" s="1"/>
@@ -16066,7 +16069,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="672" customHeight="1" ht="18">
       <c r="A672" s="1"/>
-      <c r="B672" s="2"/>
+      <c r="B672" s="7"/>
       <c r="C672" s="1"/>
       <c r="D672" s="1"/>
       <c r="E672" s="1"/>
@@ -16089,7 +16092,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="673" customHeight="1" ht="18">
       <c r="A673" s="1"/>
-      <c r="B673" s="2"/>
+      <c r="B673" s="7"/>
       <c r="C673" s="1"/>
       <c r="D673" s="1"/>
       <c r="E673" s="1"/>
@@ -16112,7 +16115,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="674" customHeight="1" ht="18">
       <c r="A674" s="1"/>
-      <c r="B674" s="2"/>
+      <c r="B674" s="7"/>
       <c r="C674" s="1"/>
       <c r="D674" s="1"/>
       <c r="E674" s="1"/>
@@ -16135,7 +16138,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="675" customHeight="1" ht="18">
       <c r="A675" s="1"/>
-      <c r="B675" s="2"/>
+      <c r="B675" s="7"/>
       <c r="C675" s="1"/>
       <c r="D675" s="1"/>
       <c r="E675" s="1"/>
@@ -16158,7 +16161,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="676" customHeight="1" ht="18">
       <c r="A676" s="1"/>
-      <c r="B676" s="2"/>
+      <c r="B676" s="7"/>
       <c r="C676" s="1"/>
       <c r="D676" s="1"/>
       <c r="E676" s="1"/>
@@ -16181,7 +16184,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="677" customHeight="1" ht="18">
       <c r="A677" s="1"/>
-      <c r="B677" s="2"/>
+      <c r="B677" s="7"/>
       <c r="C677" s="1"/>
       <c r="D677" s="1"/>
       <c r="E677" s="1"/>
@@ -16204,7 +16207,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="678" customHeight="1" ht="18">
       <c r="A678" s="1"/>
-      <c r="B678" s="2"/>
+      <c r="B678" s="7"/>
       <c r="C678" s="1"/>
       <c r="D678" s="1"/>
       <c r="E678" s="1"/>
@@ -16227,7 +16230,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="679" customHeight="1" ht="18">
       <c r="A679" s="1"/>
-      <c r="B679" s="2"/>
+      <c r="B679" s="7"/>
       <c r="C679" s="1"/>
       <c r="D679" s="1"/>
       <c r="E679" s="1"/>
@@ -16250,7 +16253,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="680" customHeight="1" ht="18">
       <c r="A680" s="1"/>
-      <c r="B680" s="2"/>
+      <c r="B680" s="7"/>
       <c r="C680" s="1"/>
       <c r="D680" s="1"/>
       <c r="E680" s="1"/>
@@ -16273,7 +16276,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="681" customHeight="1" ht="18">
       <c r="A681" s="1"/>
-      <c r="B681" s="2"/>
+      <c r="B681" s="7"/>
       <c r="C681" s="1"/>
       <c r="D681" s="1"/>
       <c r="E681" s="1"/>
@@ -16296,7 +16299,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="682" customHeight="1" ht="18">
       <c r="A682" s="1"/>
-      <c r="B682" s="2"/>
+      <c r="B682" s="7"/>
       <c r="C682" s="1"/>
       <c r="D682" s="1"/>
       <c r="E682" s="1"/>
@@ -16319,7 +16322,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="683" customHeight="1" ht="18">
       <c r="A683" s="1"/>
-      <c r="B683" s="2"/>
+      <c r="B683" s="7"/>
       <c r="C683" s="1"/>
       <c r="D683" s="1"/>
       <c r="E683" s="1"/>
@@ -16342,7 +16345,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="684" customHeight="1" ht="18">
       <c r="A684" s="1"/>
-      <c r="B684" s="2"/>
+      <c r="B684" s="7"/>
       <c r="C684" s="1"/>
       <c r="D684" s="1"/>
       <c r="E684" s="1"/>
@@ -16365,7 +16368,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="685" customHeight="1" ht="18">
       <c r="A685" s="1"/>
-      <c r="B685" s="2"/>
+      <c r="B685" s="7"/>
       <c r="C685" s="1"/>
       <c r="D685" s="1"/>
       <c r="E685" s="1"/>
@@ -16388,7 +16391,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="686" customHeight="1" ht="18">
       <c r="A686" s="1"/>
-      <c r="B686" s="2"/>
+      <c r="B686" s="7"/>
       <c r="C686" s="1"/>
       <c r="D686" s="1"/>
       <c r="E686" s="1"/>
@@ -16411,7 +16414,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="687" customHeight="1" ht="18">
       <c r="A687" s="1"/>
-      <c r="B687" s="2"/>
+      <c r="B687" s="7"/>
       <c r="C687" s="1"/>
       <c r="D687" s="1"/>
       <c r="E687" s="1"/>
@@ -16434,7 +16437,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="688" customHeight="1" ht="18">
       <c r="A688" s="1"/>
-      <c r="B688" s="2"/>
+      <c r="B688" s="7"/>
       <c r="C688" s="1"/>
       <c r="D688" s="1"/>
       <c r="E688" s="1"/>
@@ -16457,7 +16460,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="689" customHeight="1" ht="18">
       <c r="A689" s="1"/>
-      <c r="B689" s="2"/>
+      <c r="B689" s="7"/>
       <c r="C689" s="1"/>
       <c r="D689" s="1"/>
       <c r="E689" s="1"/>
@@ -16480,7 +16483,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="690" customHeight="1" ht="18">
       <c r="A690" s="1"/>
-      <c r="B690" s="2"/>
+      <c r="B690" s="7"/>
       <c r="C690" s="1"/>
       <c r="D690" s="1"/>
       <c r="E690" s="1"/>
@@ -16503,7 +16506,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="691" customHeight="1" ht="18">
       <c r="A691" s="1"/>
-      <c r="B691" s="2"/>
+      <c r="B691" s="7"/>
       <c r="C691" s="1"/>
       <c r="D691" s="1"/>
       <c r="E691" s="1"/>
@@ -16526,7 +16529,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="692" customHeight="1" ht="18">
       <c r="A692" s="1"/>
-      <c r="B692" s="2"/>
+      <c r="B692" s="7"/>
       <c r="C692" s="1"/>
       <c r="D692" s="1"/>
       <c r="E692" s="1"/>
@@ -16549,7 +16552,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="693" customHeight="1" ht="18">
       <c r="A693" s="1"/>
-      <c r="B693" s="2"/>
+      <c r="B693" s="7"/>
       <c r="C693" s="1"/>
       <c r="D693" s="1"/>
       <c r="E693" s="1"/>
@@ -16572,7 +16575,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="694" customHeight="1" ht="18">
       <c r="A694" s="1"/>
-      <c r="B694" s="2"/>
+      <c r="B694" s="7"/>
       <c r="C694" s="1"/>
       <c r="D694" s="1"/>
       <c r="E694" s="1"/>
@@ -16595,7 +16598,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="695" customHeight="1" ht="18">
       <c r="A695" s="1"/>
-      <c r="B695" s="2"/>
+      <c r="B695" s="7"/>
       <c r="C695" s="1"/>
       <c r="D695" s="1"/>
       <c r="E695" s="1"/>
@@ -16618,7 +16621,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="696" customHeight="1" ht="18">
       <c r="A696" s="1"/>
-      <c r="B696" s="2"/>
+      <c r="B696" s="7"/>
       <c r="C696" s="1"/>
       <c r="D696" s="1"/>
       <c r="E696" s="1"/>
@@ -16641,7 +16644,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="697" customHeight="1" ht="18">
       <c r="A697" s="1"/>
-      <c r="B697" s="2"/>
+      <c r="B697" s="7"/>
       <c r="C697" s="1"/>
       <c r="D697" s="1"/>
       <c r="E697" s="1"/>
@@ -16664,7 +16667,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="698" customHeight="1" ht="18">
       <c r="A698" s="1"/>
-      <c r="B698" s="2"/>
+      <c r="B698" s="7"/>
       <c r="C698" s="1"/>
       <c r="D698" s="1"/>
       <c r="E698" s="1"/>
@@ -16687,7 +16690,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="699" customHeight="1" ht="18">
       <c r="A699" s="1"/>
-      <c r="B699" s="2"/>
+      <c r="B699" s="7"/>
       <c r="C699" s="1"/>
       <c r="D699" s="1"/>
       <c r="E699" s="1"/>
@@ -16710,7 +16713,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="700" customHeight="1" ht="18">
       <c r="A700" s="1"/>
-      <c r="B700" s="2"/>
+      <c r="B700" s="7"/>
       <c r="C700" s="1"/>
       <c r="D700" s="1"/>
       <c r="E700" s="1"/>
@@ -16733,7 +16736,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="701" customHeight="1" ht="18">
       <c r="A701" s="1"/>
-      <c r="B701" s="2"/>
+      <c r="B701" s="7"/>
       <c r="C701" s="1"/>
       <c r="D701" s="1"/>
       <c r="E701" s="1"/>
@@ -16756,7 +16759,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="702" customHeight="1" ht="18">
       <c r="A702" s="1"/>
-      <c r="B702" s="2"/>
+      <c r="B702" s="7"/>
       <c r="C702" s="1"/>
       <c r="D702" s="1"/>
       <c r="E702" s="1"/>
@@ -16779,7 +16782,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="703" customHeight="1" ht="18">
       <c r="A703" s="1"/>
-      <c r="B703" s="2"/>
+      <c r="B703" s="7"/>
       <c r="C703" s="1"/>
       <c r="D703" s="1"/>
       <c r="E703" s="1"/>
@@ -16802,7 +16805,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="704" customHeight="1" ht="18">
       <c r="A704" s="1"/>
-      <c r="B704" s="2"/>
+      <c r="B704" s="7"/>
       <c r="C704" s="1"/>
       <c r="D704" s="1"/>
       <c r="E704" s="1"/>
@@ -16825,7 +16828,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="705" customHeight="1" ht="18">
       <c r="A705" s="1"/>
-      <c r="B705" s="2"/>
+      <c r="B705" s="7"/>
       <c r="C705" s="1"/>
       <c r="D705" s="1"/>
       <c r="E705" s="1"/>
@@ -16848,7 +16851,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="706" customHeight="1" ht="18">
       <c r="A706" s="1"/>
-      <c r="B706" s="2"/>
+      <c r="B706" s="7"/>
       <c r="C706" s="1"/>
       <c r="D706" s="1"/>
       <c r="E706" s="1"/>
@@ -16871,7 +16874,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="707" customHeight="1" ht="18">
       <c r="A707" s="1"/>
-      <c r="B707" s="2"/>
+      <c r="B707" s="7"/>
       <c r="C707" s="1"/>
       <c r="D707" s="1"/>
       <c r="E707" s="1"/>
@@ -16894,7 +16897,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="708" customHeight="1" ht="18">
       <c r="A708" s="1"/>
-      <c r="B708" s="2"/>
+      <c r="B708" s="7"/>
       <c r="C708" s="1"/>
       <c r="D708" s="1"/>
       <c r="E708" s="1"/>
@@ -16917,7 +16920,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="709" customHeight="1" ht="18">
       <c r="A709" s="1"/>
-      <c r="B709" s="2"/>
+      <c r="B709" s="7"/>
       <c r="C709" s="1"/>
       <c r="D709" s="1"/>
       <c r="E709" s="1"/>
@@ -16940,7 +16943,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="710" customHeight="1" ht="18">
       <c r="A710" s="1"/>
-      <c r="B710" s="2"/>
+      <c r="B710" s="7"/>
       <c r="C710" s="1"/>
       <c r="D710" s="1"/>
       <c r="E710" s="1"/>
@@ -16963,7 +16966,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="711" customHeight="1" ht="18">
       <c r="A711" s="1"/>
-      <c r="B711" s="2"/>
+      <c r="B711" s="7"/>
       <c r="C711" s="1"/>
       <c r="D711" s="1"/>
       <c r="E711" s="1"/>
@@ -16986,7 +16989,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="712" customHeight="1" ht="18">
       <c r="A712" s="1"/>
-      <c r="B712" s="2"/>
+      <c r="B712" s="7"/>
       <c r="C712" s="1"/>
       <c r="D712" s="1"/>
       <c r="E712" s="1"/>
@@ -17009,7 +17012,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="713" customHeight="1" ht="18">
       <c r="A713" s="1"/>
-      <c r="B713" s="2"/>
+      <c r="B713" s="7"/>
       <c r="C713" s="1"/>
       <c r="D713" s="1"/>
       <c r="E713" s="1"/>
@@ -17032,7 +17035,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="714" customHeight="1" ht="18">
       <c r="A714" s="1"/>
-      <c r="B714" s="2"/>
+      <c r="B714" s="7"/>
       <c r="C714" s="1"/>
       <c r="D714" s="1"/>
       <c r="E714" s="1"/>
@@ -17055,7 +17058,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="715" customHeight="1" ht="18">
       <c r="A715" s="1"/>
-      <c r="B715" s="2"/>
+      <c r="B715" s="7"/>
       <c r="C715" s="1"/>
       <c r="D715" s="1"/>
       <c r="E715" s="1"/>
@@ -17078,7 +17081,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="716" customHeight="1" ht="18">
       <c r="A716" s="1"/>
-      <c r="B716" s="2"/>
+      <c r="B716" s="7"/>
       <c r="C716" s="1"/>
       <c r="D716" s="1"/>
       <c r="E716" s="1"/>
@@ -17101,7 +17104,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="717" customHeight="1" ht="18">
       <c r="A717" s="1"/>
-      <c r="B717" s="2"/>
+      <c r="B717" s="7"/>
       <c r="C717" s="1"/>
       <c r="D717" s="1"/>
       <c r="E717" s="1"/>
@@ -17124,7 +17127,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="718" customHeight="1" ht="18">
       <c r="A718" s="1"/>
-      <c r="B718" s="2"/>
+      <c r="B718" s="7"/>
       <c r="C718" s="1"/>
       <c r="D718" s="1"/>
       <c r="E718" s="1"/>
@@ -17147,7 +17150,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="719" customHeight="1" ht="18">
       <c r="A719" s="1"/>
-      <c r="B719" s="2"/>
+      <c r="B719" s="7"/>
       <c r="C719" s="1"/>
       <c r="D719" s="1"/>
       <c r="E719" s="1"/>
@@ -17170,7 +17173,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="720" customHeight="1" ht="18">
       <c r="A720" s="1"/>
-      <c r="B720" s="2"/>
+      <c r="B720" s="7"/>
       <c r="C720" s="1"/>
       <c r="D720" s="1"/>
       <c r="E720" s="1"/>
@@ -17193,7 +17196,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="721" customHeight="1" ht="18">
       <c r="A721" s="1"/>
-      <c r="B721" s="2"/>
+      <c r="B721" s="7"/>
       <c r="C721" s="1"/>
       <c r="D721" s="1"/>
       <c r="E721" s="1"/>
@@ -17216,7 +17219,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="722" customHeight="1" ht="18">
       <c r="A722" s="1"/>
-      <c r="B722" s="2"/>
+      <c r="B722" s="7"/>
       <c r="C722" s="1"/>
       <c r="D722" s="1"/>
       <c r="E722" s="1"/>
@@ -17239,7 +17242,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="723" customHeight="1" ht="18">
       <c r="A723" s="1"/>
-      <c r="B723" s="2"/>
+      <c r="B723" s="7"/>
       <c r="C723" s="1"/>
       <c r="D723" s="1"/>
       <c r="E723" s="1"/>
@@ -17262,7 +17265,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="724" customHeight="1" ht="18">
       <c r="A724" s="1"/>
-      <c r="B724" s="2"/>
+      <c r="B724" s="7"/>
       <c r="C724" s="1"/>
       <c r="D724" s="1"/>
       <c r="E724" s="1"/>
@@ -17285,7 +17288,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="725" customHeight="1" ht="18">
       <c r="A725" s="1"/>
-      <c r="B725" s="2"/>
+      <c r="B725" s="7"/>
       <c r="C725" s="1"/>
       <c r="D725" s="1"/>
       <c r="E725" s="1"/>
@@ -17308,7 +17311,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="726" customHeight="1" ht="18">
       <c r="A726" s="1"/>
-      <c r="B726" s="2"/>
+      <c r="B726" s="7"/>
       <c r="C726" s="1"/>
       <c r="D726" s="1"/>
       <c r="E726" s="1"/>
@@ -17331,7 +17334,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="727" customHeight="1" ht="18">
       <c r="A727" s="1"/>
-      <c r="B727" s="2"/>
+      <c r="B727" s="7"/>
       <c r="C727" s="1"/>
       <c r="D727" s="1"/>
       <c r="E727" s="1"/>
@@ -17354,7 +17357,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="728" customHeight="1" ht="18">
       <c r="A728" s="1"/>
-      <c r="B728" s="2"/>
+      <c r="B728" s="7"/>
       <c r="C728" s="1"/>
       <c r="D728" s="1"/>
       <c r="E728" s="1"/>
@@ -17377,7 +17380,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="729" customHeight="1" ht="18">
       <c r="A729" s="1"/>
-      <c r="B729" s="2"/>
+      <c r="B729" s="7"/>
       <c r="C729" s="1"/>
       <c r="D729" s="1"/>
       <c r="E729" s="1"/>
@@ -17400,7 +17403,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="730" customHeight="1" ht="18">
       <c r="A730" s="1"/>
-      <c r="B730" s="2"/>
+      <c r="B730" s="7"/>
       <c r="C730" s="1"/>
       <c r="D730" s="1"/>
       <c r="E730" s="1"/>
@@ -17423,7 +17426,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="731" customHeight="1" ht="18">
       <c r="A731" s="1"/>
-      <c r="B731" s="2"/>
+      <c r="B731" s="7"/>
       <c r="C731" s="1"/>
       <c r="D731" s="1"/>
       <c r="E731" s="1"/>
@@ -17446,7 +17449,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="732" customHeight="1" ht="18">
       <c r="A732" s="1"/>
-      <c r="B732" s="2"/>
+      <c r="B732" s="7"/>
       <c r="C732" s="1"/>
       <c r="D732" s="1"/>
       <c r="E732" s="1"/>
@@ -17469,7 +17472,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="733" customHeight="1" ht="18">
       <c r="A733" s="1"/>
-      <c r="B733" s="2"/>
+      <c r="B733" s="7"/>
       <c r="C733" s="1"/>
       <c r="D733" s="1"/>
       <c r="E733" s="1"/>
@@ -17492,7 +17495,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="734" customHeight="1" ht="18">
       <c r="A734" s="1"/>
-      <c r="B734" s="2"/>
+      <c r="B734" s="7"/>
       <c r="C734" s="1"/>
       <c r="D734" s="1"/>
       <c r="E734" s="1"/>
@@ -17515,7 +17518,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="735" customHeight="1" ht="18">
       <c r="A735" s="1"/>
-      <c r="B735" s="2"/>
+      <c r="B735" s="7"/>
       <c r="C735" s="1"/>
       <c r="D735" s="1"/>
       <c r="E735" s="1"/>
@@ -17538,7 +17541,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="736" customHeight="1" ht="18">
       <c r="A736" s="1"/>
-      <c r="B736" s="2"/>
+      <c r="B736" s="7"/>
       <c r="C736" s="1"/>
       <c r="D736" s="1"/>
       <c r="E736" s="1"/>
@@ -17561,7 +17564,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="737" customHeight="1" ht="18">
       <c r="A737" s="1"/>
-      <c r="B737" s="2"/>
+      <c r="B737" s="7"/>
       <c r="C737" s="1"/>
       <c r="D737" s="1"/>
       <c r="E737" s="1"/>
@@ -17584,7 +17587,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="738" customHeight="1" ht="18">
       <c r="A738" s="1"/>
-      <c r="B738" s="2"/>
+      <c r="B738" s="7"/>
       <c r="C738" s="1"/>
       <c r="D738" s="1"/>
       <c r="E738" s="1"/>
@@ -17607,7 +17610,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="739" customHeight="1" ht="18">
       <c r="A739" s="1"/>
-      <c r="B739" s="2"/>
+      <c r="B739" s="7"/>
       <c r="C739" s="1"/>
       <c r="D739" s="1"/>
       <c r="E739" s="1"/>
@@ -17630,7 +17633,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="740" customHeight="1" ht="18">
       <c r="A740" s="1"/>
-      <c r="B740" s="2"/>
+      <c r="B740" s="7"/>
       <c r="C740" s="1"/>
       <c r="D740" s="1"/>
       <c r="E740" s="1"/>
@@ -17653,7 +17656,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="741" customHeight="1" ht="18">
       <c r="A741" s="1"/>
-      <c r="B741" s="2"/>
+      <c r="B741" s="7"/>
       <c r="C741" s="1"/>
       <c r="D741" s="1"/>
       <c r="E741" s="1"/>
@@ -17676,7 +17679,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="742" customHeight="1" ht="18">
       <c r="A742" s="1"/>
-      <c r="B742" s="2"/>
+      <c r="B742" s="7"/>
       <c r="C742" s="1"/>
       <c r="D742" s="1"/>
       <c r="E742" s="1"/>
@@ -17699,7 +17702,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="743" customHeight="1" ht="18">
       <c r="A743" s="1"/>
-      <c r="B743" s="2"/>
+      <c r="B743" s="7"/>
       <c r="C743" s="1"/>
       <c r="D743" s="1"/>
       <c r="E743" s="1"/>
@@ -17722,7 +17725,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="744" customHeight="1" ht="18">
       <c r="A744" s="1"/>
-      <c r="B744" s="2"/>
+      <c r="B744" s="7"/>
       <c r="C744" s="1"/>
       <c r="D744" s="1"/>
       <c r="E744" s="1"/>
@@ -17745,7 +17748,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="745" customHeight="1" ht="18">
       <c r="A745" s="1"/>
-      <c r="B745" s="2"/>
+      <c r="B745" s="7"/>
       <c r="C745" s="1"/>
       <c r="D745" s="1"/>
       <c r="E745" s="1"/>
@@ -17768,7 +17771,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="746" customHeight="1" ht="18">
       <c r="A746" s="1"/>
-      <c r="B746" s="2"/>
+      <c r="B746" s="7"/>
       <c r="C746" s="1"/>
       <c r="D746" s="1"/>
       <c r="E746" s="1"/>
@@ -17791,7 +17794,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="747" customHeight="1" ht="18">
       <c r="A747" s="1"/>
-      <c r="B747" s="2"/>
+      <c r="B747" s="7"/>
       <c r="C747" s="1"/>
       <c r="D747" s="1"/>
       <c r="E747" s="1"/>
@@ -17814,7 +17817,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="748" customHeight="1" ht="18">
       <c r="A748" s="1"/>
-      <c r="B748" s="2"/>
+      <c r="B748" s="7"/>
       <c r="C748" s="1"/>
       <c r="D748" s="1"/>
       <c r="E748" s="1"/>
@@ -17837,7 +17840,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="749" customHeight="1" ht="18">
       <c r="A749" s="1"/>
-      <c r="B749" s="2"/>
+      <c r="B749" s="7"/>
       <c r="C749" s="1"/>
       <c r="D749" s="1"/>
       <c r="E749" s="1"/>
@@ -17860,7 +17863,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="750" customHeight="1" ht="18">
       <c r="A750" s="1"/>
-      <c r="B750" s="2"/>
+      <c r="B750" s="7"/>
       <c r="C750" s="1"/>
       <c r="D750" s="1"/>
       <c r="E750" s="1"/>
@@ -17883,7 +17886,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="751" customHeight="1" ht="18">
       <c r="A751" s="1"/>
-      <c r="B751" s="2"/>
+      <c r="B751" s="7"/>
       <c r="C751" s="1"/>
       <c r="D751" s="1"/>
       <c r="E751" s="1"/>
@@ -17906,7 +17909,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="752" customHeight="1" ht="18">
       <c r="A752" s="1"/>
-      <c r="B752" s="2"/>
+      <c r="B752" s="7"/>
       <c r="C752" s="1"/>
       <c r="D752" s="1"/>
       <c r="E752" s="1"/>
@@ -17929,7 +17932,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="753" customHeight="1" ht="18">
       <c r="A753" s="1"/>
-      <c r="B753" s="2"/>
+      <c r="B753" s="7"/>
       <c r="C753" s="1"/>
       <c r="D753" s="1"/>
       <c r="E753" s="1"/>
@@ -17952,7 +17955,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="754" customHeight="1" ht="18">
       <c r="A754" s="1"/>
-      <c r="B754" s="2"/>
+      <c r="B754" s="7"/>
       <c r="C754" s="1"/>
       <c r="D754" s="1"/>
       <c r="E754" s="1"/>
@@ -17975,7 +17978,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="755" customHeight="1" ht="18">
       <c r="A755" s="1"/>
-      <c r="B755" s="2"/>
+      <c r="B755" s="7"/>
       <c r="C755" s="1"/>
       <c r="D755" s="1"/>
       <c r="E755" s="1"/>
@@ -17998,7 +18001,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="756" customHeight="1" ht="18">
       <c r="A756" s="1"/>
-      <c r="B756" s="2"/>
+      <c r="B756" s="7"/>
       <c r="C756" s="1"/>
       <c r="D756" s="1"/>
       <c r="E756" s="1"/>
@@ -18021,7 +18024,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="757" customHeight="1" ht="18">
       <c r="A757" s="1"/>
-      <c r="B757" s="2"/>
+      <c r="B757" s="7"/>
       <c r="C757" s="1"/>
       <c r="D757" s="1"/>
       <c r="E757" s="1"/>
@@ -18044,7 +18047,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="758" customHeight="1" ht="18">
       <c r="A758" s="1"/>
-      <c r="B758" s="2"/>
+      <c r="B758" s="7"/>
       <c r="C758" s="1"/>
       <c r="D758" s="1"/>
       <c r="E758" s="1"/>
@@ -18067,7 +18070,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="759" customHeight="1" ht="18">
       <c r="A759" s="1"/>
-      <c r="B759" s="2"/>
+      <c r="B759" s="7"/>
       <c r="C759" s="1"/>
       <c r="D759" s="1"/>
       <c r="E759" s="1"/>
@@ -18090,7 +18093,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="760" customHeight="1" ht="18">
       <c r="A760" s="1"/>
-      <c r="B760" s="2"/>
+      <c r="B760" s="7"/>
       <c r="C760" s="1"/>
       <c r="D760" s="1"/>
       <c r="E760" s="1"/>
@@ -18113,7 +18116,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="761" customHeight="1" ht="18">
       <c r="A761" s="1"/>
-      <c r="B761" s="2"/>
+      <c r="B761" s="7"/>
       <c r="C761" s="1"/>
       <c r="D761" s="1"/>
       <c r="E761" s="1"/>
@@ -18136,7 +18139,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="762" customHeight="1" ht="18">
       <c r="A762" s="1"/>
-      <c r="B762" s="2"/>
+      <c r="B762" s="7"/>
       <c r="C762" s="1"/>
       <c r="D762" s="1"/>
       <c r="E762" s="1"/>
@@ -18159,7 +18162,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="763" customHeight="1" ht="18">
       <c r="A763" s="1"/>
-      <c r="B763" s="2"/>
+      <c r="B763" s="7"/>
       <c r="C763" s="1"/>
       <c r="D763" s="1"/>
       <c r="E763" s="1"/>
@@ -18182,7 +18185,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="764" customHeight="1" ht="18">
       <c r="A764" s="1"/>
-      <c r="B764" s="2"/>
+      <c r="B764" s="7"/>
       <c r="C764" s="1"/>
       <c r="D764" s="1"/>
       <c r="E764" s="1"/>
@@ -18205,7 +18208,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="765" customHeight="1" ht="18">
       <c r="A765" s="1"/>
-      <c r="B765" s="2"/>
+      <c r="B765" s="7"/>
       <c r="C765" s="1"/>
       <c r="D765" s="1"/>
       <c r="E765" s="1"/>
@@ -18228,7 +18231,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="766" customHeight="1" ht="18">
       <c r="A766" s="1"/>
-      <c r="B766" s="2"/>
+      <c r="B766" s="7"/>
       <c r="C766" s="1"/>
       <c r="D766" s="1"/>
       <c r="E766" s="1"/>
@@ -18251,7 +18254,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="767" customHeight="1" ht="18">
       <c r="A767" s="1"/>
-      <c r="B767" s="2"/>
+      <c r="B767" s="7"/>
       <c r="C767" s="1"/>
       <c r="D767" s="1"/>
       <c r="E767" s="1"/>
@@ -18274,7 +18277,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="768" customHeight="1" ht="18">
       <c r="A768" s="1"/>
-      <c r="B768" s="2"/>
+      <c r="B768" s="7"/>
       <c r="C768" s="1"/>
       <c r="D768" s="1"/>
       <c r="E768" s="1"/>
@@ -18297,7 +18300,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="769" customHeight="1" ht="18">
       <c r="A769" s="1"/>
-      <c r="B769" s="2"/>
+      <c r="B769" s="7"/>
       <c r="C769" s="1"/>
       <c r="D769" s="1"/>
       <c r="E769" s="1"/>
@@ -18320,7 +18323,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="770" customHeight="1" ht="18">
       <c r="A770" s="1"/>
-      <c r="B770" s="2"/>
+      <c r="B770" s="7"/>
       <c r="C770" s="1"/>
       <c r="D770" s="1"/>
       <c r="E770" s="1"/>
@@ -18343,7 +18346,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="771" customHeight="1" ht="18">
       <c r="A771" s="1"/>
-      <c r="B771" s="2"/>
+      <c r="B771" s="7"/>
       <c r="C771" s="1"/>
       <c r="D771" s="1"/>
       <c r="E771" s="1"/>
@@ -18366,7 +18369,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="772" customHeight="1" ht="18">
       <c r="A772" s="1"/>
-      <c r="B772" s="2"/>
+      <c r="B772" s="7"/>
       <c r="C772" s="1"/>
       <c r="D772" s="1"/>
       <c r="E772" s="1"/>
@@ -18389,7 +18392,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="773" customHeight="1" ht="18">
       <c r="A773" s="1"/>
-      <c r="B773" s="2"/>
+      <c r="B773" s="7"/>
       <c r="C773" s="1"/>
       <c r="D773" s="1"/>
       <c r="E773" s="1"/>
@@ -18412,7 +18415,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="774" customHeight="1" ht="18">
       <c r="A774" s="1"/>
-      <c r="B774" s="2"/>
+      <c r="B774" s="7"/>
       <c r="C774" s="1"/>
       <c r="D774" s="1"/>
       <c r="E774" s="1"/>
@@ -18435,7 +18438,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="775" customHeight="1" ht="18">
       <c r="A775" s="1"/>
-      <c r="B775" s="2"/>
+      <c r="B775" s="7"/>
       <c r="C775" s="1"/>
       <c r="D775" s="1"/>
       <c r="E775" s="1"/>
@@ -18458,7 +18461,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="776" customHeight="1" ht="18">
       <c r="A776" s="1"/>
-      <c r="B776" s="2"/>
+      <c r="B776" s="7"/>
       <c r="C776" s="1"/>
       <c r="D776" s="1"/>
       <c r="E776" s="1"/>
@@ -18481,7 +18484,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="777" customHeight="1" ht="18">
       <c r="A777" s="1"/>
-      <c r="B777" s="2"/>
+      <c r="B777" s="7"/>
       <c r="C777" s="1"/>
       <c r="D777" s="1"/>
       <c r="E777" s="1"/>
@@ -18504,7 +18507,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="778" customHeight="1" ht="18">
       <c r="A778" s="1"/>
-      <c r="B778" s="2"/>
+      <c r="B778" s="7"/>
       <c r="C778" s="1"/>
       <c r="D778" s="1"/>
       <c r="E778" s="1"/>
@@ -18527,7 +18530,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="779" customHeight="1" ht="18">
       <c r="A779" s="1"/>
-      <c r="B779" s="2"/>
+      <c r="B779" s="7"/>
       <c r="C779" s="1"/>
       <c r="D779" s="1"/>
       <c r="E779" s="1"/>
@@ -18550,7 +18553,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="780" customHeight="1" ht="18">
       <c r="A780" s="1"/>
-      <c r="B780" s="2"/>
+      <c r="B780" s="7"/>
       <c r="C780" s="1"/>
       <c r="D780" s="1"/>
       <c r="E780" s="1"/>
@@ -18573,7 +18576,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="781" customHeight="1" ht="18">
       <c r="A781" s="1"/>
-      <c r="B781" s="2"/>
+      <c r="B781" s="7"/>
       <c r="C781" s="1"/>
       <c r="D781" s="1"/>
       <c r="E781" s="1"/>
@@ -18596,7 +18599,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="782" customHeight="1" ht="18">
       <c r="A782" s="1"/>
-      <c r="B782" s="2"/>
+      <c r="B782" s="7"/>
       <c r="C782" s="1"/>
       <c r="D782" s="1"/>
       <c r="E782" s="1"/>
@@ -18619,7 +18622,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="783" customHeight="1" ht="18">
       <c r="A783" s="1"/>
-      <c r="B783" s="2"/>
+      <c r="B783" s="7"/>
       <c r="C783" s="1"/>
       <c r="D783" s="1"/>
       <c r="E783" s="1"/>
@@ -18642,7 +18645,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="784" customHeight="1" ht="18">
       <c r="A784" s="1"/>
-      <c r="B784" s="2"/>
+      <c r="B784" s="7"/>
       <c r="C784" s="1"/>
       <c r="D784" s="1"/>
       <c r="E784" s="1"/>
@@ -18665,7 +18668,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="785" customHeight="1" ht="18">
       <c r="A785" s="1"/>
-      <c r="B785" s="2"/>
+      <c r="B785" s="7"/>
       <c r="C785" s="1"/>
       <c r="D785" s="1"/>
       <c r="E785" s="1"/>
@@ -18688,7 +18691,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="786" customHeight="1" ht="18">
       <c r="A786" s="1"/>
-      <c r="B786" s="2"/>
+      <c r="B786" s="7"/>
       <c r="C786" s="1"/>
       <c r="D786" s="1"/>
       <c r="E786" s="1"/>
@@ -18711,7 +18714,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="787" customHeight="1" ht="18">
       <c r="A787" s="1"/>
-      <c r="B787" s="2"/>
+      <c r="B787" s="7"/>
       <c r="C787" s="1"/>
       <c r="D787" s="1"/>
       <c r="E787" s="1"/>
@@ -18734,7 +18737,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="788" customHeight="1" ht="18">
       <c r="A788" s="1"/>
-      <c r="B788" s="2"/>
+      <c r="B788" s="7"/>
       <c r="C788" s="1"/>
       <c r="D788" s="1"/>
       <c r="E788" s="1"/>
@@ -18757,7 +18760,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="789" customHeight="1" ht="18">
       <c r="A789" s="1"/>
-      <c r="B789" s="2"/>
+      <c r="B789" s="7"/>
       <c r="C789" s="1"/>
       <c r="D789" s="1"/>
       <c r="E789" s="1"/>
@@ -18780,7 +18783,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="790" customHeight="1" ht="18">
       <c r="A790" s="1"/>
-      <c r="B790" s="2"/>
+      <c r="B790" s="7"/>
       <c r="C790" s="1"/>
       <c r="D790" s="1"/>
       <c r="E790" s="1"/>
@@ -18803,7 +18806,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="791" customHeight="1" ht="18">
       <c r="A791" s="1"/>
-      <c r="B791" s="2"/>
+      <c r="B791" s="7"/>
       <c r="C791" s="1"/>
       <c r="D791" s="1"/>
       <c r="E791" s="1"/>
@@ -18826,7 +18829,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="792" customHeight="1" ht="18">
       <c r="A792" s="1"/>
-      <c r="B792" s="2"/>
+      <c r="B792" s="7"/>
       <c r="C792" s="1"/>
       <c r="D792" s="1"/>
       <c r="E792" s="1"/>
@@ -18849,7 +18852,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="793" customHeight="1" ht="18">
       <c r="A793" s="1"/>
-      <c r="B793" s="2"/>
+      <c r="B793" s="7"/>
       <c r="C793" s="1"/>
       <c r="D793" s="1"/>
       <c r="E793" s="1"/>
@@ -18872,7 +18875,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="794" customHeight="1" ht="18">
       <c r="A794" s="1"/>
-      <c r="B794" s="2"/>
+      <c r="B794" s="7"/>
       <c r="C794" s="1"/>
       <c r="D794" s="1"/>
       <c r="E794" s="1"/>
@@ -18895,7 +18898,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="795" customHeight="1" ht="18">
       <c r="A795" s="1"/>
-      <c r="B795" s="2"/>
+      <c r="B795" s="7"/>
       <c r="C795" s="1"/>
       <c r="D795" s="1"/>
       <c r="E795" s="1"/>
@@ -18918,7 +18921,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="796" customHeight="1" ht="18">
       <c r="A796" s="1"/>
-      <c r="B796" s="2"/>
+      <c r="B796" s="7"/>
       <c r="C796" s="1"/>
       <c r="D796" s="1"/>
       <c r="E796" s="1"/>
@@ -18941,7 +18944,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="797" customHeight="1" ht="18">
       <c r="A797" s="1"/>
-      <c r="B797" s="2"/>
+      <c r="B797" s="7"/>
       <c r="C797" s="1"/>
       <c r="D797" s="1"/>
       <c r="E797" s="1"/>
@@ -18964,7 +18967,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="798" customHeight="1" ht="18">
       <c r="A798" s="1"/>
-      <c r="B798" s="2"/>
+      <c r="B798" s="7"/>
       <c r="C798" s="1"/>
       <c r="D798" s="1"/>
       <c r="E798" s="1"/>
@@ -18987,7 +18990,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="799" customHeight="1" ht="18">
       <c r="A799" s="1"/>
-      <c r="B799" s="2"/>
+      <c r="B799" s="7"/>
       <c r="C799" s="1"/>
       <c r="D799" s="1"/>
       <c r="E799" s="1"/>
@@ -19010,7 +19013,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="800" customHeight="1" ht="18">
       <c r="A800" s="1"/>
-      <c r="B800" s="2"/>
+      <c r="B800" s="7"/>
       <c r="C800" s="1"/>
       <c r="D800" s="1"/>
       <c r="E800" s="1"/>
@@ -19033,7 +19036,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="801" customHeight="1" ht="18">
       <c r="A801" s="1"/>
-      <c r="B801" s="2"/>
+      <c r="B801" s="7"/>
       <c r="C801" s="1"/>
       <c r="D801" s="1"/>
       <c r="E801" s="1"/>
@@ -19056,7 +19059,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="802" customHeight="1" ht="18">
       <c r="A802" s="1"/>
-      <c r="B802" s="2"/>
+      <c r="B802" s="7"/>
       <c r="C802" s="1"/>
       <c r="D802" s="1"/>
       <c r="E802" s="1"/>
@@ -19079,7 +19082,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="803" customHeight="1" ht="18">
       <c r="A803" s="1"/>
-      <c r="B803" s="2"/>
+      <c r="B803" s="7"/>
       <c r="C803" s="1"/>
       <c r="D803" s="1"/>
       <c r="E803" s="1"/>
@@ -19102,7 +19105,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="804" customHeight="1" ht="18">
       <c r="A804" s="1"/>
-      <c r="B804" s="2"/>
+      <c r="B804" s="7"/>
       <c r="C804" s="1"/>
       <c r="D804" s="1"/>
       <c r="E804" s="1"/>
@@ -19125,7 +19128,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="805" customHeight="1" ht="18">
       <c r="A805" s="1"/>
-      <c r="B805" s="2"/>
+      <c r="B805" s="7"/>
       <c r="C805" s="1"/>
       <c r="D805" s="1"/>
       <c r="E805" s="1"/>
@@ -19148,7 +19151,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="806" customHeight="1" ht="18">
       <c r="A806" s="1"/>
-      <c r="B806" s="2"/>
+      <c r="B806" s="7"/>
       <c r="C806" s="1"/>
       <c r="D806" s="1"/>
       <c r="E806" s="1"/>
@@ -19171,7 +19174,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="807" customHeight="1" ht="18">
       <c r="A807" s="1"/>
-      <c r="B807" s="2"/>
+      <c r="B807" s="7"/>
       <c r="C807" s="1"/>
       <c r="D807" s="1"/>
       <c r="E807" s="1"/>
@@ -19194,7 +19197,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="808" customHeight="1" ht="18">
       <c r="A808" s="1"/>
-      <c r="B808" s="2"/>
+      <c r="B808" s="7"/>
       <c r="C808" s="1"/>
       <c r="D808" s="1"/>
       <c r="E808" s="1"/>
@@ -19217,7 +19220,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="809" customHeight="1" ht="18">
       <c r="A809" s="1"/>
-      <c r="B809" s="2"/>
+      <c r="B809" s="7"/>
       <c r="C809" s="1"/>
       <c r="D809" s="1"/>
       <c r="E809" s="1"/>
@@ -19240,7 +19243,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="810" customHeight="1" ht="18">
       <c r="A810" s="1"/>
-      <c r="B810" s="2"/>
+      <c r="B810" s="7"/>
       <c r="C810" s="1"/>
       <c r="D810" s="1"/>
       <c r="E810" s="1"/>
@@ -19263,7 +19266,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="811" customHeight="1" ht="18">
       <c r="A811" s="1"/>
-      <c r="B811" s="2"/>
+      <c r="B811" s="7"/>
       <c r="C811" s="1"/>
       <c r="D811" s="1"/>
       <c r="E811" s="1"/>
@@ -19286,7 +19289,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="812" customHeight="1" ht="18">
       <c r="A812" s="1"/>
-      <c r="B812" s="2"/>
+      <c r="B812" s="7"/>
       <c r="C812" s="1"/>
       <c r="D812" s="1"/>
       <c r="E812" s="1"/>
@@ -19309,7 +19312,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="813" customHeight="1" ht="18">
       <c r="A813" s="1"/>
-      <c r="B813" s="2"/>
+      <c r="B813" s="7"/>
       <c r="C813" s="1"/>
       <c r="D813" s="1"/>
       <c r="E813" s="1"/>
@@ -19332,7 +19335,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="814" customHeight="1" ht="18">
       <c r="A814" s="1"/>
-      <c r="B814" s="2"/>
+      <c r="B814" s="7"/>
       <c r="C814" s="1"/>
       <c r="D814" s="1"/>
       <c r="E814" s="1"/>
@@ -19355,7 +19358,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="815" customHeight="1" ht="18">
       <c r="A815" s="1"/>
-      <c r="B815" s="2"/>
+      <c r="B815" s="7"/>
       <c r="C815" s="1"/>
       <c r="D815" s="1"/>
       <c r="E815" s="1"/>
@@ -19378,7 +19381,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="816" customHeight="1" ht="18">
       <c r="A816" s="1"/>
-      <c r="B816" s="2"/>
+      <c r="B816" s="7"/>
       <c r="C816" s="1"/>
       <c r="D816" s="1"/>
       <c r="E816" s="1"/>
@@ -19401,7 +19404,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="817" customHeight="1" ht="18">
       <c r="A817" s="1"/>
-      <c r="B817" s="2"/>
+      <c r="B817" s="7"/>
       <c r="C817" s="1"/>
       <c r="D817" s="1"/>
       <c r="E817" s="1"/>
@@ -19424,7 +19427,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="818" customHeight="1" ht="18">
       <c r="A818" s="1"/>
-      <c r="B818" s="2"/>
+      <c r="B818" s="7"/>
       <c r="C818" s="1"/>
       <c r="D818" s="1"/>
       <c r="E818" s="1"/>
@@ -19447,7 +19450,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="819" customHeight="1" ht="18">
       <c r="A819" s="1"/>
-      <c r="B819" s="2"/>
+      <c r="B819" s="7"/>
       <c r="C819" s="1"/>
       <c r="D819" s="1"/>
       <c r="E819" s="1"/>
@@ -19470,7 +19473,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="820" customHeight="1" ht="18">
       <c r="A820" s="1"/>
-      <c r="B820" s="2"/>
+      <c r="B820" s="7"/>
       <c r="C820" s="1"/>
       <c r="D820" s="1"/>
       <c r="E820" s="1"/>
@@ -19493,7 +19496,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="821" customHeight="1" ht="18">
       <c r="A821" s="1"/>
-      <c r="B821" s="2"/>
+      <c r="B821" s="7"/>
       <c r="C821" s="1"/>
       <c r="D821" s="1"/>
       <c r="E821" s="1"/>
@@ -19516,7 +19519,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="822" customHeight="1" ht="18">
       <c r="A822" s="1"/>
-      <c r="B822" s="2"/>
+      <c r="B822" s="7"/>
       <c r="C822" s="1"/>
       <c r="D822" s="1"/>
       <c r="E822" s="1"/>
@@ -19539,7 +19542,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="823" customHeight="1" ht="18">
       <c r="A823" s="1"/>
-      <c r="B823" s="2"/>
+      <c r="B823" s="7"/>
       <c r="C823" s="1"/>
       <c r="D823" s="1"/>
       <c r="E823" s="1"/>
@@ -19562,7 +19565,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="824" customHeight="1" ht="18">
       <c r="A824" s="1"/>
-      <c r="B824" s="2"/>
+      <c r="B824" s="7"/>
       <c r="C824" s="1"/>
       <c r="D824" s="1"/>
       <c r="E824" s="1"/>
@@ -19585,7 +19588,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="825" customHeight="1" ht="18">
       <c r="A825" s="1"/>
-      <c r="B825" s="2"/>
+      <c r="B825" s="7"/>
       <c r="C825" s="1"/>
       <c r="D825" s="1"/>
       <c r="E825" s="1"/>
@@ -19608,7 +19611,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="826" customHeight="1" ht="18">
       <c r="A826" s="1"/>
-      <c r="B826" s="2"/>
+      <c r="B826" s="7"/>
       <c r="C826" s="1"/>
       <c r="D826" s="1"/>
       <c r="E826" s="1"/>
@@ -19631,7 +19634,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="827" customHeight="1" ht="18">
       <c r="A827" s="1"/>
-      <c r="B827" s="2"/>
+      <c r="B827" s="7"/>
       <c r="C827" s="1"/>
       <c r="D827" s="1"/>
       <c r="E827" s="1"/>
@@ -19654,7 +19657,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="828" customHeight="1" ht="18">
       <c r="A828" s="1"/>
-      <c r="B828" s="2"/>
+      <c r="B828" s="7"/>
       <c r="C828" s="1"/>
       <c r="D828" s="1"/>
       <c r="E828" s="1"/>
@@ -19677,7 +19680,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="829" customHeight="1" ht="18">
       <c r="A829" s="1"/>
-      <c r="B829" s="2"/>
+      <c r="B829" s="7"/>
       <c r="C829" s="1"/>
       <c r="D829" s="1"/>
       <c r="E829" s="1"/>
@@ -19700,7 +19703,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="830" customHeight="1" ht="18">
       <c r="A830" s="1"/>
-      <c r="B830" s="2"/>
+      <c r="B830" s="7"/>
       <c r="C830" s="1"/>
       <c r="D830" s="1"/>
       <c r="E830" s="1"/>
@@ -19723,7 +19726,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="831" customHeight="1" ht="18">
       <c r="A831" s="1"/>
-      <c r="B831" s="2"/>
+      <c r="B831" s="7"/>
       <c r="C831" s="1"/>
       <c r="D831" s="1"/>
       <c r="E831" s="1"/>
@@ -19746,7 +19749,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="832" customHeight="1" ht="18">
       <c r="A832" s="1"/>
-      <c r="B832" s="2"/>
+      <c r="B832" s="7"/>
       <c r="C832" s="1"/>
       <c r="D832" s="1"/>
       <c r="E832" s="1"/>
@@ -19769,7 +19772,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="833" customHeight="1" ht="18">
       <c r="A833" s="1"/>
-      <c r="B833" s="2"/>
+      <c r="B833" s="7"/>
       <c r="C833" s="1"/>
       <c r="D833" s="1"/>
       <c r="E833" s="1"/>
@@ -19792,7 +19795,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="834" customHeight="1" ht="18">
       <c r="A834" s="1"/>
-      <c r="B834" s="2"/>
+      <c r="B834" s="7"/>
       <c r="C834" s="1"/>
       <c r="D834" s="1"/>
       <c r="E834" s="1"/>
@@ -19815,7 +19818,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="835" customHeight="1" ht="18">
       <c r="A835" s="1"/>
-      <c r="B835" s="2"/>
+      <c r="B835" s="7"/>
       <c r="C835" s="1"/>
       <c r="D835" s="1"/>
       <c r="E835" s="1"/>
@@ -19838,7 +19841,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="836" customHeight="1" ht="18">
       <c r="A836" s="1"/>
-      <c r="B836" s="2"/>
+      <c r="B836" s="7"/>
       <c r="C836" s="1"/>
       <c r="D836" s="1"/>
       <c r="E836" s="1"/>
@@ -19861,7 +19864,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="837" customHeight="1" ht="18">
       <c r="A837" s="1"/>
-      <c r="B837" s="2"/>
+      <c r="B837" s="7"/>
       <c r="C837" s="1"/>
       <c r="D837" s="1"/>
       <c r="E837" s="1"/>
@@ -19884,7 +19887,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="838" customHeight="1" ht="18">
       <c r="A838" s="1"/>
-      <c r="B838" s="2"/>
+      <c r="B838" s="7"/>
       <c r="C838" s="1"/>
       <c r="D838" s="1"/>
       <c r="E838" s="1"/>
@@ -19907,7 +19910,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="839" customHeight="1" ht="18">
       <c r="A839" s="1"/>
-      <c r="B839" s="2"/>
+      <c r="B839" s="7"/>
       <c r="C839" s="1"/>
       <c r="D839" s="1"/>
       <c r="E839" s="1"/>
@@ -19930,7 +19933,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="840" customHeight="1" ht="18">
       <c r="A840" s="1"/>
-      <c r="B840" s="2"/>
+      <c r="B840" s="7"/>
       <c r="C840" s="1"/>
       <c r="D840" s="1"/>
       <c r="E840" s="1"/>
@@ -19953,7 +19956,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="841" customHeight="1" ht="18">
       <c r="A841" s="1"/>
-      <c r="B841" s="2"/>
+      <c r="B841" s="7"/>
       <c r="C841" s="1"/>
       <c r="D841" s="1"/>
       <c r="E841" s="1"/>
@@ -19976,7 +19979,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="842" customHeight="1" ht="18">
       <c r="A842" s="1"/>
-      <c r="B842" s="2"/>
+      <c r="B842" s="7"/>
       <c r="C842" s="1"/>
       <c r="D842" s="1"/>
       <c r="E842" s="1"/>
@@ -19999,7 +20002,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="843" customHeight="1" ht="18">
       <c r="A843" s="1"/>
-      <c r="B843" s="2"/>
+      <c r="B843" s="7"/>
       <c r="C843" s="1"/>
       <c r="D843" s="1"/>
       <c r="E843" s="1"/>
@@ -20022,7 +20025,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="844" customHeight="1" ht="18">
       <c r="A844" s="1"/>
-      <c r="B844" s="2"/>
+      <c r="B844" s="7"/>
       <c r="C844" s="1"/>
       <c r="D844" s="1"/>
       <c r="E844" s="1"/>
@@ -20045,7 +20048,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="845" customHeight="1" ht="18">
       <c r="A845" s="1"/>
-      <c r="B845" s="2"/>
+      <c r="B845" s="7"/>
       <c r="C845" s="1"/>
       <c r="D845" s="1"/>
       <c r="E845" s="1"/>
@@ -20068,7 +20071,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="846" customHeight="1" ht="18">
       <c r="A846" s="1"/>
-      <c r="B846" s="2"/>
+      <c r="B846" s="7"/>
       <c r="C846" s="1"/>
       <c r="D846" s="1"/>
       <c r="E846" s="1"/>
@@ -20091,7 +20094,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="847" customHeight="1" ht="18">
       <c r="A847" s="1"/>
-      <c r="B847" s="2"/>
+      <c r="B847" s="7"/>
       <c r="C847" s="1"/>
       <c r="D847" s="1"/>
       <c r="E847" s="1"/>
@@ -20114,7 +20117,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="848" customHeight="1" ht="18">
       <c r="A848" s="1"/>
-      <c r="B848" s="2"/>
+      <c r="B848" s="7"/>
       <c r="C848" s="1"/>
       <c r="D848" s="1"/>
       <c r="E848" s="1"/>
@@ -20137,7 +20140,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="849" customHeight="1" ht="18">
       <c r="A849" s="1"/>
-      <c r="B849" s="2"/>
+      <c r="B849" s="7"/>
       <c r="C849" s="1"/>
       <c r="D849" s="1"/>
       <c r="E849" s="1"/>
@@ -20160,7 +20163,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="850" customHeight="1" ht="18">
       <c r="A850" s="1"/>
-      <c r="B850" s="2"/>
+      <c r="B850" s="7"/>
       <c r="C850" s="1"/>
       <c r="D850" s="1"/>
       <c r="E850" s="1"/>
@@ -20183,7 +20186,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="851" customHeight="1" ht="18">
       <c r="A851" s="1"/>
-      <c r="B851" s="2"/>
+      <c r="B851" s="7"/>
       <c r="C851" s="1"/>
       <c r="D851" s="1"/>
       <c r="E851" s="1"/>
@@ -20206,7 +20209,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="852" customHeight="1" ht="18">
       <c r="A852" s="1"/>
-      <c r="B852" s="2"/>
+      <c r="B852" s="7"/>
       <c r="C852" s="1"/>
       <c r="D852" s="1"/>
       <c r="E852" s="1"/>
@@ -20229,7 +20232,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="853" customHeight="1" ht="18">
       <c r="A853" s="1"/>
-      <c r="B853" s="2"/>
+      <c r="B853" s="7"/>
       <c r="C853" s="1"/>
       <c r="D853" s="1"/>
       <c r="E853" s="1"/>
@@ -20252,7 +20255,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="854" customHeight="1" ht="18">
       <c r="A854" s="1"/>
-      <c r="B854" s="2"/>
+      <c r="B854" s="7"/>
       <c r="C854" s="1"/>
       <c r="D854" s="1"/>
       <c r="E854" s="1"/>
@@ -20275,7 +20278,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="855" customHeight="1" ht="18">
       <c r="A855" s="1"/>
-      <c r="B855" s="2"/>
+      <c r="B855" s="7"/>
       <c r="C855" s="1"/>
       <c r="D855" s="1"/>
       <c r="E855" s="1"/>
@@ -20298,7 +20301,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="856" customHeight="1" ht="18">
       <c r="A856" s="1"/>
-      <c r="B856" s="2"/>
+      <c r="B856" s="7"/>
       <c r="C856" s="1"/>
       <c r="D856" s="1"/>
       <c r="E856" s="1"/>
@@ -20321,7 +20324,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="857" customHeight="1" ht="18">
       <c r="A857" s="1"/>
-      <c r="B857" s="2"/>
+      <c r="B857" s="7"/>
       <c r="C857" s="1"/>
       <c r="D857" s="1"/>
       <c r="E857" s="1"/>
@@ -20344,7 +20347,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="858" customHeight="1" ht="18">
       <c r="A858" s="1"/>
-      <c r="B858" s="2"/>
+      <c r="B858" s="7"/>
       <c r="C858" s="1"/>
       <c r="D858" s="1"/>
       <c r="E858" s="1"/>
@@ -20367,7 +20370,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="859" customHeight="1" ht="18">
       <c r="A859" s="1"/>
-      <c r="B859" s="2"/>
+      <c r="B859" s="7"/>
       <c r="C859" s="1"/>
       <c r="D859" s="1"/>
       <c r="E859" s="1"/>
@@ -20390,7 +20393,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="860" customHeight="1" ht="18">
       <c r="A860" s="1"/>
-      <c r="B860" s="2"/>
+      <c r="B860" s="7"/>
       <c r="C860" s="1"/>
       <c r="D860" s="1"/>
       <c r="E860" s="1"/>
@@ -20413,7 +20416,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="861" customHeight="1" ht="18">
       <c r="A861" s="1"/>
-      <c r="B861" s="2"/>
+      <c r="B861" s="7"/>
       <c r="C861" s="1"/>
       <c r="D861" s="1"/>
       <c r="E861" s="1"/>
@@ -20436,7 +20439,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="862" customHeight="1" ht="18">
       <c r="A862" s="1"/>
-      <c r="B862" s="2"/>
+      <c r="B862" s="7"/>
       <c r="C862" s="1"/>
       <c r="D862" s="1"/>
       <c r="E862" s="1"/>
@@ -20459,7 +20462,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="863" customHeight="1" ht="18">
       <c r="A863" s="1"/>
-      <c r="B863" s="2"/>
+      <c r="B863" s="7"/>
       <c r="C863" s="1"/>
       <c r="D863" s="1"/>
       <c r="E863" s="1"/>
@@ -20482,7 +20485,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="864" customHeight="1" ht="18">
       <c r="A864" s="1"/>
-      <c r="B864" s="2"/>
+      <c r="B864" s="7"/>
       <c r="C864" s="1"/>
       <c r="D864" s="1"/>
       <c r="E864" s="1"/>
@@ -20505,7 +20508,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="865" customHeight="1" ht="18">
       <c r="A865" s="1"/>
-      <c r="B865" s="2"/>
+      <c r="B865" s="7"/>
       <c r="C865" s="1"/>
       <c r="D865" s="1"/>
       <c r="E865" s="1"/>
@@ -20528,7 +20531,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="866" customHeight="1" ht="18">
       <c r="A866" s="1"/>
-      <c r="B866" s="2"/>
+      <c r="B866" s="7"/>
       <c r="C866" s="1"/>
       <c r="D866" s="1"/>
       <c r="E866" s="1"/>
@@ -20551,7 +20554,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="867" customHeight="1" ht="18">
       <c r="A867" s="1"/>
-      <c r="B867" s="2"/>
+      <c r="B867" s="7"/>
       <c r="C867" s="1"/>
       <c r="D867" s="1"/>
       <c r="E867" s="1"/>
@@ -20574,7 +20577,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="868" customHeight="1" ht="18">
       <c r="A868" s="1"/>
-      <c r="B868" s="2"/>
+      <c r="B868" s="7"/>
       <c r="C868" s="1"/>
       <c r="D868" s="1"/>
       <c r="E868" s="1"/>
@@ -20597,7 +20600,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="869" customHeight="1" ht="18">
       <c r="A869" s="1"/>
-      <c r="B869" s="2"/>
+      <c r="B869" s="7"/>
       <c r="C869" s="1"/>
       <c r="D869" s="1"/>
       <c r="E869" s="1"/>
@@ -20620,7 +20623,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="870" customHeight="1" ht="18">
       <c r="A870" s="1"/>
-      <c r="B870" s="2"/>
+      <c r="B870" s="7"/>
       <c r="C870" s="1"/>
       <c r="D870" s="1"/>
       <c r="E870" s="1"/>
@@ -20643,7 +20646,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="871" customHeight="1" ht="18">
       <c r="A871" s="1"/>
-      <c r="B871" s="2"/>
+      <c r="B871" s="7"/>
       <c r="C871" s="1"/>
       <c r="D871" s="1"/>
       <c r="E871" s="1"/>
@@ -20666,7 +20669,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="872" customHeight="1" ht="18">
       <c r="A872" s="1"/>
-      <c r="B872" s="2"/>
+      <c r="B872" s="7"/>
       <c r="C872" s="1"/>
       <c r="D872" s="1"/>
       <c r="E872" s="1"/>
@@ -20689,7 +20692,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="873" customHeight="1" ht="18">
       <c r="A873" s="1"/>
-      <c r="B873" s="2"/>
+      <c r="B873" s="7"/>
       <c r="C873" s="1"/>
       <c r="D873" s="1"/>
       <c r="E873" s="1"/>
@@ -20712,7 +20715,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="874" customHeight="1" ht="18">
       <c r="A874" s="1"/>
-      <c r="B874" s="2"/>
+      <c r="B874" s="7"/>
       <c r="C874" s="1"/>
       <c r="D874" s="1"/>
       <c r="E874" s="1"/>
@@ -20735,7 +20738,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="875" customHeight="1" ht="18">
       <c r="A875" s="1"/>
-      <c r="B875" s="2"/>
+      <c r="B875" s="7"/>
       <c r="C875" s="1"/>
       <c r="D875" s="1"/>
       <c r="E875" s="1"/>
@@ -20758,7 +20761,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="876" customHeight="1" ht="18">
       <c r="A876" s="1"/>
-      <c r="B876" s="2"/>
+      <c r="B876" s="7"/>
       <c r="C876" s="1"/>
       <c r="D876" s="1"/>
       <c r="E876" s="1"/>
@@ -20781,7 +20784,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="877" customHeight="1" ht="18">
       <c r="A877" s="1"/>
-      <c r="B877" s="2"/>
+      <c r="B877" s="7"/>
       <c r="C877" s="1"/>
       <c r="D877" s="1"/>
       <c r="E877" s="1"/>
@@ -20804,7 +20807,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="878" customHeight="1" ht="18">
       <c r="A878" s="1"/>
-      <c r="B878" s="2"/>
+      <c r="B878" s="7"/>
       <c r="C878" s="1"/>
       <c r="D878" s="1"/>
       <c r="E878" s="1"/>
@@ -20827,7 +20830,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="879" customHeight="1" ht="18">
       <c r="A879" s="1"/>
-      <c r="B879" s="2"/>
+      <c r="B879" s="7"/>
       <c r="C879" s="1"/>
       <c r="D879" s="1"/>
       <c r="E879" s="1"/>
@@ -20850,7 +20853,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="880" customHeight="1" ht="18">
       <c r="A880" s="1"/>
-      <c r="B880" s="2"/>
+      <c r="B880" s="7"/>
       <c r="C880" s="1"/>
       <c r="D880" s="1"/>
       <c r="E880" s="1"/>
@@ -20873,7 +20876,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="881" customHeight="1" ht="18">
       <c r="A881" s="1"/>
-      <c r="B881" s="2"/>
+      <c r="B881" s="7"/>
       <c r="C881" s="1"/>
       <c r="D881" s="1"/>
       <c r="E881" s="1"/>
@@ -20896,7 +20899,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="882" customHeight="1" ht="18">
       <c r="A882" s="1"/>
-      <c r="B882" s="2"/>
+      <c r="B882" s="7"/>
       <c r="C882" s="1"/>
       <c r="D882" s="1"/>
       <c r="E882" s="1"/>
@@ -20919,7 +20922,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="883" customHeight="1" ht="18">
       <c r="A883" s="1"/>
-      <c r="B883" s="2"/>
+      <c r="B883" s="7"/>
       <c r="C883" s="1"/>
       <c r="D883" s="1"/>
       <c r="E883" s="1"/>
@@ -20942,7 +20945,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="884" customHeight="1" ht="18">
       <c r="A884" s="1"/>
-      <c r="B884" s="2"/>
+      <c r="B884" s="7"/>
       <c r="C884" s="1"/>
       <c r="D884" s="1"/>
       <c r="E884" s="1"/>
@@ -20965,7 +20968,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="885" customHeight="1" ht="18">
       <c r="A885" s="1"/>
-      <c r="B885" s="2"/>
+      <c r="B885" s="7"/>
       <c r="C885" s="1"/>
       <c r="D885" s="1"/>
       <c r="E885" s="1"/>
@@ -20988,7 +20991,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="886" customHeight="1" ht="18">
       <c r="A886" s="1"/>
-      <c r="B886" s="2"/>
+      <c r="B886" s="7"/>
       <c r="C886" s="1"/>
       <c r="D886" s="1"/>
       <c r="E886" s="1"/>
@@ -21011,7 +21014,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="887" customHeight="1" ht="18">
       <c r="A887" s="1"/>
-      <c r="B887" s="2"/>
+      <c r="B887" s="7"/>
       <c r="C887" s="1"/>
       <c r="D887" s="1"/>
       <c r="E887" s="1"/>
@@ -21034,7 +21037,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="888" customHeight="1" ht="18">
       <c r="A888" s="1"/>
-      <c r="B888" s="2"/>
+      <c r="B888" s="7"/>
       <c r="C888" s="1"/>
       <c r="D888" s="1"/>
       <c r="E888" s="1"/>
@@ -21057,7 +21060,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="889" customHeight="1" ht="18">
       <c r="A889" s="1"/>
-      <c r="B889" s="2"/>
+      <c r="B889" s="7"/>
       <c r="C889" s="1"/>
       <c r="D889" s="1"/>
       <c r="E889" s="1"/>
@@ -21080,7 +21083,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="890" customHeight="1" ht="18">
       <c r="A890" s="1"/>
-      <c r="B890" s="2"/>
+      <c r="B890" s="7"/>
       <c r="C890" s="1"/>
       <c r="D890" s="1"/>
       <c r="E890" s="1"/>
@@ -21103,7 +21106,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="891" customHeight="1" ht="18">
       <c r="A891" s="1"/>
-      <c r="B891" s="2"/>
+      <c r="B891" s="7"/>
       <c r="C891" s="1"/>
       <c r="D891" s="1"/>
       <c r="E891" s="1"/>
@@ -21126,7 +21129,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="892" customHeight="1" ht="18">
       <c r="A892" s="1"/>
-      <c r="B892" s="2"/>
+      <c r="B892" s="7"/>
       <c r="C892" s="1"/>
       <c r="D892" s="1"/>
       <c r="E892" s="1"/>
@@ -21149,7 +21152,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="893" customHeight="1" ht="18">
       <c r="A893" s="1"/>
-      <c r="B893" s="2"/>
+      <c r="B893" s="7"/>
       <c r="C893" s="1"/>
       <c r="D893" s="1"/>
       <c r="E893" s="1"/>
@@ -21172,7 +21175,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="894" customHeight="1" ht="18">
       <c r="A894" s="1"/>
-      <c r="B894" s="2"/>
+      <c r="B894" s="7"/>
       <c r="C894" s="1"/>
       <c r="D894" s="1"/>
       <c r="E894" s="1"/>
@@ -21195,7 +21198,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="895" customHeight="1" ht="18">
       <c r="A895" s="1"/>
-      <c r="B895" s="2"/>
+      <c r="B895" s="7"/>
       <c r="C895" s="1"/>
       <c r="D895" s="1"/>
       <c r="E895" s="1"/>
@@ -21218,7 +21221,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="896" customHeight="1" ht="18">
       <c r="A896" s="1"/>
-      <c r="B896" s="2"/>
+      <c r="B896" s="7"/>
       <c r="C896" s="1"/>
       <c r="D896" s="1"/>
       <c r="E896" s="1"/>
@@ -21241,7 +21244,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="897" customHeight="1" ht="18">
       <c r="A897" s="1"/>
-      <c r="B897" s="2"/>
+      <c r="B897" s="7"/>
       <c r="C897" s="1"/>
       <c r="D897" s="1"/>
       <c r="E897" s="1"/>
@@ -21264,7 +21267,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="898" customHeight="1" ht="18">
       <c r="A898" s="1"/>
-      <c r="B898" s="2"/>
+      <c r="B898" s="7"/>
       <c r="C898" s="1"/>
       <c r="D898" s="1"/>
       <c r="E898" s="1"/>
@@ -21287,7 +21290,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="899" customHeight="1" ht="18">
       <c r="A899" s="1"/>
-      <c r="B899" s="2"/>
+      <c r="B899" s="7"/>
       <c r="C899" s="1"/>
       <c r="D899" s="1"/>
       <c r="E899" s="1"/>
@@ -21310,7 +21313,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="900" customHeight="1" ht="18">
       <c r="A900" s="1"/>
-      <c r="B900" s="2"/>
+      <c r="B900" s="7"/>
       <c r="C900" s="1"/>
       <c r="D900" s="1"/>
       <c r="E900" s="1"/>
@@ -21333,7 +21336,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="901" customHeight="1" ht="18">
       <c r="A901" s="1"/>
-      <c r="B901" s="2"/>
+      <c r="B901" s="7"/>
       <c r="C901" s="1"/>
       <c r="D901" s="1"/>
       <c r="E901" s="1"/>
@@ -21356,7 +21359,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="902" customHeight="1" ht="18">
       <c r="A902" s="1"/>
-      <c r="B902" s="2"/>
+      <c r="B902" s="7"/>
       <c r="C902" s="1"/>
       <c r="D902" s="1"/>
       <c r="E902" s="1"/>
@@ -21379,7 +21382,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="903" customHeight="1" ht="18">
       <c r="A903" s="1"/>
-      <c r="B903" s="2"/>
+      <c r="B903" s="7"/>
       <c r="C903" s="1"/>
       <c r="D903" s="1"/>
       <c r="E903" s="1"/>
@@ -21402,7 +21405,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="904" customHeight="1" ht="18">
       <c r="A904" s="1"/>
-      <c r="B904" s="2"/>
+      <c r="B904" s="7"/>
       <c r="C904" s="1"/>
       <c r="D904" s="1"/>
       <c r="E904" s="1"/>
@@ -21425,7 +21428,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="905" customHeight="1" ht="18">
       <c r="A905" s="1"/>
-      <c r="B905" s="2"/>
+      <c r="B905" s="7"/>
       <c r="C905" s="1"/>
       <c r="D905" s="1"/>
       <c r="E905" s="1"/>
@@ -21448,7 +21451,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="906" customHeight="1" ht="18">
       <c r="A906" s="1"/>
-      <c r="B906" s="2"/>
+      <c r="B906" s="7"/>
       <c r="C906" s="1"/>
       <c r="D906" s="1"/>
       <c r="E906" s="1"/>
@@ -21471,7 +21474,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="907" customHeight="1" ht="18">
       <c r="A907" s="1"/>
-      <c r="B907" s="2"/>
+      <c r="B907" s="7"/>
       <c r="C907" s="1"/>
       <c r="D907" s="1"/>
       <c r="E907" s="1"/>
@@ -21494,7 +21497,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="908" customHeight="1" ht="18">
       <c r="A908" s="1"/>
-      <c r="B908" s="2"/>
+      <c r="B908" s="7"/>
       <c r="C908" s="1"/>
       <c r="D908" s="1"/>
       <c r="E908" s="1"/>
@@ -21517,7 +21520,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="909" customHeight="1" ht="18">
       <c r="A909" s="1"/>
-      <c r="B909" s="2"/>
+      <c r="B909" s="7"/>
       <c r="C909" s="1"/>
       <c r="D909" s="1"/>
       <c r="E909" s="1"/>
@@ -21540,7 +21543,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="910" customHeight="1" ht="18">
       <c r="A910" s="1"/>
-      <c r="B910" s="2"/>
+      <c r="B910" s="7"/>
       <c r="C910" s="1"/>
       <c r="D910" s="1"/>
       <c r="E910" s="1"/>
@@ -21563,7 +21566,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="911" customHeight="1" ht="18">
       <c r="A911" s="1"/>
-      <c r="B911" s="2"/>
+      <c r="B911" s="7"/>
       <c r="C911" s="1"/>
       <c r="D911" s="1"/>
       <c r="E911" s="1"/>
@@ -21586,7 +21589,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="912" customHeight="1" ht="18">
       <c r="A912" s="1"/>
-      <c r="B912" s="2"/>
+      <c r="B912" s="7"/>
       <c r="C912" s="1"/>
       <c r="D912" s="1"/>
       <c r="E912" s="1"/>
@@ -21609,7 +21612,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="913" customHeight="1" ht="18">
       <c r="A913" s="1"/>
-      <c r="B913" s="2"/>
+      <c r="B913" s="7"/>
       <c r="C913" s="1"/>
       <c r="D913" s="1"/>
       <c r="E913" s="1"/>
@@ -21632,7 +21635,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="914" customHeight="1" ht="18">
       <c r="A914" s="1"/>
-      <c r="B914" s="2"/>
+      <c r="B914" s="7"/>
       <c r="C914" s="1"/>
       <c r="D914" s="1"/>
       <c r="E914" s="1"/>
@@ -21655,7 +21658,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="915" customHeight="1" ht="18">
       <c r="A915" s="1"/>
-      <c r="B915" s="2"/>
+      <c r="B915" s="7"/>
       <c r="C915" s="1"/>
       <c r="D915" s="1"/>
       <c r="E915" s="1"/>
@@ -21678,7 +21681,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="916" customHeight="1" ht="18">
       <c r="A916" s="1"/>
-      <c r="B916" s="2"/>
+      <c r="B916" s="7"/>
       <c r="C916" s="1"/>
       <c r="D916" s="1"/>
       <c r="E916" s="1"/>
@@ -21701,7 +21704,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="917" customHeight="1" ht="18">
       <c r="A917" s="1"/>
-      <c r="B917" s="2"/>
+      <c r="B917" s="7"/>
       <c r="C917" s="1"/>
       <c r="D917" s="1"/>
       <c r="E917" s="1"/>
@@ -21724,7 +21727,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="918" customHeight="1" ht="18">
       <c r="A918" s="1"/>
-      <c r="B918" s="2"/>
+      <c r="B918" s="7"/>
       <c r="C918" s="1"/>
       <c r="D918" s="1"/>
       <c r="E918" s="1"/>
@@ -21747,7 +21750,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="919" customHeight="1" ht="18">
       <c r="A919" s="1"/>
-      <c r="B919" s="2"/>
+      <c r="B919" s="7"/>
       <c r="C919" s="1"/>
       <c r="D919" s="1"/>
       <c r="E919" s="1"/>
@@ -21770,7 +21773,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="920" customHeight="1" ht="18">
       <c r="A920" s="1"/>
-      <c r="B920" s="2"/>
+      <c r="B920" s="7"/>
       <c r="C920" s="1"/>
       <c r="D920" s="1"/>
       <c r="E920" s="1"/>
@@ -21793,7 +21796,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="921" customHeight="1" ht="18">
       <c r="A921" s="1"/>
-      <c r="B921" s="2"/>
+      <c r="B921" s="7"/>
       <c r="C921" s="1"/>
       <c r="D921" s="1"/>
       <c r="E921" s="1"/>
@@ -21816,7 +21819,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="922" customHeight="1" ht="18">
       <c r="A922" s="1"/>
-      <c r="B922" s="2"/>
+      <c r="B922" s="7"/>
       <c r="C922" s="1"/>
       <c r="D922" s="1"/>
       <c r="E922" s="1"/>
@@ -21839,7 +21842,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="923" customHeight="1" ht="18">
       <c r="A923" s="1"/>
-      <c r="B923" s="2"/>
+      <c r="B923" s="7"/>
       <c r="C923" s="1"/>
       <c r="D923" s="1"/>
       <c r="E923" s="1"/>
@@ -21862,7 +21865,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="924" customHeight="1" ht="18">
       <c r="A924" s="1"/>
-      <c r="B924" s="2"/>
+      <c r="B924" s="7"/>
       <c r="C924" s="1"/>
       <c r="D924" s="1"/>
       <c r="E924" s="1"/>
@@ -21885,7 +21888,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="925" customHeight="1" ht="18">
       <c r="A925" s="1"/>
-      <c r="B925" s="2"/>
+      <c r="B925" s="7"/>
       <c r="C925" s="1"/>
       <c r="D925" s="1"/>
       <c r="E925" s="1"/>
@@ -21908,7 +21911,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="926" customHeight="1" ht="18">
       <c r="A926" s="1"/>
-      <c r="B926" s="2"/>
+      <c r="B926" s="7"/>
       <c r="C926" s="1"/>
       <c r="D926" s="1"/>
       <c r="E926" s="1"/>
@@ -21931,7 +21934,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="927" customHeight="1" ht="18">
       <c r="A927" s="1"/>
-      <c r="B927" s="2"/>
+      <c r="B927" s="7"/>
       <c r="C927" s="1"/>
       <c r="D927" s="1"/>
       <c r="E927" s="1"/>
@@ -21954,7 +21957,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="928" customHeight="1" ht="18">
       <c r="A928" s="1"/>
-      <c r="B928" s="2"/>
+      <c r="B928" s="7"/>
       <c r="C928" s="1"/>
       <c r="D928" s="1"/>
       <c r="E928" s="1"/>
@@ -21977,7 +21980,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="929" customHeight="1" ht="18">
       <c r="A929" s="1"/>
-      <c r="B929" s="2"/>
+      <c r="B929" s="7"/>
       <c r="C929" s="1"/>
       <c r="D929" s="1"/>
       <c r="E929" s="1"/>
@@ -22000,7 +22003,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="930" customHeight="1" ht="18">
       <c r="A930" s="1"/>
-      <c r="B930" s="2"/>
+      <c r="B930" s="7"/>
       <c r="C930" s="1"/>
       <c r="D930" s="1"/>
       <c r="E930" s="1"/>
@@ -22023,7 +22026,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="931" customHeight="1" ht="18">
       <c r="A931" s="1"/>
-      <c r="B931" s="2"/>
+      <c r="B931" s="7"/>
       <c r="C931" s="1"/>
       <c r="D931" s="1"/>
       <c r="E931" s="1"/>
@@ -22046,7 +22049,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="932" customHeight="1" ht="18">
       <c r="A932" s="1"/>
-      <c r="B932" s="2"/>
+      <c r="B932" s="7"/>
       <c r="C932" s="1"/>
       <c r="D932" s="1"/>
       <c r="E932" s="1"/>
@@ -22069,7 +22072,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="933" customHeight="1" ht="18">
       <c r="A933" s="1"/>
-      <c r="B933" s="2"/>
+      <c r="B933" s="7"/>
       <c r="C933" s="1"/>
       <c r="D933" s="1"/>
       <c r="E933" s="1"/>
@@ -22092,7 +22095,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="934" customHeight="1" ht="18">
       <c r="A934" s="1"/>
-      <c r="B934" s="2"/>
+      <c r="B934" s="7"/>
       <c r="C934" s="1"/>
       <c r="D934" s="1"/>
       <c r="E934" s="1"/>
@@ -22115,7 +22118,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="935" customHeight="1" ht="18">
       <c r="A935" s="1"/>
-      <c r="B935" s="2"/>
+      <c r="B935" s="7"/>
       <c r="C935" s="1"/>
       <c r="D935" s="1"/>
       <c r="E935" s="1"/>
@@ -22138,7 +22141,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="936" customHeight="1" ht="18">
       <c r="A936" s="1"/>
-      <c r="B936" s="2"/>
+      <c r="B936" s="7"/>
       <c r="C936" s="1"/>
       <c r="D936" s="1"/>
       <c r="E936" s="1"/>
@@ -22161,7 +22164,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="937" customHeight="1" ht="18">
       <c r="A937" s="1"/>
-      <c r="B937" s="2"/>
+      <c r="B937" s="7"/>
       <c r="C937" s="1"/>
       <c r="D937" s="1"/>
       <c r="E937" s="1"/>
@@ -22184,7 +22187,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="938" customHeight="1" ht="18">
       <c r="A938" s="1"/>
-      <c r="B938" s="2"/>
+      <c r="B938" s="7"/>
       <c r="C938" s="1"/>
       <c r="D938" s="1"/>
       <c r="E938" s="1"/>
@@ -22207,7 +22210,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="939" customHeight="1" ht="18">
       <c r="A939" s="1"/>
-      <c r="B939" s="2"/>
+      <c r="B939" s="7"/>
       <c r="C939" s="1"/>
       <c r="D939" s="1"/>
       <c r="E939" s="1"/>
@@ -22230,7 +22233,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="940" customHeight="1" ht="18">
       <c r="A940" s="1"/>
-      <c r="B940" s="2"/>
+      <c r="B940" s="7"/>
       <c r="C940" s="1"/>
       <c r="D940" s="1"/>
       <c r="E940" s="1"/>
@@ -22253,7 +22256,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="941" customHeight="1" ht="18">
       <c r="A941" s="1"/>
-      <c r="B941" s="2"/>
+      <c r="B941" s="7"/>
       <c r="C941" s="1"/>
       <c r="D941" s="1"/>
       <c r="E941" s="1"/>
@@ -22276,7 +22279,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="942" customHeight="1" ht="18">
       <c r="A942" s="1"/>
-      <c r="B942" s="2"/>
+      <c r="B942" s="7"/>
       <c r="C942" s="1"/>
       <c r="D942" s="1"/>
       <c r="E942" s="1"/>
@@ -22299,7 +22302,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="943" customHeight="1" ht="18">
       <c r="A943" s="1"/>
-      <c r="B943" s="2"/>
+      <c r="B943" s="7"/>
       <c r="C943" s="1"/>
       <c r="D943" s="1"/>
       <c r="E943" s="1"/>
@@ -22322,7 +22325,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="944" customHeight="1" ht="18">
       <c r="A944" s="1"/>
-      <c r="B944" s="2"/>
+      <c r="B944" s="7"/>
       <c r="C944" s="1"/>
       <c r="D944" s="1"/>
       <c r="E944" s="1"/>
@@ -22345,7 +22348,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="945" customHeight="1" ht="18">
       <c r="A945" s="1"/>
-      <c r="B945" s="2"/>
+      <c r="B945" s="7"/>
       <c r="C945" s="1"/>
       <c r="D945" s="1"/>
       <c r="E945" s="1"/>
@@ -22368,7 +22371,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="946" customHeight="1" ht="18">
       <c r="A946" s="1"/>
-      <c r="B946" s="2"/>
+      <c r="B946" s="7"/>
       <c r="C946" s="1"/>
       <c r="D946" s="1"/>
       <c r="E946" s="1"/>
@@ -22391,7 +22394,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="947" customHeight="1" ht="18">
       <c r="A947" s="1"/>
-      <c r="B947" s="2"/>
+      <c r="B947" s="7"/>
       <c r="C947" s="1"/>
       <c r="D947" s="1"/>
       <c r="E947" s="1"/>
@@ -22414,7 +22417,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="948" customHeight="1" ht="18">
       <c r="A948" s="1"/>
-      <c r="B948" s="2"/>
+      <c r="B948" s="7"/>
       <c r="C948" s="1"/>
       <c r="D948" s="1"/>
       <c r="E948" s="1"/>
@@ -22437,7 +22440,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="949" customHeight="1" ht="18">
       <c r="A949" s="1"/>
-      <c r="B949" s="2"/>
+      <c r="B949" s="7"/>
       <c r="C949" s="1"/>
       <c r="D949" s="1"/>
       <c r="E949" s="1"/>
@@ -22460,7 +22463,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="950" customHeight="1" ht="18">
       <c r="A950" s="1"/>
-      <c r="B950" s="2"/>
+      <c r="B950" s="7"/>
       <c r="C950" s="1"/>
       <c r="D950" s="1"/>
       <c r="E950" s="1"/>
@@ -22483,7 +22486,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="951" customHeight="1" ht="18">
       <c r="A951" s="1"/>
-      <c r="B951" s="2"/>
+      <c r="B951" s="7"/>
       <c r="C951" s="1"/>
       <c r="D951" s="1"/>
       <c r="E951" s="1"/>
@@ -22506,7 +22509,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="952" customHeight="1" ht="18">
       <c r="A952" s="1"/>
-      <c r="B952" s="2"/>
+      <c r="B952" s="7"/>
       <c r="C952" s="1"/>
       <c r="D952" s="1"/>
       <c r="E952" s="1"/>
@@ -22529,7 +22532,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="953" customHeight="1" ht="18">
       <c r="A953" s="1"/>
-      <c r="B953" s="2"/>
+      <c r="B953" s="7"/>
       <c r="C953" s="1"/>
       <c r="D953" s="1"/>
       <c r="E953" s="1"/>
@@ -22552,7 +22555,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="954" customHeight="1" ht="18">
       <c r="A954" s="1"/>
-      <c r="B954" s="2"/>
+      <c r="B954" s="7"/>
       <c r="C954" s="1"/>
       <c r="D954" s="1"/>
       <c r="E954" s="1"/>
@@ -22575,7 +22578,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="955" customHeight="1" ht="18">
       <c r="A955" s="1"/>
-      <c r="B955" s="2"/>
+      <c r="B955" s="7"/>
       <c r="C955" s="1"/>
       <c r="D955" s="1"/>
       <c r="E955" s="1"/>
@@ -22598,7 +22601,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="956" customHeight="1" ht="18">
       <c r="A956" s="1"/>
-      <c r="B956" s="2"/>
+      <c r="B956" s="7"/>
       <c r="C956" s="1"/>
       <c r="D956" s="1"/>
       <c r="E956" s="1"/>
@@ -22621,7 +22624,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="957" customHeight="1" ht="18">
       <c r="A957" s="1"/>
-      <c r="B957" s="2"/>
+      <c r="B957" s="7"/>
       <c r="C957" s="1"/>
       <c r="D957" s="1"/>
       <c r="E957" s="1"/>
@@ -22644,7 +22647,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="958" customHeight="1" ht="18">
       <c r="A958" s="1"/>
-      <c r="B958" s="2"/>
+      <c r="B958" s="7"/>
       <c r="C958" s="1"/>
       <c r="D958" s="1"/>
       <c r="E958" s="1"/>
@@ -22667,7 +22670,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="959" customHeight="1" ht="18">
       <c r="A959" s="1"/>
-      <c r="B959" s="2"/>
+      <c r="B959" s="7"/>
       <c r="C959" s="1"/>
       <c r="D959" s="1"/>
       <c r="E959" s="1"/>
@@ -22690,7 +22693,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="960" customHeight="1" ht="18">
       <c r="A960" s="1"/>
-      <c r="B960" s="2"/>
+      <c r="B960" s="7"/>
       <c r="C960" s="1"/>
       <c r="D960" s="1"/>
       <c r="E960" s="1"/>
@@ -22713,7 +22716,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="961" customHeight="1" ht="18">
       <c r="A961" s="1"/>
-      <c r="B961" s="2"/>
+      <c r="B961" s="7"/>
       <c r="C961" s="1"/>
       <c r="D961" s="1"/>
       <c r="E961" s="1"/>
@@ -22736,7 +22739,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="962" customHeight="1" ht="18">
       <c r="A962" s="1"/>
-      <c r="B962" s="2"/>
+      <c r="B962" s="7"/>
       <c r="C962" s="1"/>
       <c r="D962" s="1"/>
       <c r="E962" s="1"/>
@@ -22759,7 +22762,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="963" customHeight="1" ht="18">
       <c r="A963" s="1"/>
-      <c r="B963" s="2"/>
+      <c r="B963" s="7"/>
       <c r="C963" s="1"/>
       <c r="D963" s="1"/>
       <c r="E963" s="1"/>
@@ -22782,7 +22785,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="964" customHeight="1" ht="18">
       <c r="A964" s="1"/>
-      <c r="B964" s="2"/>
+      <c r="B964" s="7"/>
       <c r="C964" s="1"/>
       <c r="D964" s="1"/>
       <c r="E964" s="1"/>
@@ -22805,7 +22808,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="965" customHeight="1" ht="18">
       <c r="A965" s="1"/>
-      <c r="B965" s="2"/>
+      <c r="B965" s="7"/>
       <c r="C965" s="1"/>
       <c r="D965" s="1"/>
       <c r="E965" s="1"/>
@@ -22828,7 +22831,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="966" customHeight="1" ht="18">
       <c r="A966" s="1"/>
-      <c r="B966" s="2"/>
+      <c r="B966" s="7"/>
       <c r="C966" s="1"/>
       <c r="D966" s="1"/>
       <c r="E966" s="1"/>
@@ -22851,7 +22854,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="967" customHeight="1" ht="18">
       <c r="A967" s="1"/>
-      <c r="B967" s="2"/>
+      <c r="B967" s="7"/>
       <c r="C967" s="1"/>
       <c r="D967" s="1"/>
       <c r="E967" s="1"/>
@@ -22874,7 +22877,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="968" customHeight="1" ht="18">
       <c r="A968" s="1"/>
-      <c r="B968" s="2"/>
+      <c r="B968" s="7"/>
       <c r="C968" s="1"/>
       <c r="D968" s="1"/>
       <c r="E968" s="1"/>
@@ -22897,7 +22900,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="969" customHeight="1" ht="18">
       <c r="A969" s="1"/>
-      <c r="B969" s="2"/>
+      <c r="B969" s="7"/>
       <c r="C969" s="1"/>
       <c r="D969" s="1"/>
       <c r="E969" s="1"/>
@@ -22920,7 +22923,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="970" customHeight="1" ht="18">
       <c r="A970" s="1"/>
-      <c r="B970" s="2"/>
+      <c r="B970" s="7"/>
       <c r="C970" s="1"/>
       <c r="D970" s="1"/>
       <c r="E970" s="1"/>
@@ -22943,7 +22946,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="971" customHeight="1" ht="18">
       <c r="A971" s="1"/>
-      <c r="B971" s="2"/>
+      <c r="B971" s="7"/>
       <c r="C971" s="1"/>
       <c r="D971" s="1"/>
       <c r="E971" s="1"/>
@@ -22966,7 +22969,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="972" customHeight="1" ht="18">
       <c r="A972" s="1"/>
-      <c r="B972" s="2"/>
+      <c r="B972" s="7"/>
       <c r="C972" s="1"/>
       <c r="D972" s="1"/>
       <c r="E972" s="1"/>
@@ -22989,7 +22992,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="973" customHeight="1" ht="18">
       <c r="A973" s="1"/>
-      <c r="B973" s="2"/>
+      <c r="B973" s="7"/>
       <c r="C973" s="1"/>
       <c r="D973" s="1"/>
       <c r="E973" s="1"/>
@@ -23012,7 +23015,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="974" customHeight="1" ht="18">
       <c r="A974" s="1"/>
-      <c r="B974" s="2"/>
+      <c r="B974" s="7"/>
       <c r="C974" s="1"/>
       <c r="D974" s="1"/>
       <c r="E974" s="1"/>
@@ -23035,7 +23038,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="975" customHeight="1" ht="18">
       <c r="A975" s="1"/>
-      <c r="B975" s="2"/>
+      <c r="B975" s="7"/>
       <c r="C975" s="1"/>
       <c r="D975" s="1"/>
       <c r="E975" s="1"/>
@@ -23058,7 +23061,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="976" customHeight="1" ht="18">
       <c r="A976" s="1"/>
-      <c r="B976" s="2"/>
+      <c r="B976" s="7"/>
       <c r="C976" s="1"/>
       <c r="D976" s="1"/>
       <c r="E976" s="1"/>
@@ -23081,7 +23084,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="977" customHeight="1" ht="18">
       <c r="A977" s="1"/>
-      <c r="B977" s="2"/>
+      <c r="B977" s="7"/>
       <c r="C977" s="1"/>
       <c r="D977" s="1"/>
       <c r="E977" s="1"/>
@@ -23104,7 +23107,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="978" customHeight="1" ht="18">
       <c r="A978" s="1"/>
-      <c r="B978" s="2"/>
+      <c r="B978" s="7"/>
       <c r="C978" s="1"/>
       <c r="D978" s="1"/>
       <c r="E978" s="1"/>
@@ -23127,7 +23130,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="979" customHeight="1" ht="18">
       <c r="A979" s="1"/>
-      <c r="B979" s="2"/>
+      <c r="B979" s="7"/>
       <c r="C979" s="1"/>
       <c r="D979" s="1"/>
       <c r="E979" s="1"/>
@@ -23150,7 +23153,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="980" customHeight="1" ht="18">
       <c r="A980" s="1"/>
-      <c r="B980" s="2"/>
+      <c r="B980" s="7"/>
       <c r="C980" s="1"/>
       <c r="D980" s="1"/>
       <c r="E980" s="1"/>
@@ -23173,7 +23176,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="981" customHeight="1" ht="18">
       <c r="A981" s="1"/>
-      <c r="B981" s="2"/>
+      <c r="B981" s="7"/>
       <c r="C981" s="1"/>
       <c r="D981" s="1"/>
       <c r="E981" s="1"/>
@@ -23196,7 +23199,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="982" customHeight="1" ht="18">
       <c r="A982" s="1"/>
-      <c r="B982" s="2"/>
+      <c r="B982" s="7"/>
       <c r="C982" s="1"/>
       <c r="D982" s="1"/>
       <c r="E982" s="1"/>
@@ -23219,7 +23222,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="983" customHeight="1" ht="18">
       <c r="A983" s="1"/>
-      <c r="B983" s="2"/>
+      <c r="B983" s="7"/>
       <c r="C983" s="1"/>
       <c r="D983" s="1"/>
       <c r="E983" s="1"/>
@@ -23242,7 +23245,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="984" customHeight="1" ht="18">
       <c r="A984" s="1"/>
-      <c r="B984" s="2"/>
+      <c r="B984" s="7"/>
       <c r="C984" s="1"/>
       <c r="D984" s="1"/>
       <c r="E984" s="1"/>
@@ -23265,7 +23268,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="985" customHeight="1" ht="18">
       <c r="A985" s="1"/>
-      <c r="B985" s="2"/>
+      <c r="B985" s="7"/>
       <c r="C985" s="1"/>
       <c r="D985" s="1"/>
       <c r="E985" s="1"/>
@@ -23288,7 +23291,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="986" customHeight="1" ht="18">
       <c r="A986" s="1"/>
-      <c r="B986" s="2"/>
+      <c r="B986" s="7"/>
       <c r="C986" s="1"/>
       <c r="D986" s="1"/>
       <c r="E986" s="1"/>
@@ -23311,7 +23314,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="987" customHeight="1" ht="18">
       <c r="A987" s="1"/>
-      <c r="B987" s="2"/>
+      <c r="B987" s="7"/>
       <c r="C987" s="1"/>
       <c r="D987" s="1"/>
       <c r="E987" s="1"/>
@@ -23334,7 +23337,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="988" customHeight="1" ht="18">
       <c r="A988" s="1"/>
-      <c r="B988" s="2"/>
+      <c r="B988" s="7"/>
       <c r="C988" s="1"/>
       <c r="D988" s="1"/>
       <c r="E988" s="1"/>
@@ -23357,7 +23360,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="989" customHeight="1" ht="18">
       <c r="A989" s="1"/>
-      <c r="B989" s="2"/>
+      <c r="B989" s="7"/>
       <c r="C989" s="1"/>
       <c r="D989" s="1"/>
       <c r="E989" s="1"/>
@@ -23380,7 +23383,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="990" customHeight="1" ht="18">
       <c r="A990" s="1"/>
-      <c r="B990" s="2"/>
+      <c r="B990" s="7"/>
       <c r="C990" s="1"/>
       <c r="D990" s="1"/>
       <c r="E990" s="1"/>
@@ -23403,7 +23406,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="991" customHeight="1" ht="18">
       <c r="A991" s="1"/>
-      <c r="B991" s="2"/>
+      <c r="B991" s="7"/>
       <c r="C991" s="1"/>
       <c r="D991" s="1"/>
       <c r="E991" s="1"/>
@@ -23426,7 +23429,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="992" customHeight="1" ht="18">
       <c r="A992" s="1"/>
-      <c r="B992" s="2"/>
+      <c r="B992" s="7"/>
       <c r="C992" s="1"/>
       <c r="D992" s="1"/>
       <c r="E992" s="1"/>
@@ -23449,7 +23452,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="993" customHeight="1" ht="18">
       <c r="A993" s="1"/>
-      <c r="B993" s="2"/>
+      <c r="B993" s="7"/>
       <c r="C993" s="1"/>
       <c r="D993" s="1"/>
       <c r="E993" s="1"/>
@@ -23472,7 +23475,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="994" customHeight="1" ht="18">
       <c r="A994" s="1"/>
-      <c r="B994" s="2"/>
+      <c r="B994" s="7"/>
       <c r="C994" s="1"/>
       <c r="D994" s="1"/>
       <c r="E994" s="1"/>
@@ -23495,7 +23498,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="995" customHeight="1" ht="18">
       <c r="A995" s="1"/>
-      <c r="B995" s="2"/>
+      <c r="B995" s="7"/>
       <c r="C995" s="1"/>
       <c r="D995" s="1"/>
       <c r="E995" s="1"/>
@@ -23518,7 +23521,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="996" customHeight="1" ht="18">
       <c r="A996" s="1"/>
-      <c r="B996" s="2"/>
+      <c r="B996" s="7"/>
       <c r="C996" s="1"/>
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
@@ -23541,7 +23544,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="997" customHeight="1" ht="18">
       <c r="A997" s="1"/>
-      <c r="B997" s="2"/>
+      <c r="B997" s="7"/>
       <c r="C997" s="1"/>
       <c r="D997" s="1"/>
       <c r="E997" s="1"/>
@@ -23564,7 +23567,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="998" customHeight="1" ht="18">
       <c r="A998" s="1"/>
-      <c r="B998" s="2"/>
+      <c r="B998" s="7"/>
       <c r="C998" s="1"/>
       <c r="D998" s="1"/>
       <c r="E998" s="1"/>
@@ -23587,7 +23590,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="999" customHeight="1" ht="18">
       <c r="A999" s="1"/>
-      <c r="B999" s="2"/>
+      <c r="B999" s="7"/>
       <c r="C999" s="1"/>
       <c r="D999" s="1"/>
       <c r="E999" s="1"/>
@@ -23606,53 +23609,53 @@
       <c r="R999" s="1"/>
       <c r="S999" s="1"/>
       <c r="T999" s="1"/>
-      <c r="U999" s="10"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1000" customHeight="1" ht="18" customFormat="1" s="12">
-      <c r="A1000" s="11"/>
-      <c r="B1000" s="2"/>
-      <c r="C1000" s="11"/>
-      <c r="D1000" s="11"/>
-      <c r="E1000" s="11"/>
-      <c r="F1000" s="11"/>
-      <c r="G1000" s="11"/>
-      <c r="H1000" s="11"/>
-      <c r="I1000" s="11"/>
-      <c r="J1000" s="11"/>
-      <c r="K1000" s="11"/>
-      <c r="L1000" s="11"/>
-      <c r="M1000" s="11"/>
-      <c r="N1000" s="11"/>
-      <c r="O1000" s="11"/>
-      <c r="P1000" s="11"/>
-      <c r="Q1000" s="11"/>
-      <c r="R1000" s="11"/>
-      <c r="S1000" s="11"/>
-      <c r="T1000" s="11"/>
-      <c r="U1000" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="1001" customHeight="1" ht="18" customFormat="1" s="12">
-      <c r="A1001" s="11"/>
-      <c r="B1001" s="2"/>
-      <c r="C1001" s="11"/>
-      <c r="D1001" s="11"/>
-      <c r="E1001" s="11"/>
-      <c r="F1001" s="11"/>
-      <c r="G1001" s="11"/>
-      <c r="H1001" s="11"/>
-      <c r="I1001" s="11"/>
-      <c r="J1001" s="11"/>
-      <c r="K1001" s="11"/>
-      <c r="L1001" s="11"/>
-      <c r="M1001" s="11"/>
-      <c r="N1001" s="11"/>
-      <c r="O1001" s="11"/>
-      <c r="P1001" s="11"/>
-      <c r="Q1001" s="11"/>
-      <c r="R1001" s="11"/>
-      <c r="S1001" s="11"/>
-      <c r="T1001" s="11"/>
-      <c r="U1001" s="11"/>
+      <c r="U999" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="1000" customHeight="1" ht="18" customFormat="1" s="13">
+      <c r="A1000" s="12"/>
+      <c r="B1000" s="7"/>
+      <c r="C1000" s="12"/>
+      <c r="D1000" s="12"/>
+      <c r="E1000" s="12"/>
+      <c r="F1000" s="12"/>
+      <c r="G1000" s="12"/>
+      <c r="H1000" s="12"/>
+      <c r="I1000" s="12"/>
+      <c r="J1000" s="12"/>
+      <c r="K1000" s="12"/>
+      <c r="L1000" s="12"/>
+      <c r="M1000" s="12"/>
+      <c r="N1000" s="12"/>
+      <c r="O1000" s="12"/>
+      <c r="P1000" s="12"/>
+      <c r="Q1000" s="12"/>
+      <c r="R1000" s="12"/>
+      <c r="S1000" s="12"/>
+      <c r="T1000" s="12"/>
+      <c r="U1000" s="12"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="1001" customHeight="1" ht="18" customFormat="1" s="13">
+      <c r="A1001" s="12"/>
+      <c r="B1001" s="7"/>
+      <c r="C1001" s="12"/>
+      <c r="D1001" s="12"/>
+      <c r="E1001" s="12"/>
+      <c r="F1001" s="12"/>
+      <c r="G1001" s="12"/>
+      <c r="H1001" s="12"/>
+      <c r="I1001" s="12"/>
+      <c r="J1001" s="12"/>
+      <c r="K1001" s="12"/>
+      <c r="L1001" s="12"/>
+      <c r="M1001" s="12"/>
+      <c r="N1001" s="12"/>
+      <c r="O1001" s="12"/>
+      <c r="P1001" s="12"/>
+      <c r="Q1001" s="12"/>
+      <c r="R1001" s="12"/>
+      <c r="S1001" s="12"/>
+      <c r="T1001" s="12"/>
+      <c r="U1001" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23697,7 +23700,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1"/>
@@ -23879,7 +23882,7 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="1"/>
-      <c r="B7" s="8"/>
+      <c r="B7" s="9"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -51723,12 +51726,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="13.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="40.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="40.57642857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -51753,20 +51756,20 @@
       <c r="B5" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="7"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="7"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="7"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="1"/>
-      <c r="B9" s="8"/>
+      <c r="B9" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
